--- a/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
+++ b/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
@@ -1573,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N179"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="3" customWidth="1" style="21" min="1" max="1"/>
@@ -1596,7 +1596,6 @@
       </c>
       <c r="C1" s="48" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="37" t="inlineStr">
         <is>
@@ -1825,7 +1824,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="B10" s="37" t="inlineStr">
         <is>
@@ -1968,7 +1966,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="37" t="inlineStr">
         <is>
@@ -2111,7 +2108,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="37" t="inlineStr">
         <is>
@@ -2254,7 +2250,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="37" t="inlineStr">
         <is>
@@ -2550,7 +2545,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="B33" s="37" t="inlineStr">
         <is>
@@ -2846,7 +2840,6 @@
         <v/>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="B41" s="37" t="inlineStr">
         <is>
@@ -3142,8 +3135,6 @@
         <v/>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50" ht="19.2" customHeight="1" s="21">
       <c r="A50" s="113" t="n"/>
       <c r="B50" s="114" t="inlineStr">
@@ -6344,7 +6335,11 @@
     </row>
     <row r="148">
       <c r="A148" s="113" t="n"/>
-      <c r="B148" s="113" t="n"/>
+      <c r="B148" s="115" t="inlineStr">
+        <is>
+          <t>5. 유통사별 품목별 쿠폰 사용액</t>
+        </is>
+      </c>
       <c r="C148" s="113" t="n"/>
       <c r="D148" s="113" t="n"/>
       <c r="E148" s="113" t="n"/>
@@ -6360,11 +6355,31 @@
     </row>
     <row r="149">
       <c r="A149" s="113" t="n"/>
-      <c r="B149" s="113" t="n"/>
-      <c r="C149" s="113" t="n"/>
-      <c r="D149" s="113" t="n"/>
-      <c r="E149" s="113" t="n"/>
-      <c r="F149" s="113" t="n"/>
+      <c r="B149" s="116" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C149" s="116" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D149" s="116" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="E149" s="116" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F149" s="116" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
       <c r="G149" s="113" t="n"/>
       <c r="H149" s="113" t="n"/>
       <c r="I149" s="113" t="n"/>
@@ -6376,11 +6391,24 @@
     </row>
     <row r="150">
       <c r="A150" s="113" t="n"/>
-      <c r="B150" s="113" t="n"/>
-      <c r="C150" s="113" t="n"/>
-      <c r="D150" s="113" t="n"/>
-      <c r="E150" s="113" t="n"/>
-      <c r="F150" s="113" t="n"/>
+      <c r="B150" s="116" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="C150" s="117" t="n"/>
+      <c r="D150" s="124">
+        <f>SUM(E150:F150)</f>
+        <v/>
+      </c>
+      <c r="E150" s="124">
+        <f>E151+E154+E157</f>
+        <v/>
+      </c>
+      <c r="F150" s="124">
+        <f>F151+F154+F157</f>
+        <v/>
+      </c>
       <c r="G150" s="113" t="n"/>
       <c r="H150" s="113" t="n"/>
       <c r="I150" s="113" t="n"/>
@@ -6392,11 +6420,28 @@
     </row>
     <row r="151">
       <c r="A151" s="113" t="n"/>
-      <c r="B151" s="113" t="n"/>
-      <c r="C151" s="113" t="n"/>
-      <c r="D151" s="122" t="n"/>
-      <c r="E151" s="122" t="n"/>
-      <c r="F151" s="122" t="n"/>
+      <c r="B151" s="118" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="C151" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D151" s="125">
+        <f>SUM(E151:F151)</f>
+        <v/>
+      </c>
+      <c r="E151" s="125">
+        <f>E152+E153</f>
+        <v/>
+      </c>
+      <c r="F151" s="125">
+        <f>F152+F153</f>
+        <v/>
+      </c>
       <c r="G151" s="113" t="n"/>
       <c r="H151" s="113" t="n"/>
       <c r="I151" s="113" t="n"/>
@@ -6408,11 +6453,22 @@
     </row>
     <row r="152">
       <c r="A152" s="113" t="n"/>
-      <c r="B152" s="113" t="n"/>
-      <c r="C152" s="113" t="n"/>
-      <c r="D152" s="122" t="n"/>
-      <c r="E152" s="122" t="n"/>
-      <c r="F152" s="122" t="n"/>
+      <c r="B152" s="126" t="n"/>
+      <c r="C152" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D152" s="120">
+        <f>SUM(E152:F152)</f>
+        <v/>
+      </c>
+      <c r="E152" s="120" t="n">
+        <v>8603490</v>
+      </c>
+      <c r="F152" s="120" t="n">
+        <v>4825119</v>
+      </c>
       <c r="G152" s="113" t="n"/>
       <c r="H152" s="113" t="n"/>
       <c r="I152" s="113" t="n"/>
@@ -6424,11 +6480,24 @@
     </row>
     <row r="153">
       <c r="A153" s="113" t="n"/>
-      <c r="B153" s="113" t="n"/>
-      <c r="C153" s="113" t="n"/>
-      <c r="D153" s="122" t="n"/>
-      <c r="E153" s="122" t="n"/>
-      <c r="F153" s="122" t="n"/>
+      <c r="B153" s="121" t="n"/>
+      <c r="C153" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D153" s="120">
+        <f>SUM(E153:F153)</f>
+        <v/>
+      </c>
+      <c r="E153" s="120">
+        <f>SUMIFS('②유기농raw'!$H$6:$H$207,'②유기농raw'!$A$6:$A$207,E$149,'②유기농raw'!$B$6:$B$207,$B151)-E152</f>
+        <v/>
+      </c>
+      <c r="F153" s="120">
+        <f>SUMIFS('②유기농raw'!$H$6:$H$207,'②유기농raw'!$A$6:$A$207,F$149,'②유기농raw'!$B$6:$B$207,$B151)-F152</f>
+        <v/>
+      </c>
       <c r="G153" s="113" t="n"/>
       <c r="H153" s="113" t="n"/>
       <c r="I153" s="113" t="n"/>
@@ -6440,11 +6509,28 @@
     </row>
     <row r="154">
       <c r="A154" s="113" t="n"/>
-      <c r="B154" s="113" t="n"/>
-      <c r="C154" s="113" t="n"/>
-      <c r="D154" s="122" t="n"/>
-      <c r="E154" s="122" t="n"/>
-      <c r="F154" s="122" t="n"/>
+      <c r="B154" s="118" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="C154" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D154" s="125">
+        <f>SUM(E154:F154)</f>
+        <v/>
+      </c>
+      <c r="E154" s="125">
+        <f>E155+E156</f>
+        <v/>
+      </c>
+      <c r="F154" s="125">
+        <f>F155+F156</f>
+        <v/>
+      </c>
       <c r="G154" s="113" t="n"/>
       <c r="H154" s="113" t="n"/>
       <c r="I154" s="113" t="n"/>
@@ -6456,11 +6542,22 @@
     </row>
     <row r="155">
       <c r="A155" s="113" t="n"/>
-      <c r="B155" s="113" t="n"/>
-      <c r="C155" s="113" t="n"/>
-      <c r="D155" s="122" t="n"/>
-      <c r="E155" s="122" t="n"/>
-      <c r="F155" s="122" t="n"/>
+      <c r="B155" s="126" t="n"/>
+      <c r="C155" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D155" s="120">
+        <f>SUM(E155:F155)</f>
+        <v/>
+      </c>
+      <c r="E155" s="120" t="n">
+        <v>25800</v>
+      </c>
+      <c r="F155" s="120" t="n">
+        <v>251120</v>
+      </c>
       <c r="G155" s="113" t="n"/>
       <c r="H155" s="113" t="n"/>
       <c r="I155" s="113" t="n"/>
@@ -6472,11 +6569,24 @@
     </row>
     <row r="156">
       <c r="A156" s="113" t="n"/>
-      <c r="B156" s="113" t="n"/>
-      <c r="C156" s="113" t="n"/>
-      <c r="D156" s="122" t="n"/>
-      <c r="E156" s="122" t="n"/>
-      <c r="F156" s="122" t="n"/>
+      <c r="B156" s="121" t="n"/>
+      <c r="C156" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D156" s="120">
+        <f>SUM(E156:F156)</f>
+        <v/>
+      </c>
+      <c r="E156" s="120">
+        <f>SUMIFS('②유기농raw'!$H$6:$H$207,'②유기농raw'!$A$6:$A$207,E$149,'②유기농raw'!$B$6:$B$207,$B154)-E155</f>
+        <v/>
+      </c>
+      <c r="F156" s="120">
+        <f>SUMIFS('②유기농raw'!$H$6:$H$207,'②유기농raw'!$A$6:$A$207,F$149,'②유기농raw'!$B$6:$B$207,$B154)-F155</f>
+        <v/>
+      </c>
       <c r="G156" s="113" t="n"/>
       <c r="H156" s="113" t="n"/>
       <c r="I156" s="113" t="n"/>
@@ -6488,11 +6598,28 @@
     </row>
     <row r="157">
       <c r="A157" s="113" t="n"/>
-      <c r="B157" s="113" t="n"/>
-      <c r="C157" s="113" t="n"/>
-      <c r="D157" s="122" t="n"/>
-      <c r="E157" s="122" t="n"/>
-      <c r="F157" s="122" t="n"/>
+      <c r="B157" s="118" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="C157" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D157" s="125">
+        <f>SUM(E157:F157)</f>
+        <v/>
+      </c>
+      <c r="E157" s="125">
+        <f>E158+E159</f>
+        <v/>
+      </c>
+      <c r="F157" s="125">
+        <f>F158+F159</f>
+        <v/>
+      </c>
       <c r="G157" s="113" t="n"/>
       <c r="H157" s="113" t="n"/>
       <c r="I157" s="113" t="n"/>
@@ -6504,11 +6631,22 @@
     </row>
     <row r="158">
       <c r="A158" s="113" t="n"/>
-      <c r="B158" s="113" t="n"/>
-      <c r="C158" s="113" t="n"/>
-      <c r="D158" s="113" t="n"/>
-      <c r="E158" s="113" t="n"/>
-      <c r="F158" s="113" t="n"/>
+      <c r="B158" s="126" t="n"/>
+      <c r="C158" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D158" s="120">
+        <f>SUM(E158:F158)</f>
+        <v/>
+      </c>
+      <c r="E158" s="120" t="n">
+        <v>1784210</v>
+      </c>
+      <c r="F158" s="120" t="n">
+        <v>4544192</v>
+      </c>
       <c r="G158" s="113" t="n"/>
       <c r="H158" s="113" t="n"/>
       <c r="I158" s="113" t="n"/>
@@ -6520,11 +6658,24 @@
     </row>
     <row r="159">
       <c r="A159" s="113" t="n"/>
-      <c r="B159" s="113" t="n"/>
-      <c r="C159" s="113" t="n"/>
-      <c r="D159" s="113" t="n"/>
-      <c r="E159" s="113" t="n"/>
-      <c r="F159" s="113" t="n"/>
+      <c r="B159" s="121" t="n"/>
+      <c r="C159" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D159" s="120">
+        <f>SUM(E159:F159)</f>
+        <v/>
+      </c>
+      <c r="E159" s="120">
+        <f>SUMIFS('②유기농raw'!$H$6:$H$207,'②유기농raw'!$A$6:$A$207,E$149,'②유기농raw'!$B$6:$B$207,$B157)-E158</f>
+        <v/>
+      </c>
+      <c r="F159" s="120">
+        <f>SUMIFS('②유기농raw'!$H$6:$H$207,'②유기농raw'!$A$6:$A$207,F$149,'②유기농raw'!$B$6:$B$207,$B157)-F158</f>
+        <v/>
+      </c>
       <c r="G159" s="113" t="n"/>
       <c r="H159" s="113" t="n"/>
       <c r="I159" s="113" t="n"/>
@@ -6552,7 +6703,11 @@
     </row>
     <row r="161">
       <c r="A161" s="113" t="n"/>
-      <c r="B161" s="113" t="n"/>
+      <c r="B161" s="115" t="inlineStr">
+        <is>
+          <t>6. 유통사별 품목별 매출 분석</t>
+        </is>
+      </c>
       <c r="C161" s="113" t="n"/>
       <c r="D161" s="113" t="n"/>
       <c r="E161" s="113" t="n"/>
@@ -6568,11 +6723,31 @@
     </row>
     <row r="162">
       <c r="A162" s="113" t="n"/>
-      <c r="B162" s="113" t="n"/>
-      <c r="C162" s="113" t="n"/>
-      <c r="D162" s="113" t="n"/>
-      <c r="E162" s="113" t="n"/>
-      <c r="F162" s="113" t="n"/>
+      <c r="B162" s="116" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C162" s="116" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D162" s="116" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="E162" s="116" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F162" s="116" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
       <c r="G162" s="113" t="n"/>
       <c r="H162" s="113" t="n"/>
       <c r="I162" s="113" t="n"/>
@@ -6584,11 +6759,24 @@
     </row>
     <row r="163">
       <c r="A163" s="113" t="n"/>
-      <c r="B163" s="113" t="n"/>
-      <c r="C163" s="113" t="n"/>
-      <c r="D163" s="113" t="n"/>
-      <c r="E163" s="113" t="n"/>
-      <c r="F163" s="113" t="n"/>
+      <c r="B163" s="116" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="C163" s="117" t="n"/>
+      <c r="D163" s="124">
+        <f>SUM(E163:F163)</f>
+        <v/>
+      </c>
+      <c r="E163" s="124">
+        <f>E164+E167+E170</f>
+        <v/>
+      </c>
+      <c r="F163" s="124">
+        <f>F164+F167+F170</f>
+        <v/>
+      </c>
       <c r="G163" s="113" t="n"/>
       <c r="H163" s="113" t="n"/>
       <c r="I163" s="113" t="n"/>
@@ -6600,11 +6788,28 @@
     </row>
     <row r="164">
       <c r="A164" s="113" t="n"/>
-      <c r="B164" s="113" t="n"/>
-      <c r="C164" s="113" t="n"/>
-      <c r="D164" s="113" t="n"/>
-      <c r="E164" s="113" t="n"/>
-      <c r="F164" s="113" t="n"/>
+      <c r="B164" s="118" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="C164" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D164" s="125">
+        <f>SUM(E164:F164)</f>
+        <v/>
+      </c>
+      <c r="E164" s="125">
+        <f>E165+E166</f>
+        <v/>
+      </c>
+      <c r="F164" s="125">
+        <f>F165+F166</f>
+        <v/>
+      </c>
       <c r="G164" s="113" t="n"/>
       <c r="H164" s="113" t="n"/>
       <c r="I164" s="113" t="n"/>
@@ -6616,11 +6821,22 @@
     </row>
     <row r="165">
       <c r="A165" s="113" t="n"/>
-      <c r="B165" s="113" t="n"/>
-      <c r="C165" s="113" t="n"/>
-      <c r="D165" s="113" t="n"/>
-      <c r="E165" s="113" t="n"/>
-      <c r="F165" s="113" t="n"/>
+      <c r="B165" s="126" t="n"/>
+      <c r="C165" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D165" s="120">
+        <f>SUM(E165:F165)</f>
+        <v/>
+      </c>
+      <c r="E165" s="120" t="n">
+        <v>92842530</v>
+      </c>
+      <c r="F165" s="120" t="n">
+        <v>435129830</v>
+      </c>
       <c r="G165" s="113" t="n"/>
       <c r="H165" s="113" t="n"/>
       <c r="I165" s="113" t="n"/>
@@ -6632,11 +6848,24 @@
     </row>
     <row r="166">
       <c r="A166" s="113" t="n"/>
-      <c r="B166" s="113" t="n"/>
-      <c r="C166" s="113" t="n"/>
-      <c r="D166" s="113" t="n"/>
-      <c r="E166" s="113" t="n"/>
-      <c r="F166" s="113" t="n"/>
+      <c r="B166" s="121" t="n"/>
+      <c r="C166" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D166" s="120">
+        <f>SUM(E166:F166)</f>
+        <v/>
+      </c>
+      <c r="E166" s="120">
+        <f>SUMIFS('②유기농raw'!$G$6:$G$207,'②유기농raw'!$A$6:$A$207,E$162,'②유기농raw'!$B$6:$B$207,$B164)-E165</f>
+        <v/>
+      </c>
+      <c r="F166" s="120">
+        <f>SUMIFS('②유기농raw'!$G$6:$G$207,'②유기농raw'!$A$6:$A$207,F$162,'②유기농raw'!$B$6:$B$207,$B164)-F165</f>
+        <v/>
+      </c>
       <c r="G166" s="113" t="n"/>
       <c r="H166" s="113" t="n"/>
       <c r="I166" s="113" t="n"/>
@@ -6648,11 +6877,28 @@
     </row>
     <row r="167">
       <c r="A167" s="113" t="n"/>
-      <c r="B167" s="113" t="n"/>
-      <c r="C167" s="113" t="n"/>
-      <c r="D167" s="113" t="n"/>
-      <c r="E167" s="113" t="n"/>
-      <c r="F167" s="113" t="n"/>
+      <c r="B167" s="118" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="C167" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D167" s="125">
+        <f>SUM(E167:F167)</f>
+        <v/>
+      </c>
+      <c r="E167" s="125">
+        <f>E168+E169</f>
+        <v/>
+      </c>
+      <c r="F167" s="125">
+        <f>F168+F169</f>
+        <v/>
+      </c>
       <c r="G167" s="113" t="n"/>
       <c r="H167" s="113" t="n"/>
       <c r="I167" s="113" t="n"/>
@@ -6664,11 +6910,22 @@
     </row>
     <row r="168">
       <c r="A168" s="113" t="n"/>
-      <c r="B168" s="113" t="n"/>
-      <c r="C168" s="113" t="n"/>
-      <c r="D168" s="113" t="n"/>
-      <c r="E168" s="113" t="n"/>
-      <c r="F168" s="113" t="n"/>
+      <c r="B168" s="126" t="n"/>
+      <c r="C168" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D168" s="120">
+        <f>SUM(E168:F168)</f>
+        <v/>
+      </c>
+      <c r="E168" s="120" t="n">
+        <v>132000</v>
+      </c>
+      <c r="F168" s="120" t="n">
+        <v>3448700</v>
+      </c>
       <c r="G168" s="113" t="n"/>
       <c r="H168" s="113" t="n"/>
       <c r="I168" s="113" t="n"/>
@@ -6680,11 +6937,24 @@
     </row>
     <row r="169">
       <c r="A169" s="113" t="n"/>
-      <c r="B169" s="113" t="n"/>
-      <c r="C169" s="113" t="n"/>
-      <c r="D169" s="113" t="n"/>
-      <c r="E169" s="113" t="n"/>
-      <c r="F169" s="113" t="n"/>
+      <c r="B169" s="121" t="n"/>
+      <c r="C169" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D169" s="120">
+        <f>SUM(E169:F169)</f>
+        <v/>
+      </c>
+      <c r="E169" s="120">
+        <f>SUMIFS('②유기농raw'!$G$6:$G$207,'②유기농raw'!$A$6:$A$207,E$162,'②유기농raw'!$B$6:$B$207,$B167)-E168</f>
+        <v/>
+      </c>
+      <c r="F169" s="120">
+        <f>SUMIFS('②유기농raw'!$G$6:$G$207,'②유기농raw'!$A$6:$A$207,F$162,'②유기농raw'!$B$6:$B$207,$B167)-F168</f>
+        <v/>
+      </c>
       <c r="G169" s="113" t="n"/>
       <c r="H169" s="113" t="n"/>
       <c r="I169" s="113" t="n"/>
@@ -6696,11 +6966,28 @@
     </row>
     <row r="170">
       <c r="A170" s="113" t="n"/>
-      <c r="B170" s="113" t="n"/>
-      <c r="C170" s="113" t="n"/>
-      <c r="D170" s="113" t="n"/>
-      <c r="E170" s="113" t="n"/>
-      <c r="F170" s="113" t="n"/>
+      <c r="B170" s="118" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="C170" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D170" s="125">
+        <f>SUM(E170:F170)</f>
+        <v/>
+      </c>
+      <c r="E170" s="125">
+        <f>E171+E172</f>
+        <v/>
+      </c>
+      <c r="F170" s="125">
+        <f>F171+F172</f>
+        <v/>
+      </c>
       <c r="G170" s="113" t="n"/>
       <c r="H170" s="113" t="n"/>
       <c r="I170" s="113" t="n"/>
@@ -6712,11 +6999,22 @@
     </row>
     <row r="171">
       <c r="A171" s="113" t="n"/>
-      <c r="B171" s="113" t="n"/>
-      <c r="C171" s="113" t="n"/>
-      <c r="D171" s="113" t="n"/>
-      <c r="E171" s="113" t="n"/>
-      <c r="F171" s="113" t="n"/>
+      <c r="B171" s="126" t="n"/>
+      <c r="C171" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D171" s="120">
+        <f>SUM(E171:F171)</f>
+        <v/>
+      </c>
+      <c r="E171" s="120" t="n">
+        <v>15398300</v>
+      </c>
+      <c r="F171" s="120" t="n">
+        <v>99623530</v>
+      </c>
       <c r="G171" s="113" t="n"/>
       <c r="H171" s="113" t="n"/>
       <c r="I171" s="113" t="n"/>
@@ -6728,11 +7026,24 @@
     </row>
     <row r="172">
       <c r="A172" s="113" t="n"/>
-      <c r="B172" s="113" t="n"/>
-      <c r="C172" s="113" t="n"/>
-      <c r="D172" s="113" t="n"/>
-      <c r="E172" s="113" t="n"/>
-      <c r="F172" s="113" t="n"/>
+      <c r="B172" s="121" t="n"/>
+      <c r="C172" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D172" s="120">
+        <f>SUM(E172:F172)</f>
+        <v/>
+      </c>
+      <c r="E172" s="120">
+        <f>SUMIFS('②유기농raw'!$G$6:$G$207,'②유기농raw'!$A$6:$A$207,E$162,'②유기농raw'!$B$6:$B$207,$B170)-E171</f>
+        <v/>
+      </c>
+      <c r="F172" s="120">
+        <f>SUMIFS('②유기농raw'!$G$6:$G$207,'②유기농raw'!$A$6:$A$207,F$162,'②유기농raw'!$B$6:$B$207,$B170)-F171</f>
+        <v/>
+      </c>
       <c r="G172" s="113" t="n"/>
       <c r="H172" s="113" t="n"/>
       <c r="I172" s="113" t="n"/>
@@ -6760,7 +7071,11 @@
     </row>
     <row r="174">
       <c r="A174" s="113" t="n"/>
-      <c r="B174" s="113" t="n"/>
+      <c r="B174" s="115" t="inlineStr">
+        <is>
+          <t>7. 유통사별 품목별 판매 건수</t>
+        </is>
+      </c>
       <c r="C174" s="113" t="n"/>
       <c r="D174" s="113" t="n"/>
       <c r="E174" s="113" t="n"/>
@@ -6776,11 +7091,31 @@
     </row>
     <row r="175">
       <c r="A175" s="113" t="n"/>
-      <c r="B175" s="113" t="n"/>
-      <c r="C175" s="113" t="n"/>
-      <c r="D175" s="113" t="n"/>
-      <c r="E175" s="113" t="n"/>
-      <c r="F175" s="113" t="n"/>
+      <c r="B175" s="116" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C175" s="116" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D175" s="116" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="E175" s="116" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F175" s="116" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
       <c r="G175" s="113" t="n"/>
       <c r="H175" s="113" t="n"/>
       <c r="I175" s="113" t="n"/>
@@ -6792,11 +7127,24 @@
     </row>
     <row r="176">
       <c r="A176" s="113" t="n"/>
-      <c r="B176" s="113" t="n"/>
-      <c r="C176" s="113" t="n"/>
-      <c r="D176" s="113" t="n"/>
-      <c r="E176" s="113" t="n"/>
-      <c r="F176" s="113" t="n"/>
+      <c r="B176" s="116" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="C176" s="117" t="n"/>
+      <c r="D176" s="124">
+        <f>SUM(E176:F176)</f>
+        <v/>
+      </c>
+      <c r="E176" s="124">
+        <f>E177+E180+E183</f>
+        <v/>
+      </c>
+      <c r="F176" s="124">
+        <f>F177+F180+F183</f>
+        <v/>
+      </c>
       <c r="G176" s="113" t="n"/>
       <c r="H176" s="113" t="n"/>
       <c r="I176" s="113" t="n"/>
@@ -6808,11 +7156,28 @@
     </row>
     <row r="177">
       <c r="A177" s="113" t="n"/>
-      <c r="B177" s="113" t="n"/>
-      <c r="C177" s="113" t="n"/>
-      <c r="D177" s="113" t="n"/>
-      <c r="E177" s="113" t="n"/>
-      <c r="F177" s="113" t="n"/>
+      <c r="B177" s="118" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="C177" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D177" s="125">
+        <f>SUM(E177:F177)</f>
+        <v/>
+      </c>
+      <c r="E177" s="125">
+        <f>E178+E179</f>
+        <v/>
+      </c>
+      <c r="F177" s="125">
+        <f>F178+F179</f>
+        <v/>
+      </c>
       <c r="G177" s="113" t="n"/>
       <c r="H177" s="113" t="n"/>
       <c r="I177" s="113" t="n"/>
@@ -6824,11 +7189,22 @@
     </row>
     <row r="178">
       <c r="A178" s="113" t="n"/>
-      <c r="B178" s="113" t="n"/>
-      <c r="C178" s="113" t="n"/>
-      <c r="D178" s="113" t="n"/>
-      <c r="E178" s="113" t="n"/>
-      <c r="F178" s="113" t="n"/>
+      <c r="B178" s="126" t="n"/>
+      <c r="C178" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D178" s="120">
+        <f>SUM(E178:F178)</f>
+        <v/>
+      </c>
+      <c r="E178" s="120" t="n">
+        <v>3893</v>
+      </c>
+      <c r="F178" s="120" t="n">
+        <v>100661</v>
+      </c>
       <c r="G178" s="113" t="n"/>
       <c r="H178" s="113" t="n"/>
       <c r="I178" s="113" t="n"/>
@@ -6840,11 +7216,24 @@
     </row>
     <row r="179">
       <c r="A179" s="113" t="n"/>
-      <c r="B179" s="113" t="n"/>
-      <c r="C179" s="113" t="n"/>
-      <c r="D179" s="113" t="n"/>
-      <c r="E179" s="113" t="n"/>
-      <c r="F179" s="113" t="n"/>
+      <c r="B179" s="121" t="n"/>
+      <c r="C179" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D179" s="120">
+        <f>SUM(E179:F179)</f>
+        <v/>
+      </c>
+      <c r="E179" s="120">
+        <f>SUMIFS('②유기농raw'!$F$6:$F$207,'②유기농raw'!$A$6:$A$207,E$175,'②유기농raw'!$B$6:$B$207,$B177)-E178</f>
+        <v/>
+      </c>
+      <c r="F179" s="120">
+        <f>SUMIFS('②유기농raw'!$F$6:$F$207,'②유기농raw'!$A$6:$A$207,F$175,'②유기농raw'!$B$6:$B$207,$B177)-F178</f>
+        <v/>
+      </c>
       <c r="G179" s="113" t="n"/>
       <c r="H179" s="113" t="n"/>
       <c r="I179" s="113" t="n"/>
@@ -6854,82 +7243,1296 @@
       <c r="M179" s="113" t="n"/>
       <c r="N179" s="113" t="n"/>
     </row>
+    <row r="180">
+      <c r="A180" s="113" t="n"/>
+      <c r="B180" s="118" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="C180" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D180" s="125">
+        <f>SUM(E180:F180)</f>
+        <v/>
+      </c>
+      <c r="E180" s="125">
+        <f>E181+E182</f>
+        <v/>
+      </c>
+      <c r="F180" s="125">
+        <f>F181+F182</f>
+        <v/>
+      </c>
+      <c r="G180" s="113" t="n"/>
+      <c r="H180" s="113" t="n"/>
+      <c r="I180" s="113" t="n"/>
+      <c r="J180" s="113" t="n"/>
+      <c r="K180" s="113" t="n"/>
+      <c r="L180" s="113" t="n"/>
+      <c r="M180" s="113" t="n"/>
+      <c r="N180" s="113" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="113" t="n"/>
+      <c r="B181" s="126" t="n"/>
+      <c r="C181" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D181" s="120">
+        <f>SUM(E181:F181)</f>
+        <v/>
+      </c>
+      <c r="E181" s="120" t="n">
+        <v>5</v>
+      </c>
+      <c r="F181" s="120" t="n">
+        <v>598</v>
+      </c>
+      <c r="G181" s="113" t="n"/>
+      <c r="H181" s="113" t="n"/>
+      <c r="I181" s="113" t="n"/>
+      <c r="J181" s="113" t="n"/>
+      <c r="K181" s="113" t="n"/>
+      <c r="L181" s="113" t="n"/>
+      <c r="M181" s="113" t="n"/>
+      <c r="N181" s="113" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="113" t="n"/>
+      <c r="B182" s="121" t="n"/>
+      <c r="C182" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D182" s="120">
+        <f>SUM(E182:F182)</f>
+        <v/>
+      </c>
+      <c r="E182" s="120">
+        <f>SUMIFS('②유기농raw'!$F$6:$F$207,'②유기농raw'!$A$6:$A$207,E$175,'②유기농raw'!$B$6:$B$207,$B180)-E181</f>
+        <v/>
+      </c>
+      <c r="F182" s="120">
+        <f>SUMIFS('②유기농raw'!$F$6:$F$207,'②유기농raw'!$A$6:$A$207,F$175,'②유기농raw'!$B$6:$B$207,$B180)-F181</f>
+        <v/>
+      </c>
+      <c r="G182" s="113" t="n"/>
+      <c r="H182" s="113" t="n"/>
+      <c r="I182" s="113" t="n"/>
+      <c r="J182" s="113" t="n"/>
+      <c r="K182" s="113" t="n"/>
+      <c r="L182" s="113" t="n"/>
+      <c r="M182" s="113" t="n"/>
+      <c r="N182" s="113" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="113" t="n"/>
+      <c r="B183" s="118" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="C183" s="118" t="inlineStr">
+        <is>
+          <t>소 계</t>
+        </is>
+      </c>
+      <c r="D183" s="125">
+        <f>SUM(E183:F183)</f>
+        <v/>
+      </c>
+      <c r="E183" s="125">
+        <f>E184+E185</f>
+        <v/>
+      </c>
+      <c r="F183" s="125">
+        <f>F184+F185</f>
+        <v/>
+      </c>
+      <c r="G183" s="113" t="n"/>
+      <c r="H183" s="113" t="n"/>
+      <c r="I183" s="113" t="n"/>
+      <c r="J183" s="113" t="n"/>
+      <c r="K183" s="113" t="n"/>
+      <c r="L183" s="113" t="n"/>
+      <c r="M183" s="113" t="n"/>
+      <c r="N183" s="113" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="113" t="n"/>
+      <c r="B184" s="126" t="n"/>
+      <c r="C184" s="119" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="D184" s="120">
+        <f>SUM(E184:F184)</f>
+        <v/>
+      </c>
+      <c r="E184" s="120" t="n">
+        <v>580</v>
+      </c>
+      <c r="F184" s="120" t="n">
+        <v>21914</v>
+      </c>
+      <c r="G184" s="113" t="n"/>
+      <c r="H184" s="113" t="n"/>
+      <c r="I184" s="113" t="n"/>
+      <c r="J184" s="113" t="n"/>
+      <c r="K184" s="113" t="n"/>
+      <c r="L184" s="113" t="n"/>
+      <c r="M184" s="113" t="n"/>
+      <c r="N184" s="113" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="113" t="n"/>
+      <c r="B185" s="121" t="n"/>
+      <c r="C185" s="119" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="D185" s="120">
+        <f>SUM(E185:F185)</f>
+        <v/>
+      </c>
+      <c r="E185" s="120">
+        <f>SUMIFS('②유기농raw'!$F$6:$F$207,'②유기농raw'!$A$6:$A$207,E$175,'②유기농raw'!$B$6:$B$207,$B183)-E184</f>
+        <v/>
+      </c>
+      <c r="F185" s="120">
+        <f>SUMIFS('②유기농raw'!$F$6:$F$207,'②유기농raw'!$A$6:$A$207,F$175,'②유기농raw'!$B$6:$B$207,$B183)-F184</f>
+        <v/>
+      </c>
+      <c r="G185" s="113" t="n"/>
+      <c r="H185" s="113" t="n"/>
+      <c r="I185" s="113" t="n"/>
+      <c r="J185" s="113" t="n"/>
+      <c r="K185" s="113" t="n"/>
+      <c r="L185" s="113" t="n"/>
+      <c r="M185" s="113" t="n"/>
+      <c r="N185" s="113" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="113" t="n"/>
+      <c r="B186" s="113" t="n"/>
+      <c r="C186" s="113" t="n"/>
+      <c r="D186" s="113" t="n"/>
+      <c r="E186" s="113" t="n"/>
+      <c r="F186" s="113" t="n"/>
+      <c r="G186" s="113" t="n"/>
+      <c r="H186" s="113" t="n"/>
+      <c r="I186" s="113" t="n"/>
+      <c r="J186" s="113" t="n"/>
+      <c r="K186" s="113" t="n"/>
+      <c r="L186" s="113" t="n"/>
+      <c r="M186" s="113" t="n"/>
+      <c r="N186" s="113" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="113" t="n"/>
+      <c r="B187" s="113" t="n"/>
+      <c r="C187" s="113" t="n"/>
+      <c r="D187" s="113" t="n"/>
+      <c r="E187" s="113" t="n"/>
+      <c r="F187" s="113" t="n"/>
+      <c r="G187" s="113" t="n"/>
+      <c r="H187" s="113" t="n"/>
+      <c r="I187" s="113" t="n"/>
+      <c r="J187" s="113" t="n"/>
+      <c r="K187" s="113" t="n"/>
+      <c r="L187" s="113" t="n"/>
+      <c r="M187" s="113" t="n"/>
+      <c r="N187" s="113" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="113" t="n"/>
+      <c r="B188" s="113" t="n"/>
+      <c r="C188" s="113" t="n"/>
+      <c r="D188" s="113" t="n"/>
+      <c r="E188" s="113" t="n"/>
+      <c r="F188" s="113" t="n"/>
+      <c r="G188" s="113" t="n"/>
+      <c r="H188" s="113" t="n"/>
+      <c r="I188" s="113" t="n"/>
+      <c r="J188" s="113" t="n"/>
+      <c r="K188" s="113" t="n"/>
+      <c r="L188" s="113" t="n"/>
+      <c r="M188" s="113" t="n"/>
+      <c r="N188" s="113" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="113" t="n"/>
+      <c r="B189" s="113" t="n"/>
+      <c r="C189" s="113" t="n"/>
+      <c r="D189" s="113" t="n"/>
+      <c r="E189" s="113" t="n"/>
+      <c r="F189" s="113" t="n"/>
+      <c r="G189" s="113" t="n"/>
+      <c r="H189" s="113" t="n"/>
+      <c r="I189" s="113" t="n"/>
+      <c r="J189" s="113" t="n"/>
+      <c r="K189" s="113" t="n"/>
+      <c r="L189" s="113" t="n"/>
+      <c r="M189" s="113" t="n"/>
+      <c r="N189" s="113" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="113" t="n"/>
+      <c r="B190" s="113" t="n"/>
+      <c r="C190" s="113" t="n"/>
+      <c r="D190" s="113" t="n"/>
+      <c r="E190" s="113" t="n"/>
+      <c r="F190" s="113" t="n"/>
+      <c r="G190" s="113" t="n"/>
+      <c r="H190" s="113" t="n"/>
+      <c r="I190" s="113" t="n"/>
+      <c r="J190" s="113" t="n"/>
+      <c r="K190" s="113" t="n"/>
+      <c r="L190" s="113" t="n"/>
+      <c r="M190" s="113" t="n"/>
+      <c r="N190" s="113" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="113" t="n"/>
+      <c r="B191" s="113" t="n"/>
+      <c r="C191" s="113" t="n"/>
+      <c r="D191" s="113" t="n"/>
+      <c r="E191" s="113" t="n"/>
+      <c r="F191" s="113" t="n"/>
+      <c r="G191" s="113" t="n"/>
+      <c r="H191" s="113" t="n"/>
+      <c r="I191" s="113" t="n"/>
+      <c r="J191" s="113" t="n"/>
+      <c r="K191" s="113" t="n"/>
+      <c r="L191" s="113" t="n"/>
+      <c r="M191" s="113" t="n"/>
+      <c r="N191" s="113" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="113" t="n"/>
+      <c r="B192" s="113" t="n"/>
+      <c r="C192" s="113" t="n"/>
+      <c r="D192" s="113" t="n"/>
+      <c r="E192" s="113" t="n"/>
+      <c r="F192" s="113" t="n"/>
+      <c r="G192" s="113" t="n"/>
+      <c r="H192" s="113" t="n"/>
+      <c r="I192" s="113" t="n"/>
+      <c r="J192" s="113" t="n"/>
+      <c r="K192" s="113" t="n"/>
+      <c r="L192" s="113" t="n"/>
+      <c r="M192" s="113" t="n"/>
+      <c r="N192" s="113" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="113" t="n"/>
+      <c r="B193" s="113" t="n"/>
+      <c r="C193" s="113" t="n"/>
+      <c r="D193" s="113" t="n"/>
+      <c r="E193" s="113" t="n"/>
+      <c r="F193" s="113" t="n"/>
+      <c r="G193" s="113" t="n"/>
+      <c r="H193" s="113" t="n"/>
+      <c r="I193" s="113" t="n"/>
+      <c r="J193" s="113" t="n"/>
+      <c r="K193" s="113" t="n"/>
+      <c r="L193" s="113" t="n"/>
+      <c r="M193" s="113" t="n"/>
+      <c r="N193" s="113" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="113" t="n"/>
+      <c r="B194" s="113" t="n"/>
+      <c r="C194" s="113" t="n"/>
+      <c r="D194" s="113" t="n"/>
+      <c r="E194" s="113" t="n"/>
+      <c r="F194" s="113" t="n"/>
+      <c r="G194" s="113" t="n"/>
+      <c r="H194" s="113" t="n"/>
+      <c r="I194" s="113" t="n"/>
+      <c r="J194" s="113" t="n"/>
+      <c r="K194" s="113" t="n"/>
+      <c r="L194" s="113" t="n"/>
+      <c r="M194" s="113" t="n"/>
+      <c r="N194" s="113" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="113" t="n"/>
+      <c r="B195" s="113" t="n"/>
+      <c r="C195" s="113" t="n"/>
+      <c r="D195" s="113" t="n"/>
+      <c r="E195" s="113" t="n"/>
+      <c r="F195" s="113" t="n"/>
+      <c r="G195" s="113" t="n"/>
+      <c r="H195" s="113" t="n"/>
+      <c r="I195" s="113" t="n"/>
+      <c r="J195" s="113" t="n"/>
+      <c r="K195" s="113" t="n"/>
+      <c r="L195" s="113" t="n"/>
+      <c r="M195" s="113" t="n"/>
+      <c r="N195" s="113" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="113" t="n"/>
+      <c r="B196" s="113" t="n"/>
+      <c r="C196" s="113" t="n"/>
+      <c r="D196" s="113" t="n"/>
+      <c r="E196" s="113" t="n"/>
+      <c r="F196" s="113" t="n"/>
+      <c r="G196" s="113" t="n"/>
+      <c r="H196" s="113" t="n"/>
+      <c r="I196" s="113" t="n"/>
+      <c r="J196" s="113" t="n"/>
+      <c r="K196" s="113" t="n"/>
+      <c r="L196" s="113" t="n"/>
+      <c r="M196" s="113" t="n"/>
+      <c r="N196" s="113" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="113" t="n"/>
+      <c r="B197" s="113" t="n"/>
+      <c r="C197" s="113" t="n"/>
+      <c r="D197" s="113" t="n"/>
+      <c r="E197" s="113" t="n"/>
+      <c r="F197" s="113" t="n"/>
+      <c r="G197" s="113" t="n"/>
+      <c r="H197" s="113" t="n"/>
+      <c r="I197" s="113" t="n"/>
+      <c r="J197" s="113" t="n"/>
+      <c r="K197" s="113" t="n"/>
+      <c r="L197" s="113" t="n"/>
+      <c r="M197" s="113" t="n"/>
+      <c r="N197" s="113" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="113" t="n"/>
+      <c r="B198" s="113" t="n"/>
+      <c r="C198" s="113" t="n"/>
+      <c r="D198" s="113" t="n"/>
+      <c r="E198" s="113" t="n"/>
+      <c r="F198" s="113" t="n"/>
+      <c r="G198" s="113" t="n"/>
+      <c r="H198" s="113" t="n"/>
+      <c r="I198" s="113" t="n"/>
+      <c r="J198" s="113" t="n"/>
+      <c r="K198" s="113" t="n"/>
+      <c r="L198" s="113" t="n"/>
+      <c r="M198" s="113" t="n"/>
+      <c r="N198" s="113" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="113" t="n"/>
+      <c r="B199" s="113" t="n"/>
+      <c r="C199" s="113" t="n"/>
+      <c r="D199" s="113" t="n"/>
+      <c r="E199" s="113" t="n"/>
+      <c r="F199" s="113" t="n"/>
+      <c r="G199" s="113" t="n"/>
+      <c r="H199" s="113" t="n"/>
+      <c r="I199" s="113" t="n"/>
+      <c r="J199" s="113" t="n"/>
+      <c r="K199" s="113" t="n"/>
+      <c r="L199" s="113" t="n"/>
+      <c r="M199" s="113" t="n"/>
+      <c r="N199" s="113" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="113" t="n"/>
+      <c r="B200" s="113" t="n"/>
+      <c r="C200" s="113" t="n"/>
+      <c r="D200" s="113" t="n"/>
+      <c r="E200" s="113" t="n"/>
+      <c r="F200" s="113" t="n"/>
+      <c r="G200" s="113" t="n"/>
+      <c r="H200" s="113" t="n"/>
+      <c r="I200" s="113" t="n"/>
+      <c r="J200" s="113" t="n"/>
+      <c r="K200" s="113" t="n"/>
+      <c r="L200" s="113" t="n"/>
+      <c r="M200" s="113" t="n"/>
+      <c r="N200" s="113" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="113" t="n"/>
+      <c r="B201" s="113" t="n"/>
+      <c r="C201" s="113" t="n"/>
+      <c r="D201" s="113" t="n"/>
+      <c r="E201" s="113" t="n"/>
+      <c r="F201" s="113" t="n"/>
+      <c r="G201" s="113" t="n"/>
+      <c r="H201" s="113" t="n"/>
+      <c r="I201" s="113" t="n"/>
+      <c r="J201" s="113" t="n"/>
+      <c r="K201" s="113" t="n"/>
+      <c r="L201" s="113" t="n"/>
+      <c r="M201" s="113" t="n"/>
+      <c r="N201" s="113" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="113" t="n"/>
+      <c r="B202" s="113" t="n"/>
+      <c r="C202" s="113" t="n"/>
+      <c r="D202" s="113" t="n"/>
+      <c r="E202" s="113" t="n"/>
+      <c r="F202" s="113" t="n"/>
+      <c r="G202" s="113" t="n"/>
+      <c r="H202" s="113" t="n"/>
+      <c r="I202" s="113" t="n"/>
+      <c r="J202" s="113" t="n"/>
+      <c r="K202" s="113" t="n"/>
+      <c r="L202" s="113" t="n"/>
+      <c r="M202" s="113" t="n"/>
+      <c r="N202" s="113" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="113" t="n"/>
+      <c r="B203" s="113" t="n"/>
+      <c r="C203" s="113" t="n"/>
+      <c r="D203" s="113" t="n"/>
+      <c r="E203" s="113" t="n"/>
+      <c r="F203" s="113" t="n"/>
+      <c r="G203" s="113" t="n"/>
+      <c r="H203" s="113" t="n"/>
+      <c r="I203" s="113" t="n"/>
+      <c r="J203" s="113" t="n"/>
+      <c r="K203" s="113" t="n"/>
+      <c r="L203" s="113" t="n"/>
+      <c r="M203" s="113" t="n"/>
+      <c r="N203" s="113" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="113" t="n"/>
+      <c r="B204" s="113" t="n"/>
+      <c r="C204" s="113" t="n"/>
+      <c r="D204" s="113" t="n"/>
+      <c r="E204" s="113" t="n"/>
+      <c r="F204" s="113" t="n"/>
+      <c r="G204" s="113" t="n"/>
+      <c r="H204" s="113" t="n"/>
+      <c r="I204" s="113" t="n"/>
+      <c r="J204" s="113" t="n"/>
+      <c r="K204" s="113" t="n"/>
+      <c r="L204" s="113" t="n"/>
+      <c r="M204" s="113" t="n"/>
+      <c r="N204" s="113" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="113" t="n"/>
+      <c r="B205" s="113" t="n"/>
+      <c r="C205" s="113" t="n"/>
+      <c r="D205" s="113" t="n"/>
+      <c r="E205" s="113" t="n"/>
+      <c r="F205" s="113" t="n"/>
+      <c r="G205" s="113" t="n"/>
+      <c r="H205" s="113" t="n"/>
+      <c r="I205" s="113" t="n"/>
+      <c r="J205" s="113" t="n"/>
+      <c r="K205" s="113" t="n"/>
+      <c r="L205" s="113" t="n"/>
+      <c r="M205" s="113" t="n"/>
+      <c r="N205" s="113" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="113" t="n"/>
+      <c r="B206" s="113" t="n"/>
+      <c r="C206" s="113" t="n"/>
+      <c r="D206" s="113" t="n"/>
+      <c r="E206" s="113" t="n"/>
+      <c r="F206" s="113" t="n"/>
+      <c r="G206" s="113" t="n"/>
+      <c r="H206" s="113" t="n"/>
+      <c r="I206" s="113" t="n"/>
+      <c r="J206" s="113" t="n"/>
+      <c r="K206" s="113" t="n"/>
+      <c r="L206" s="113" t="n"/>
+      <c r="M206" s="113" t="n"/>
+      <c r="N206" s="113" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="113" t="n"/>
+      <c r="B207" s="113" t="n"/>
+      <c r="C207" s="113" t="n"/>
+      <c r="D207" s="113" t="n"/>
+      <c r="E207" s="113" t="n"/>
+      <c r="F207" s="113" t="n"/>
+      <c r="G207" s="113" t="n"/>
+      <c r="H207" s="113" t="n"/>
+      <c r="I207" s="113" t="n"/>
+      <c r="J207" s="113" t="n"/>
+      <c r="K207" s="113" t="n"/>
+      <c r="L207" s="113" t="n"/>
+      <c r="M207" s="113" t="n"/>
+      <c r="N207" s="113" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="113" t="n"/>
+      <c r="B208" s="113" t="n"/>
+      <c r="C208" s="113" t="n"/>
+      <c r="D208" s="113" t="n"/>
+      <c r="E208" s="113" t="n"/>
+      <c r="F208" s="113" t="n"/>
+      <c r="G208" s="113" t="n"/>
+      <c r="H208" s="113" t="n"/>
+      <c r="I208" s="113" t="n"/>
+      <c r="J208" s="113" t="n"/>
+      <c r="K208" s="113" t="n"/>
+      <c r="L208" s="113" t="n"/>
+      <c r="M208" s="113" t="n"/>
+      <c r="N208" s="113" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="113" t="n"/>
+      <c r="B209" s="113" t="n"/>
+      <c r="C209" s="113" t="n"/>
+      <c r="D209" s="113" t="n"/>
+      <c r="E209" s="113" t="n"/>
+      <c r="F209" s="113" t="n"/>
+      <c r="G209" s="113" t="n"/>
+      <c r="H209" s="113" t="n"/>
+      <c r="I209" s="113" t="n"/>
+      <c r="J209" s="113" t="n"/>
+      <c r="K209" s="113" t="n"/>
+      <c r="L209" s="113" t="n"/>
+      <c r="M209" s="113" t="n"/>
+      <c r="N209" s="113" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="113" t="n"/>
+      <c r="B210" s="113" t="n"/>
+      <c r="C210" s="113" t="n"/>
+      <c r="D210" s="113" t="n"/>
+      <c r="E210" s="113" t="n"/>
+      <c r="F210" s="113" t="n"/>
+      <c r="G210" s="113" t="n"/>
+      <c r="H210" s="113" t="n"/>
+      <c r="I210" s="113" t="n"/>
+      <c r="J210" s="113" t="n"/>
+      <c r="K210" s="113" t="n"/>
+      <c r="L210" s="113" t="n"/>
+      <c r="M210" s="113" t="n"/>
+      <c r="N210" s="113" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="113" t="n"/>
+      <c r="B211" s="113" t="n"/>
+      <c r="C211" s="113" t="n"/>
+      <c r="D211" s="113" t="n"/>
+      <c r="E211" s="113" t="n"/>
+      <c r="F211" s="113" t="n"/>
+      <c r="G211" s="113" t="n"/>
+      <c r="H211" s="113" t="n"/>
+      <c r="I211" s="113" t="n"/>
+      <c r="J211" s="113" t="n"/>
+      <c r="K211" s="113" t="n"/>
+      <c r="L211" s="113" t="n"/>
+      <c r="M211" s="113" t="n"/>
+      <c r="N211" s="113" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="113" t="n"/>
+      <c r="B212" s="113" t="n"/>
+      <c r="C212" s="113" t="n"/>
+      <c r="D212" s="113" t="n"/>
+      <c r="E212" s="113" t="n"/>
+      <c r="F212" s="113" t="n"/>
+      <c r="G212" s="113" t="n"/>
+      <c r="H212" s="113" t="n"/>
+      <c r="I212" s="113" t="n"/>
+      <c r="J212" s="113" t="n"/>
+      <c r="K212" s="113" t="n"/>
+      <c r="L212" s="113" t="n"/>
+      <c r="M212" s="113" t="n"/>
+      <c r="N212" s="113" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="113" t="n"/>
+      <c r="B213" s="113" t="n"/>
+      <c r="C213" s="113" t="n"/>
+      <c r="D213" s="113" t="n"/>
+      <c r="E213" s="113" t="n"/>
+      <c r="F213" s="113" t="n"/>
+      <c r="G213" s="113" t="n"/>
+      <c r="H213" s="113" t="n"/>
+      <c r="I213" s="113" t="n"/>
+      <c r="J213" s="113" t="n"/>
+      <c r="K213" s="113" t="n"/>
+      <c r="L213" s="113" t="n"/>
+      <c r="M213" s="113" t="n"/>
+      <c r="N213" s="113" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="113" t="n"/>
+      <c r="B214" s="113" t="n"/>
+      <c r="C214" s="113" t="n"/>
+      <c r="D214" s="113" t="n"/>
+      <c r="E214" s="113" t="n"/>
+      <c r="F214" s="113" t="n"/>
+      <c r="G214" s="113" t="n"/>
+      <c r="H214" s="113" t="n"/>
+      <c r="I214" s="113" t="n"/>
+      <c r="J214" s="113" t="n"/>
+      <c r="K214" s="113" t="n"/>
+      <c r="L214" s="113" t="n"/>
+      <c r="M214" s="113" t="n"/>
+      <c r="N214" s="113" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="113" t="n"/>
+      <c r="B215" s="113" t="n"/>
+      <c r="C215" s="113" t="n"/>
+      <c r="D215" s="113" t="n"/>
+      <c r="E215" s="113" t="n"/>
+      <c r="F215" s="113" t="n"/>
+      <c r="G215" s="113" t="n"/>
+      <c r="H215" s="113" t="n"/>
+      <c r="I215" s="113" t="n"/>
+      <c r="J215" s="113" t="n"/>
+      <c r="K215" s="113" t="n"/>
+      <c r="L215" s="113" t="n"/>
+      <c r="M215" s="113" t="n"/>
+      <c r="N215" s="113" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="113" t="n"/>
+      <c r="B216" s="113" t="n"/>
+      <c r="C216" s="113" t="n"/>
+      <c r="D216" s="113" t="n"/>
+      <c r="E216" s="113" t="n"/>
+      <c r="F216" s="113" t="n"/>
+      <c r="G216" s="113" t="n"/>
+      <c r="H216" s="113" t="n"/>
+      <c r="I216" s="113" t="n"/>
+      <c r="J216" s="113" t="n"/>
+      <c r="K216" s="113" t="n"/>
+      <c r="L216" s="113" t="n"/>
+      <c r="M216" s="113" t="n"/>
+      <c r="N216" s="113" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="113" t="n"/>
+      <c r="B217" s="113" t="n"/>
+      <c r="C217" s="113" t="n"/>
+      <c r="D217" s="113" t="n"/>
+      <c r="E217" s="113" t="n"/>
+      <c r="F217" s="113" t="n"/>
+      <c r="G217" s="113" t="n"/>
+      <c r="H217" s="113" t="n"/>
+      <c r="I217" s="113" t="n"/>
+      <c r="J217" s="113" t="n"/>
+      <c r="K217" s="113" t="n"/>
+      <c r="L217" s="113" t="n"/>
+      <c r="M217" s="113" t="n"/>
+      <c r="N217" s="113" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="113" t="n"/>
+      <c r="B218" s="113" t="n"/>
+      <c r="C218" s="113" t="n"/>
+      <c r="D218" s="113" t="n"/>
+      <c r="E218" s="113" t="n"/>
+      <c r="F218" s="113" t="n"/>
+      <c r="G218" s="113" t="n"/>
+      <c r="H218" s="113" t="n"/>
+      <c r="I218" s="113" t="n"/>
+      <c r="J218" s="113" t="n"/>
+      <c r="K218" s="113" t="n"/>
+      <c r="L218" s="113" t="n"/>
+      <c r="M218" s="113" t="n"/>
+      <c r="N218" s="113" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="113" t="n"/>
+      <c r="B219" s="113" t="n"/>
+      <c r="C219" s="113" t="n"/>
+      <c r="D219" s="113" t="n"/>
+      <c r="E219" s="113" t="n"/>
+      <c r="F219" s="113" t="n"/>
+      <c r="G219" s="113" t="n"/>
+      <c r="H219" s="113" t="n"/>
+      <c r="I219" s="113" t="n"/>
+      <c r="J219" s="113" t="n"/>
+      <c r="K219" s="113" t="n"/>
+      <c r="L219" s="113" t="n"/>
+      <c r="M219" s="113" t="n"/>
+      <c r="N219" s="113" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="113" t="n"/>
+      <c r="B220" s="113" t="n"/>
+      <c r="C220" s="113" t="n"/>
+      <c r="D220" s="113" t="n"/>
+      <c r="E220" s="113" t="n"/>
+      <c r="F220" s="113" t="n"/>
+      <c r="G220" s="113" t="n"/>
+      <c r="H220" s="113" t="n"/>
+      <c r="I220" s="113" t="n"/>
+      <c r="J220" s="113" t="n"/>
+      <c r="K220" s="113" t="n"/>
+      <c r="L220" s="113" t="n"/>
+      <c r="M220" s="113" t="n"/>
+      <c r="N220" s="113" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="113" t="n"/>
+      <c r="B221" s="113" t="n"/>
+      <c r="C221" s="113" t="n"/>
+      <c r="D221" s="113" t="n"/>
+      <c r="E221" s="113" t="n"/>
+      <c r="F221" s="113" t="n"/>
+      <c r="G221" s="113" t="n"/>
+      <c r="H221" s="113" t="n"/>
+      <c r="I221" s="113" t="n"/>
+      <c r="J221" s="113" t="n"/>
+      <c r="K221" s="113" t="n"/>
+      <c r="L221" s="113" t="n"/>
+      <c r="M221" s="113" t="n"/>
+      <c r="N221" s="113" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="113" t="n"/>
+      <c r="B222" s="113" t="n"/>
+      <c r="C222" s="113" t="n"/>
+      <c r="D222" s="113" t="n"/>
+      <c r="E222" s="113" t="n"/>
+      <c r="F222" s="113" t="n"/>
+      <c r="G222" s="113" t="n"/>
+      <c r="H222" s="113" t="n"/>
+      <c r="I222" s="113" t="n"/>
+      <c r="J222" s="113" t="n"/>
+      <c r="K222" s="113" t="n"/>
+      <c r="L222" s="113" t="n"/>
+      <c r="M222" s="113" t="n"/>
+      <c r="N222" s="113" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="113" t="n"/>
+      <c r="B223" s="113" t="n"/>
+      <c r="C223" s="113" t="n"/>
+      <c r="D223" s="113" t="n"/>
+      <c r="E223" s="113" t="n"/>
+      <c r="F223" s="113" t="n"/>
+      <c r="G223" s="113" t="n"/>
+      <c r="H223" s="113" t="n"/>
+      <c r="I223" s="113" t="n"/>
+      <c r="J223" s="113" t="n"/>
+      <c r="K223" s="113" t="n"/>
+      <c r="L223" s="113" t="n"/>
+      <c r="M223" s="113" t="n"/>
+      <c r="N223" s="113" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="113" t="n"/>
+      <c r="B224" s="113" t="n"/>
+      <c r="C224" s="113" t="n"/>
+      <c r="D224" s="113" t="n"/>
+      <c r="E224" s="113" t="n"/>
+      <c r="F224" s="113" t="n"/>
+      <c r="G224" s="113" t="n"/>
+      <c r="H224" s="113" t="n"/>
+      <c r="I224" s="113" t="n"/>
+      <c r="J224" s="113" t="n"/>
+      <c r="K224" s="113" t="n"/>
+      <c r="L224" s="113" t="n"/>
+      <c r="M224" s="113" t="n"/>
+      <c r="N224" s="113" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="113" t="n"/>
+      <c r="B225" s="113" t="n"/>
+      <c r="C225" s="113" t="n"/>
+      <c r="D225" s="113" t="n"/>
+      <c r="E225" s="113" t="n"/>
+      <c r="F225" s="113" t="n"/>
+      <c r="G225" s="113" t="n"/>
+      <c r="H225" s="113" t="n"/>
+      <c r="I225" s="113" t="n"/>
+      <c r="J225" s="113" t="n"/>
+      <c r="K225" s="113" t="n"/>
+      <c r="L225" s="113" t="n"/>
+      <c r="M225" s="113" t="n"/>
+      <c r="N225" s="113" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="113" t="n"/>
+      <c r="B226" s="113" t="n"/>
+      <c r="C226" s="113" t="n"/>
+      <c r="D226" s="113" t="n"/>
+      <c r="E226" s="113" t="n"/>
+      <c r="F226" s="113" t="n"/>
+      <c r="G226" s="113" t="n"/>
+      <c r="H226" s="113" t="n"/>
+      <c r="I226" s="113" t="n"/>
+      <c r="J226" s="113" t="n"/>
+      <c r="K226" s="113" t="n"/>
+      <c r="L226" s="113" t="n"/>
+      <c r="M226" s="113" t="n"/>
+      <c r="N226" s="113" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="113" t="n"/>
+      <c r="B227" s="113" t="n"/>
+      <c r="C227" s="113" t="n"/>
+      <c r="D227" s="113" t="n"/>
+      <c r="E227" s="113" t="n"/>
+      <c r="F227" s="113" t="n"/>
+      <c r="G227" s="113" t="n"/>
+      <c r="H227" s="113" t="n"/>
+      <c r="I227" s="113" t="n"/>
+      <c r="J227" s="113" t="n"/>
+      <c r="K227" s="113" t="n"/>
+      <c r="L227" s="113" t="n"/>
+      <c r="M227" s="113" t="n"/>
+      <c r="N227" s="113" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="113" t="n"/>
+      <c r="B228" s="113" t="n"/>
+      <c r="C228" s="113" t="n"/>
+      <c r="D228" s="113" t="n"/>
+      <c r="E228" s="113" t="n"/>
+      <c r="F228" s="113" t="n"/>
+      <c r="G228" s="113" t="n"/>
+      <c r="H228" s="113" t="n"/>
+      <c r="I228" s="113" t="n"/>
+      <c r="J228" s="113" t="n"/>
+      <c r="K228" s="113" t="n"/>
+      <c r="L228" s="113" t="n"/>
+      <c r="M228" s="113" t="n"/>
+      <c r="N228" s="113" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="113" t="n"/>
+      <c r="B229" s="113" t="n"/>
+      <c r="C229" s="113" t="n"/>
+      <c r="D229" s="113" t="n"/>
+      <c r="E229" s="113" t="n"/>
+      <c r="F229" s="113" t="n"/>
+      <c r="G229" s="113" t="n"/>
+      <c r="H229" s="113" t="n"/>
+      <c r="I229" s="113" t="n"/>
+      <c r="J229" s="113" t="n"/>
+      <c r="K229" s="113" t="n"/>
+      <c r="L229" s="113" t="n"/>
+      <c r="M229" s="113" t="n"/>
+      <c r="N229" s="113" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="113" t="n"/>
+      <c r="B230" s="113" t="n"/>
+      <c r="C230" s="113" t="n"/>
+      <c r="D230" s="113" t="n"/>
+      <c r="E230" s="113" t="n"/>
+      <c r="F230" s="113" t="n"/>
+      <c r="G230" s="113" t="n"/>
+      <c r="H230" s="113" t="n"/>
+      <c r="I230" s="113" t="n"/>
+      <c r="J230" s="113" t="n"/>
+      <c r="K230" s="113" t="n"/>
+      <c r="L230" s="113" t="n"/>
+      <c r="M230" s="113" t="n"/>
+      <c r="N230" s="113" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="113" t="n"/>
+      <c r="B231" s="113" t="n"/>
+      <c r="C231" s="113" t="n"/>
+      <c r="D231" s="113" t="n"/>
+      <c r="E231" s="113" t="n"/>
+      <c r="F231" s="113" t="n"/>
+      <c r="G231" s="113" t="n"/>
+      <c r="H231" s="113" t="n"/>
+      <c r="I231" s="113" t="n"/>
+      <c r="J231" s="113" t="n"/>
+      <c r="K231" s="113" t="n"/>
+      <c r="L231" s="113" t="n"/>
+      <c r="M231" s="113" t="n"/>
+      <c r="N231" s="113" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="113" t="n"/>
+      <c r="B232" s="113" t="n"/>
+      <c r="C232" s="113" t="n"/>
+      <c r="D232" s="113" t="n"/>
+      <c r="E232" s="113" t="n"/>
+      <c r="F232" s="113" t="n"/>
+      <c r="G232" s="113" t="n"/>
+      <c r="H232" s="113" t="n"/>
+      <c r="I232" s="113" t="n"/>
+      <c r="J232" s="113" t="n"/>
+      <c r="K232" s="113" t="n"/>
+      <c r="L232" s="113" t="n"/>
+      <c r="M232" s="113" t="n"/>
+      <c r="N232" s="113" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="113" t="n"/>
+      <c r="B233" s="113" t="n"/>
+      <c r="C233" s="113" t="n"/>
+      <c r="D233" s="113" t="n"/>
+      <c r="E233" s="113" t="n"/>
+      <c r="F233" s="113" t="n"/>
+      <c r="G233" s="113" t="n"/>
+      <c r="H233" s="113" t="n"/>
+      <c r="I233" s="113" t="n"/>
+      <c r="J233" s="113" t="n"/>
+      <c r="K233" s="113" t="n"/>
+      <c r="L233" s="113" t="n"/>
+      <c r="M233" s="113" t="n"/>
+      <c r="N233" s="113" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="113" t="n"/>
+      <c r="B234" s="113" t="n"/>
+      <c r="C234" s="113" t="n"/>
+      <c r="D234" s="113" t="n"/>
+      <c r="E234" s="113" t="n"/>
+      <c r="F234" s="113" t="n"/>
+      <c r="G234" s="113" t="n"/>
+      <c r="H234" s="113" t="n"/>
+      <c r="I234" s="113" t="n"/>
+      <c r="J234" s="113" t="n"/>
+      <c r="K234" s="113" t="n"/>
+      <c r="L234" s="113" t="n"/>
+      <c r="M234" s="113" t="n"/>
+      <c r="N234" s="113" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="113" t="n"/>
+      <c r="B235" s="113" t="n"/>
+      <c r="C235" s="113" t="n"/>
+      <c r="D235" s="113" t="n"/>
+      <c r="E235" s="113" t="n"/>
+      <c r="F235" s="113" t="n"/>
+      <c r="G235" s="113" t="n"/>
+      <c r="H235" s="113" t="n"/>
+      <c r="I235" s="113" t="n"/>
+      <c r="J235" s="113" t="n"/>
+      <c r="K235" s="113" t="n"/>
+      <c r="L235" s="113" t="n"/>
+      <c r="M235" s="113" t="n"/>
+      <c r="N235" s="113" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="113" t="n"/>
+      <c r="B236" s="113" t="n"/>
+      <c r="C236" s="113" t="n"/>
+      <c r="D236" s="113" t="n"/>
+      <c r="E236" s="113" t="n"/>
+      <c r="F236" s="113" t="n"/>
+      <c r="G236" s="113" t="n"/>
+      <c r="H236" s="113" t="n"/>
+      <c r="I236" s="113" t="n"/>
+      <c r="J236" s="113" t="n"/>
+      <c r="K236" s="113" t="n"/>
+      <c r="L236" s="113" t="n"/>
+      <c r="M236" s="113" t="n"/>
+      <c r="N236" s="113" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="113" t="n"/>
+      <c r="B237" s="113" t="n"/>
+      <c r="C237" s="113" t="n"/>
+      <c r="D237" s="113" t="n"/>
+      <c r="E237" s="113" t="n"/>
+      <c r="F237" s="113" t="n"/>
+      <c r="G237" s="113" t="n"/>
+      <c r="H237" s="113" t="n"/>
+      <c r="I237" s="113" t="n"/>
+      <c r="J237" s="113" t="n"/>
+      <c r="K237" s="113" t="n"/>
+      <c r="L237" s="113" t="n"/>
+      <c r="M237" s="113" t="n"/>
+      <c r="N237" s="113" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="113" t="n"/>
+      <c r="B238" s="113" t="n"/>
+      <c r="C238" s="113" t="n"/>
+      <c r="D238" s="113" t="n"/>
+      <c r="E238" s="113" t="n"/>
+      <c r="F238" s="113" t="n"/>
+      <c r="G238" s="113" t="n"/>
+      <c r="H238" s="113" t="n"/>
+      <c r="I238" s="113" t="n"/>
+      <c r="J238" s="113" t="n"/>
+      <c r="K238" s="113" t="n"/>
+      <c r="L238" s="113" t="n"/>
+      <c r="M238" s="113" t="n"/>
+      <c r="N238" s="113" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="113" t="n"/>
+      <c r="B239" s="113" t="n"/>
+      <c r="C239" s="113" t="n"/>
+      <c r="D239" s="113" t="n"/>
+      <c r="E239" s="113" t="n"/>
+      <c r="F239" s="113" t="n"/>
+      <c r="G239" s="113" t="n"/>
+      <c r="H239" s="113" t="n"/>
+      <c r="I239" s="113" t="n"/>
+      <c r="J239" s="113" t="n"/>
+      <c r="K239" s="113" t="n"/>
+      <c r="L239" s="113" t="n"/>
+      <c r="M239" s="113" t="n"/>
+      <c r="N239" s="113" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="113" t="n"/>
+      <c r="B240" s="113" t="n"/>
+      <c r="C240" s="113" t="n"/>
+      <c r="D240" s="113" t="n"/>
+      <c r="E240" s="113" t="n"/>
+      <c r="F240" s="113" t="n"/>
+      <c r="G240" s="113" t="n"/>
+      <c r="H240" s="113" t="n"/>
+      <c r="I240" s="113" t="n"/>
+      <c r="J240" s="113" t="n"/>
+      <c r="K240" s="113" t="n"/>
+      <c r="L240" s="113" t="n"/>
+      <c r="M240" s="113" t="n"/>
+      <c r="N240" s="113" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="113" t="n"/>
+      <c r="B241" s="113" t="n"/>
+      <c r="C241" s="113" t="n"/>
+      <c r="D241" s="113" t="n"/>
+      <c r="E241" s="113" t="n"/>
+      <c r="F241" s="113" t="n"/>
+      <c r="G241" s="113" t="n"/>
+      <c r="H241" s="113" t="n"/>
+      <c r="I241" s="113" t="n"/>
+      <c r="J241" s="113" t="n"/>
+      <c r="K241" s="113" t="n"/>
+      <c r="L241" s="113" t="n"/>
+      <c r="M241" s="113" t="n"/>
+      <c r="N241" s="113" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="113" t="n"/>
+      <c r="B242" s="113" t="n"/>
+      <c r="C242" s="113" t="n"/>
+      <c r="D242" s="113" t="n"/>
+      <c r="E242" s="113" t="n"/>
+      <c r="F242" s="113" t="n"/>
+      <c r="G242" s="113" t="n"/>
+      <c r="H242" s="113" t="n"/>
+      <c r="I242" s="113" t="n"/>
+      <c r="J242" s="113" t="n"/>
+      <c r="K242" s="113" t="n"/>
+      <c r="L242" s="113" t="n"/>
+      <c r="M242" s="113" t="n"/>
+      <c r="N242" s="113" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="113" t="n"/>
+      <c r="B243" s="113" t="n"/>
+      <c r="C243" s="113" t="n"/>
+      <c r="D243" s="113" t="n"/>
+      <c r="E243" s="113" t="n"/>
+      <c r="F243" s="113" t="n"/>
+      <c r="G243" s="113" t="n"/>
+      <c r="H243" s="113" t="n"/>
+      <c r="I243" s="113" t="n"/>
+      <c r="J243" s="113" t="n"/>
+      <c r="K243" s="113" t="n"/>
+      <c r="L243" s="113" t="n"/>
+      <c r="M243" s="113" t="n"/>
+      <c r="N243" s="113" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="113" t="n"/>
+      <c r="B244" s="113" t="n"/>
+      <c r="C244" s="113" t="n"/>
+      <c r="D244" s="113" t="n"/>
+      <c r="E244" s="113" t="n"/>
+      <c r="F244" s="113" t="n"/>
+      <c r="G244" s="113" t="n"/>
+      <c r="H244" s="113" t="n"/>
+      <c r="I244" s="113" t="n"/>
+      <c r="J244" s="113" t="n"/>
+      <c r="K244" s="113" t="n"/>
+      <c r="L244" s="113" t="n"/>
+      <c r="M244" s="113" t="n"/>
+      <c r="N244" s="113" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="113" t="n"/>
+      <c r="B245" s="113" t="n"/>
+      <c r="C245" s="113" t="n"/>
+      <c r="D245" s="113" t="n"/>
+      <c r="E245" s="113" t="n"/>
+      <c r="F245" s="113" t="n"/>
+      <c r="G245" s="113" t="n"/>
+      <c r="H245" s="113" t="n"/>
+      <c r="I245" s="113" t="n"/>
+      <c r="J245" s="113" t="n"/>
+      <c r="K245" s="113" t="n"/>
+      <c r="L245" s="113" t="n"/>
+      <c r="M245" s="113" t="n"/>
+      <c r="N245" s="113" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="113" t="n"/>
+      <c r="B246" s="113" t="n"/>
+      <c r="C246" s="113" t="n"/>
+      <c r="D246" s="113" t="n"/>
+      <c r="E246" s="113" t="n"/>
+      <c r="F246" s="113" t="n"/>
+      <c r="G246" s="113" t="n"/>
+      <c r="H246" s="113" t="n"/>
+      <c r="I246" s="113" t="n"/>
+      <c r="J246" s="113" t="n"/>
+      <c r="K246" s="113" t="n"/>
+      <c r="L246" s="113" t="n"/>
+      <c r="M246" s="113" t="n"/>
+      <c r="N246" s="113" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="113" t="n"/>
+      <c r="B247" s="113" t="n"/>
+      <c r="C247" s="113" t="n"/>
+      <c r="D247" s="113" t="n"/>
+      <c r="E247" s="113" t="n"/>
+      <c r="F247" s="113" t="n"/>
+      <c r="G247" s="113" t="n"/>
+      <c r="H247" s="113" t="n"/>
+      <c r="I247" s="113" t="n"/>
+      <c r="J247" s="113" t="n"/>
+      <c r="K247" s="113" t="n"/>
+      <c r="L247" s="113" t="n"/>
+      <c r="M247" s="113" t="n"/>
+      <c r="N247" s="113" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="113" t="n"/>
+      <c r="B248" s="113" t="n"/>
+      <c r="C248" s="113" t="n"/>
+      <c r="D248" s="113" t="n"/>
+      <c r="E248" s="113" t="n"/>
+      <c r="F248" s="113" t="n"/>
+      <c r="G248" s="113" t="n"/>
+      <c r="H248" s="113" t="n"/>
+      <c r="I248" s="113" t="n"/>
+      <c r="J248" s="113" t="n"/>
+      <c r="K248" s="113" t="n"/>
+      <c r="L248" s="113" t="n"/>
+      <c r="M248" s="113" t="n"/>
+      <c r="N248" s="113" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="113" t="n"/>
+      <c r="B249" s="113" t="n"/>
+      <c r="C249" s="113" t="n"/>
+      <c r="D249" s="113" t="n"/>
+      <c r="E249" s="113" t="n"/>
+      <c r="F249" s="113" t="n"/>
+      <c r="G249" s="113" t="n"/>
+      <c r="H249" s="113" t="n"/>
+      <c r="I249" s="113" t="n"/>
+      <c r="J249" s="113" t="n"/>
+      <c r="K249" s="113" t="n"/>
+      <c r="L249" s="113" t="n"/>
+      <c r="M249" s="113" t="n"/>
+      <c r="N249" s="113" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="B129:C129"/>
+  <mergeCells count="86">
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="B134:C134"/>
     <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="D42:J42"/>
     <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B140:C140"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B176:C176"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="K42:M42"/>
     <mergeCell ref="D26:J26"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B88:B90"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="B107:C107"/>
     <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="D34:J34"/>
-    <mergeCell ref="B85:B87"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B69:C69"/>
-    <mergeCell ref="K4:M4"/>
     <mergeCell ref="D21:J21"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="K11:M11"/>
     <mergeCell ref="K34:M34"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B167:B169"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B157:B159"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B183:B185"/>
+    <mergeCell ref="B177:B179"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="B164:B166"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="D34:J34"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B180:B182"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B170:B172"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B54:B55"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B151:B153"/>
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="B139:C139"/>
     <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B76:C76"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D16:J16"/>
     <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B163:C163"/>
     <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B125:B126"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>

--- a/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
+++ b/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①농산물raw" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유기농업체" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②유기농raw" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="※ 이상치 및 규정검토" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'농산물업체'!$A$2:$J$287</definedName>
@@ -32,7 +33,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="###\-##\-#####"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="31">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -215,8 +216,49 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -315,8 +357,38 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4E6"/>
+        <bgColor rgb="00FFE4E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF08A"/>
+        <bgColor rgb="00FEF08A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -551,6 +623,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -586,7 +672,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1012,6 +1098,59 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="22" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -8448,91 +8587,91 @@
   </sheetData>
   <mergeCells count="86">
     <mergeCell ref="D4:J4"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B167:B169"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B177:B179"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B164:B166"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B180:B182"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B144:C144"/>
     <mergeCell ref="C42:C43"/>
     <mergeCell ref="B134:C134"/>
     <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B108:B110"/>
     <mergeCell ref="B122:C122"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B42:B43"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="B176:C176"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="B61:C61"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="B107:C107"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B69:C69"/>
     <mergeCell ref="D21:J21"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="B54:B55"/>
     <mergeCell ref="B101:B103"/>
     <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B167:B169"/>
-    <mergeCell ref="B64:C64"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B157:B159"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B56:B57"/>
     <mergeCell ref="K21:M21"/>
     <mergeCell ref="D16:J16"/>
-    <mergeCell ref="B98:B100"/>
     <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B63:C63"/>
     <mergeCell ref="K26:M26"/>
     <mergeCell ref="B125:B126"/>
-    <mergeCell ref="B26:B27"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B88:B90"/>
     <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B129:C129"/>
     <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="C4:C5"/>
     <mergeCell ref="B150:C150"/>
     <mergeCell ref="B183:B185"/>
-    <mergeCell ref="B177:B179"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B131:C131"/>
     <mergeCell ref="D42:J42"/>
-    <mergeCell ref="B164:B166"/>
-    <mergeCell ref="B140:C140"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B130:C130"/>
     <mergeCell ref="K42:M42"/>
     <mergeCell ref="B95:B97"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="D34:J34"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B180:B182"/>
-    <mergeCell ref="K4:M4"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="B170:B172"/>
-    <mergeCell ref="B111:B113"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B151:B153"/>
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="C34:C35"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B16:B17"/>
     <mergeCell ref="B163:C163"/>
-    <mergeCell ref="B144:C144"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
@@ -82237,4 +82376,2515 @@
   <pageSetup orientation="portrait" paperSize="9" scale="36"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:K72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="21" min="1" max="1"/>
+    <col width="14" customWidth="1" style="21" min="2" max="2"/>
+    <col width="16" customWidth="1" style="21" min="3" max="3"/>
+    <col width="26" customWidth="1" style="21" min="4" max="4"/>
+    <col width="16" customWidth="1" style="21" min="5" max="5"/>
+    <col width="45" customWidth="1" style="21" min="6" max="6"/>
+    <col width="15" customWidth="1" style="21" min="7" max="7"/>
+    <col width="15" customWidth="1" style="21" min="8" max="8"/>
+    <col width="16" customWidth="1" style="21" min="9" max="9"/>
+    <col width="16" customWidth="1" style="21" min="10" max="10"/>
+    <col width="16" customWidth="1" style="21" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="156" t="inlineStr">
+        <is>
+          <t>2026 aT 온라인 판로지원 사업 - 실적 이상치 및 규정 준수 검토 리포트</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="157" t="inlineStr">
+        <is>
+          <t>1. 사업 규정 준수 여부 전수 검토 결과 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="158" t="inlineStr">
+        <is>
+          <t>검토 규정 항목</t>
+        </is>
+      </c>
+      <c r="C5" s="158" t="inlineStr">
+        <is>
+          <t>사업 운영 기준</t>
+        </is>
+      </c>
+      <c r="D5" s="158" t="inlineStr">
+        <is>
+          <t>전수 검토 결과</t>
+        </is>
+      </c>
+      <c r="E5" s="158" t="inlineStr">
+        <is>
+          <t>준수 여부</t>
+        </is>
+      </c>
+      <c r="F5" s="158" t="inlineStr">
+        <is>
+          <t>세부 검토 내역</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="159" t="inlineStr">
+        <is>
+          <t>업체당 쿠폰 한도</t>
+        </is>
+      </c>
+      <c r="C6" s="160" t="inlineStr">
+        <is>
+          <t>업체당 최대 8,000,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="161" t="inlineStr">
+        <is>
+          <t>초과 업체 0개 (최대 소진액 6,140,240원 / 76.8%)</t>
+        </is>
+      </c>
+      <c r="E6" s="162" t="inlineStr">
+        <is>
+          <t>정상 준수</t>
+        </is>
+      </c>
+      <c r="F6" s="163" t="inlineStr">
+        <is>
+          <t>농부들(76.8%), 자연푸드(73.1%), 팜앤유(71.6%) 등 전 업체 한도 내 안전 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="159" t="inlineStr">
+        <is>
+          <t>쿠폰 할인율 상한</t>
+        </is>
+      </c>
+      <c r="C7" s="160" t="inlineStr">
+        <is>
+          <t>매출액 대비 최대 20.0%</t>
+        </is>
+      </c>
+      <c r="D7" s="161" t="inlineStr">
+        <is>
+          <t>초과 건수 0건 (최대 할인율 정확히 20.00%)</t>
+        </is>
+      </c>
+      <c r="E7" s="162" t="inlineStr">
+        <is>
+          <t>정상 준수</t>
+        </is>
+      </c>
+      <c r="F7" s="163" t="inlineStr">
+        <is>
+          <t>1,651개 로우데이터 행 전수 검사 결과 20% 초과 할인 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="159" t="inlineStr">
+        <is>
+          <t>건당 쿠폰 한도</t>
+        </is>
+      </c>
+      <c r="C8" s="160" t="inlineStr">
+        <is>
+          <t>건당(개당) 최대 10,000원</t>
+        </is>
+      </c>
+      <c r="D8" s="161" t="inlineStr">
+        <is>
+          <t>초과 건수 0건 (건당 최대 쿠폰액 정확히 10,000원)</t>
+        </is>
+      </c>
+      <c r="E8" s="162" t="inlineStr">
+        <is>
+          <t>정상 준수</t>
+        </is>
+      </c>
+      <c r="F8" s="163" t="inlineStr">
+        <is>
+          <t>롯데ON 등 10,000원 정액 적용 건 존재하나 초과 건 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="157" t="inlineStr">
+        <is>
+          <t>2. 누적 실적 역전(감소) 이상치 내역 (총 4건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="158" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C12" s="158" t="inlineStr">
+        <is>
+          <t>유통사</t>
+        </is>
+      </c>
+      <c r="D12" s="158" t="inlineStr">
+        <is>
+          <t>사업자명</t>
+        </is>
+      </c>
+      <c r="E12" s="158" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="F12" s="158" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="G12" s="158" t="inlineStr">
+        <is>
+          <t>7월 실적</t>
+        </is>
+      </c>
+      <c r="H12" s="158" t="inlineStr">
+        <is>
+          <t>8월 누적실적</t>
+        </is>
+      </c>
+      <c r="I12" s="158" t="inlineStr">
+        <is>
+          <t>증감(8월순수)</t>
+        </is>
+      </c>
+      <c r="J12" s="158" t="inlineStr">
+        <is>
+          <t>이상 원인 분석 및 특이사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="164" t="inlineStr">
+        <is>
+          <t>업체 쿠폰 역전</t>
+        </is>
+      </c>
+      <c r="C13" s="164" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="D13" s="165" t="inlineStr">
+        <is>
+          <t>농업회사법인 랑이네세상 주식회사</t>
+        </is>
+      </c>
+      <c r="E13" s="164" t="inlineStr">
+        <is>
+          <t>488-88-03205</t>
+        </is>
+      </c>
+      <c r="F13" s="165" t="inlineStr">
+        <is>
+          <t>[업체 전체 쿠폰]</t>
+        </is>
+      </c>
+      <c r="G13" s="166" t="inlineStr">
+        <is>
+          <t>4,955,760원</t>
+        </is>
+      </c>
+      <c r="H13" s="166" t="inlineStr">
+        <is>
+          <t>4,947,920원</t>
+        </is>
+      </c>
+      <c r="I13" s="167" t="inlineStr">
+        <is>
+          <t>-7,840원</t>
+        </is>
+      </c>
+      <c r="J13" s="165" t="inlineStr">
+        <is>
+          <t>매출/건수는 증가했으나 쿠폰 사용액이 7월 대비 누적에서 7,840원 감소 (주문취소/환불 반영 의심)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="164" t="inlineStr">
+        <is>
+          <t>상품 매출 역전</t>
+        </is>
+      </c>
+      <c r="C14" s="164" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="D14" s="165" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)더봄</t>
+        </is>
+      </c>
+      <c r="E14" s="164" t="inlineStr">
+        <is>
+          <t>138-81-67809</t>
+        </is>
+      </c>
+      <c r="F14" s="165" t="inlineStr">
+        <is>
+          <t>생화용 백합 꽃 백합생화 1000ml x 5</t>
+        </is>
+      </c>
+      <c r="G14" s="166" t="inlineStr">
+        <is>
+          <t>60,000원 (1건)</t>
+        </is>
+      </c>
+      <c r="H14" s="166" t="inlineStr">
+        <is>
+          <t>0원 (0건)</t>
+        </is>
+      </c>
+      <c r="I14" s="167" t="inlineStr">
+        <is>
+          <t>-60,000원 (-1건)</t>
+        </is>
+      </c>
+      <c r="J14" s="165" t="inlineStr">
+        <is>
+          <t>7월에 1건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="164" t="inlineStr">
+        <is>
+          <t>상품 매출 역전</t>
+        </is>
+      </c>
+      <c r="C15" s="164" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="D15" s="165" t="inlineStr">
+        <is>
+          <t>더모닝</t>
+        </is>
+      </c>
+      <c r="E15" s="164" t="inlineStr">
+        <is>
+          <t>655-09-02685</t>
+        </is>
+      </c>
+      <c r="F15" s="165" t="inlineStr">
+        <is>
+          <t>더모닝 닭 볶음탕 닭볶음탕 90g 1인분 x 5팩 캠핑 밀키트</t>
+        </is>
+      </c>
+      <c r="G15" s="166" t="inlineStr">
+        <is>
+          <t>240,000원 (12건)</t>
+        </is>
+      </c>
+      <c r="H15" s="166" t="inlineStr">
+        <is>
+          <t>0원 (0건)</t>
+        </is>
+      </c>
+      <c r="I15" s="167" t="inlineStr">
+        <is>
+          <t>-240,000원 (-12건)</t>
+        </is>
+      </c>
+      <c r="J15" s="165" t="inlineStr">
+        <is>
+          <t>7월에 12건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="164" t="inlineStr">
+        <is>
+          <t>상품 매출 역전</t>
+        </is>
+      </c>
+      <c r="C16" s="164" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="D16" s="165" t="inlineStr">
+        <is>
+          <t>더모닝</t>
+        </is>
+      </c>
+      <c r="E16" s="164" t="inlineStr">
+        <is>
+          <t>655-09-02685</t>
+        </is>
+      </c>
+      <c r="F16" s="165" t="inlineStr">
+        <is>
+          <t>더모닝 닭 볶음탕 닭볶음탕 400g 4인분 캠핑 밀키트</t>
+        </is>
+      </c>
+      <c r="G16" s="166" t="inlineStr">
+        <is>
+          <t>54,000원 (3건)</t>
+        </is>
+      </c>
+      <c r="H16" s="166" t="inlineStr">
+        <is>
+          <t>0원 (0건)</t>
+        </is>
+      </c>
+      <c r="I16" s="167" t="inlineStr">
+        <is>
+          <t>-54,000원 (-3건)</t>
+        </is>
+      </c>
+      <c r="J16" s="165" t="inlineStr">
+        <is>
+          <t>7월에 3건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="157" t="inlineStr">
+        <is>
+          <t>3. 업체별 쿠폰 한도(800만원) 소진율 상위 Top 10 업체 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="158" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C20" s="158" t="inlineStr">
+        <is>
+          <t>사업자명</t>
+        </is>
+      </c>
+      <c r="D20" s="158" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="E20" s="158" t="inlineStr">
+        <is>
+          <t>참여 유통사</t>
+        </is>
+      </c>
+      <c r="F20" s="158" t="inlineStr">
+        <is>
+          <t>누적 매출액</t>
+        </is>
+      </c>
+      <c r="G20" s="158" t="inlineStr">
+        <is>
+          <t>누적 쿠폰사용액</t>
+        </is>
+      </c>
+      <c r="H20" s="158" t="inlineStr">
+        <is>
+          <t>한도(800만원) 소진율</t>
+        </is>
+      </c>
+      <c r="I20" s="158" t="inlineStr">
+        <is>
+          <t>잔여 한도액</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="169" t="inlineStr">
+        <is>
+          <t>농부들</t>
+        </is>
+      </c>
+      <c r="D21" s="168" t="inlineStr">
+        <is>
+          <t>579-90-00021</t>
+        </is>
+      </c>
+      <c r="E21" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F21" s="170" t="n">
+        <v>53342360</v>
+      </c>
+      <c r="G21" s="171" t="n">
+        <v>6140240</v>
+      </c>
+      <c r="H21" s="172" t="inlineStr">
+        <is>
+          <t>76.8%</t>
+        </is>
+      </c>
+      <c r="I21" s="170" t="n">
+        <v>1859760</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="168" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)자연푸드</t>
+        </is>
+      </c>
+      <c r="D22" s="168" t="inlineStr">
+        <is>
+          <t>412-81-50546</t>
+        </is>
+      </c>
+      <c r="E22" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F22" s="170" t="n">
+        <v>55214000</v>
+      </c>
+      <c r="G22" s="171" t="n">
+        <v>5847700</v>
+      </c>
+      <c r="H22" s="172" t="inlineStr">
+        <is>
+          <t>73.1%</t>
+        </is>
+      </c>
+      <c r="I22" s="170" t="n">
+        <v>2152300</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="169" t="inlineStr">
+        <is>
+          <t>팜앤유</t>
+        </is>
+      </c>
+      <c r="D23" s="168" t="inlineStr">
+        <is>
+          <t>477-93-01384</t>
+        </is>
+      </c>
+      <c r="E23" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="F23" s="170" t="n">
+        <v>41243100</v>
+      </c>
+      <c r="G23" s="171" t="n">
+        <v>5728100</v>
+      </c>
+      <c r="H23" s="172" t="inlineStr">
+        <is>
+          <t>71.6%</t>
+        </is>
+      </c>
+      <c r="I23" s="170" t="n">
+        <v>2271900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="169" t="inlineStr">
+        <is>
+          <t>(주)다채몰</t>
+        </is>
+      </c>
+      <c r="D24" s="168" t="inlineStr">
+        <is>
+          <t>114-86-65039</t>
+        </is>
+      </c>
+      <c r="E24" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F24" s="170" t="n">
+        <v>39871200</v>
+      </c>
+      <c r="G24" s="171" t="n">
+        <v>5268240</v>
+      </c>
+      <c r="H24" s="159" t="inlineStr">
+        <is>
+          <t>65.9%</t>
+        </is>
+      </c>
+      <c r="I24" s="170" t="n">
+        <v>2731760</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="169" t="inlineStr">
+        <is>
+          <t>해남농협</t>
+        </is>
+      </c>
+      <c r="D25" s="168" t="inlineStr">
+        <is>
+          <t>323-88-00158</t>
+        </is>
+      </c>
+      <c r="E25" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="F25" s="170" t="n">
+        <v>45120000</v>
+      </c>
+      <c r="G25" s="171" t="n">
+        <v>5136630</v>
+      </c>
+      <c r="H25" s="159" t="inlineStr">
+        <is>
+          <t>64.2%</t>
+        </is>
+      </c>
+      <c r="I25" s="170" t="n">
+        <v>2863370</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인 주식회사 드림마이스터</t>
+        </is>
+      </c>
+      <c r="D26" s="168" t="inlineStr">
+        <is>
+          <t>485-88-00795</t>
+        </is>
+      </c>
+      <c r="E26" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F26" s="170" t="n">
+        <v>36240000</v>
+      </c>
+      <c r="G26" s="171" t="n">
+        <v>5105280</v>
+      </c>
+      <c r="H26" s="159" t="inlineStr">
+        <is>
+          <t>63.8%</t>
+        </is>
+      </c>
+      <c r="I26" s="170" t="n">
+        <v>2894720</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인 철원이곡 주식회사</t>
+        </is>
+      </c>
+      <c r="D27" s="168" t="inlineStr">
+        <is>
+          <t>127-81-93991</t>
+        </is>
+      </c>
+      <c r="E27" s="168" t="inlineStr">
+        <is>
+          <t>농가살리기</t>
+        </is>
+      </c>
+      <c r="F27" s="170" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="G27" s="171" t="n">
+        <v>5097728</v>
+      </c>
+      <c r="H27" s="159" t="inlineStr">
+        <is>
+          <t>63.7%</t>
+        </is>
+      </c>
+      <c r="I27" s="170" t="n">
+        <v>2902272</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="168" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="169" t="inlineStr">
+        <is>
+          <t>해주농협통합</t>
+        </is>
+      </c>
+      <c r="D28" s="168" t="inlineStr">
+        <is>
+          <t>126-82-11620</t>
+        </is>
+      </c>
+      <c r="E28" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F28" s="170" t="n">
+        <v>48900000</v>
+      </c>
+      <c r="G28" s="171" t="n">
+        <v>5085890</v>
+      </c>
+      <c r="H28" s="159" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="I28" s="170" t="n">
+        <v>2914110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="168" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="169" t="inlineStr">
+        <is>
+          <t>두원식품(주)</t>
+        </is>
+      </c>
+      <c r="D29" s="168" t="inlineStr">
+        <is>
+          <t>606-81-52718</t>
+        </is>
+      </c>
+      <c r="E29" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="F29" s="170" t="n">
+        <v>55053800</v>
+      </c>
+      <c r="G29" s="171" t="n">
+        <v>5062400</v>
+      </c>
+      <c r="H29" s="159" t="inlineStr">
+        <is>
+          <t>63.3%</t>
+        </is>
+      </c>
+      <c r="I29" s="170" t="n">
+        <v>2937600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="168" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="169" t="inlineStr">
+        <is>
+          <t>청양농협</t>
+        </is>
+      </c>
+      <c r="D30" s="168" t="inlineStr">
+        <is>
+          <t>499-51-00634</t>
+        </is>
+      </c>
+      <c r="E30" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="F30" s="170" t="n">
+        <v>38100000</v>
+      </c>
+      <c r="G30" s="171" t="n">
+        <v>5049440</v>
+      </c>
+      <c r="H30" s="159" t="inlineStr">
+        <is>
+          <t>63.1%</t>
+        </is>
+      </c>
+      <c r="I30" s="170" t="n">
+        <v>2950560</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="157" t="inlineStr">
+        <is>
+          <t>4. 농가·유통사 품목분류 자의적 변경 이상건 전수 내역 (총 38건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="158" t="inlineStr">
+        <is>
+          <t>유통사</t>
+        </is>
+      </c>
+      <c r="D34" s="158" t="inlineStr">
+        <is>
+          <t>사업자명</t>
+        </is>
+      </c>
+      <c r="E34" s="158" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="F34" s="158" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="G34" s="158" t="inlineStr">
+        <is>
+          <t>7월 분류</t>
+        </is>
+      </c>
+      <c r="H34" s="158" t="inlineStr">
+        <is>
+          <t>8월 변경분류</t>
+        </is>
+      </c>
+      <c r="I34" s="158" t="inlineStr">
+        <is>
+          <t>7월 매출액</t>
+        </is>
+      </c>
+      <c r="J34" s="158" t="inlineStr">
+        <is>
+          <t>8월 누적매출액</t>
+        </is>
+      </c>
+      <c r="K34" s="158" t="inlineStr">
+        <is>
+          <t>8월 순수매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="D35" s="169" t="inlineStr">
+        <is>
+          <t>주식회사 태범프레시</t>
+        </is>
+      </c>
+      <c r="E35" s="168" t="inlineStr">
+        <is>
+          <t>832-86-02035</t>
+        </is>
+      </c>
+      <c r="F35" s="169" t="inlineStr">
+        <is>
+          <t>[홍익상회] 춘천닭갈비 500g x 3팩 국내산닭고기 양념 순살</t>
+        </is>
+      </c>
+      <c r="G35" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H35" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I35" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="168" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="D36" s="169" t="inlineStr">
+        <is>
+          <t>주식회사 태범프레시</t>
+        </is>
+      </c>
+      <c r="E36" s="168" t="inlineStr">
+        <is>
+          <t>832-86-02035</t>
+        </is>
+      </c>
+      <c r="F36" s="169" t="inlineStr">
+        <is>
+          <t>[홍익상회] 춘천 홍익닭갈비 500g x 3팩 국내산 닭고기 양념 순살</t>
+        </is>
+      </c>
+      <c r="G36" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H36" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I36" s="170" t="n">
+        <v>2552440</v>
+      </c>
+      <c r="J36" s="170" t="n">
+        <v>2552440</v>
+      </c>
+      <c r="K36" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="D37" s="169" t="inlineStr">
+        <is>
+          <t>신선식품</t>
+        </is>
+      </c>
+      <c r="E37" s="168" t="inlineStr">
+        <is>
+          <t>131-35-96215</t>
+        </is>
+      </c>
+      <c r="F37" s="169" t="inlineStr">
+        <is>
+          <t>[온누리7%혜택]고소한 국산 볶은참깨 200g</t>
+        </is>
+      </c>
+      <c r="G37" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H37" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I37" s="170" t="n">
+        <v>25600</v>
+      </c>
+      <c r="J37" s="170" t="n">
+        <v>204800</v>
+      </c>
+      <c r="K37" s="174" t="n">
+        <v>179200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D38" s="169" t="inlineStr">
+        <is>
+          <t>두원식품(주)</t>
+        </is>
+      </c>
+      <c r="E38" s="168" t="inlineStr">
+        <is>
+          <t>606-81-52718</t>
+        </is>
+      </c>
+      <c r="F38" s="169" t="inlineStr">
+        <is>
+          <t>(신선집중) 국내산 한돈 프리미엄 대패 삼겹살 1.2kg</t>
+        </is>
+      </c>
+      <c r="G38" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H38" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I38" s="170" t="n">
+        <v>51796200</v>
+      </c>
+      <c r="J38" s="170" t="n">
+        <v>55053800</v>
+      </c>
+      <c r="K38" s="174" t="n">
+        <v>3257600</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D39" s="169" t="inlineStr">
+        <is>
+          <t>다모아영농조합법인</t>
+        </is>
+      </c>
+      <c r="E39" s="168" t="inlineStr">
+        <is>
+          <t>613-81-60803</t>
+        </is>
+      </c>
+      <c r="F39" s="169" t="inlineStr">
+        <is>
+          <t>농협 공동선별 햇 남해 통마늘 3kg(상) 실중량 지리적표시품</t>
+        </is>
+      </c>
+      <c r="G39" s="159" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="H39" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I39" s="170" t="n">
+        <v>73800</v>
+      </c>
+      <c r="J39" s="170" t="n">
+        <v>701100</v>
+      </c>
+      <c r="K39" s="174" t="n">
+        <v>627300</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D40" s="169" t="inlineStr">
+        <is>
+          <t>청정태안식품</t>
+        </is>
+      </c>
+      <c r="E40" s="168" t="inlineStr">
+        <is>
+          <t>316-01-24597</t>
+        </is>
+      </c>
+      <c r="F40" s="169" t="inlineStr">
+        <is>
+          <t>김명월 검정콩 청국장가루 1kg(500g2통)</t>
+        </is>
+      </c>
+      <c r="G40" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H40" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I40" s="170" t="n">
+        <v>74000</v>
+      </c>
+      <c r="J40" s="170" t="n">
+        <v>222000</v>
+      </c>
+      <c r="K40" s="174" t="n">
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D41" s="169" t="inlineStr">
+        <is>
+          <t>청정태안식품</t>
+        </is>
+      </c>
+      <c r="E41" s="168" t="inlineStr">
+        <is>
+          <t>316-01-24597</t>
+        </is>
+      </c>
+      <c r="F41" s="169" t="inlineStr">
+        <is>
+          <t>김명월 검정콩 청국장가루 1kg(500g2통)</t>
+        </is>
+      </c>
+      <c r="G41" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H41" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I41" s="170" t="n">
+        <v>74000</v>
+      </c>
+      <c r="J41" s="170" t="n">
+        <v>259000</v>
+      </c>
+      <c r="K41" s="174" t="n">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="168" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D42" s="169" t="inlineStr">
+        <is>
+          <t>형지표고버섯</t>
+        </is>
+      </c>
+      <c r="E42" s="168" t="inlineStr">
+        <is>
+          <t>290-94-00335</t>
+        </is>
+      </c>
+      <c r="F42" s="169" t="inlineStr">
+        <is>
+          <t>형지표고버섯 흑화고 상황버섯 혼합2호 표고 버섯 선물세트</t>
+        </is>
+      </c>
+      <c r="G42" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H42" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I42" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="168" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D43" s="169" t="inlineStr">
+        <is>
+          <t>농부플러스</t>
+        </is>
+      </c>
+      <c r="E43" s="168" t="inlineStr">
+        <is>
+          <t>571-81-00383</t>
+        </is>
+      </c>
+      <c r="F43" s="169" t="inlineStr">
+        <is>
+          <t>국산 볶음참깨 햇 참깨 볶은참깨 토종 통깨 200g</t>
+        </is>
+      </c>
+      <c r="G43" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H43" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I43" s="170" t="n">
+        <v>360800</v>
+      </c>
+      <c r="J43" s="170" t="n">
+        <v>1098800</v>
+      </c>
+      <c r="K43" s="174" t="n">
+        <v>738000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="168" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D44" s="169" t="inlineStr">
+        <is>
+          <t>농부플러스</t>
+        </is>
+      </c>
+      <c r="E44" s="168" t="inlineStr">
+        <is>
+          <t>571-81-00383</t>
+        </is>
+      </c>
+      <c r="F44" s="169" t="inlineStr">
+        <is>
+          <t>국산 볶음참깨 햇 참깨 볶은참깨 토종 통깨 150g</t>
+        </is>
+      </c>
+      <c r="G44" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H44" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I44" s="170" t="n">
+        <v>13900</v>
+      </c>
+      <c r="J44" s="170" t="n">
+        <v>42700</v>
+      </c>
+      <c r="K44" s="174" t="n">
+        <v>28800</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="168" t="n">
+        <v>11</v>
+      </c>
+      <c r="C45" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D45" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간</t>
+        </is>
+      </c>
+      <c r="E45" s="168" t="inlineStr">
+        <is>
+          <t>181-02-01980</t>
+        </is>
+      </c>
+      <c r="F45" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간 국내산 볶은 귀리 / 아침식사대용 간식</t>
+        </is>
+      </c>
+      <c r="G45" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H45" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I45" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="168" t="n">
+        <v>12</v>
+      </c>
+      <c r="C46" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D46" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간</t>
+        </is>
+      </c>
+      <c r="E46" s="168" t="inlineStr">
+        <is>
+          <t>181-02-01980</t>
+        </is>
+      </c>
+      <c r="F46" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간 국내산 쑥미숫가루 / 선식 식사대용 간식 500g</t>
+        </is>
+      </c>
+      <c r="G46" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H46" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I46" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="170" t="n">
+        <v>23800</v>
+      </c>
+      <c r="K46" s="174" t="n">
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="168" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D47" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)가남농원</t>
+        </is>
+      </c>
+      <c r="E47" s="168" t="inlineStr">
+        <is>
+          <t>416-81-59229</t>
+        </is>
+      </c>
+      <c r="F47" s="169" t="inlineStr">
+        <is>
+          <t>김승희매실가 신지식 농업인이 만든 매실절임 1kg</t>
+        </is>
+      </c>
+      <c r="G47" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H47" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I47" s="170" t="n">
+        <v>66000</v>
+      </c>
+      <c r="J47" s="170" t="n">
+        <v>165000</v>
+      </c>
+      <c r="K47" s="174" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="168" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D48" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)가남농원</t>
+        </is>
+      </c>
+      <c r="E48" s="168" t="inlineStr">
+        <is>
+          <t>416-81-59229</t>
+        </is>
+      </c>
+      <c r="F48" s="169" t="inlineStr">
+        <is>
+          <t>천기누설 매실 장인이만든 매실고 (농축액) 150g</t>
+        </is>
+      </c>
+      <c r="G48" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H48" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I48" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="168" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D49" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)가남농원</t>
+        </is>
+      </c>
+      <c r="E49" s="168" t="inlineStr">
+        <is>
+          <t>416-81-59229</t>
+        </is>
+      </c>
+      <c r="F49" s="169" t="inlineStr">
+        <is>
+          <t>천기누설 매실 장인이만든 매실고 (농축액) 150g</t>
+        </is>
+      </c>
+      <c r="G49" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H49" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I49" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="170" t="n">
+        <v>43000</v>
+      </c>
+      <c r="K49" s="174" t="n">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="168" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D50" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인 팜팜(주)</t>
+        </is>
+      </c>
+      <c r="E50" s="168" t="inlineStr">
+        <is>
+          <t>177-81-00798</t>
+        </is>
+      </c>
+      <c r="F50" s="169" t="inlineStr">
+        <is>
+          <t>(품질보증) 산지직송 정품과 완숙토마토 5KG 당일수확 유럽종</t>
+        </is>
+      </c>
+      <c r="G50" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H50" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I50" s="170" t="n">
+        <v>694600</v>
+      </c>
+      <c r="J50" s="170" t="n">
+        <v>5967100</v>
+      </c>
+      <c r="K50" s="174" t="n">
+        <v>5272500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="168" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D51" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인주식회사 늘해랑</t>
+        </is>
+      </c>
+      <c r="E51" s="168" t="inlineStr">
+        <is>
+          <t>756-87-00841</t>
+        </is>
+      </c>
+      <c r="F51" s="169" t="inlineStr">
+        <is>
+          <t>조은해남 고구마 못난이 10kg (꿀호박 랜덤발송)</t>
+        </is>
+      </c>
+      <c r="G51" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H51" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I51" s="170" t="n">
+        <v>371800</v>
+      </c>
+      <c r="J51" s="170" t="n">
+        <v>2827100</v>
+      </c>
+      <c r="K51" s="174" t="n">
+        <v>2455300</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="168" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D52" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E52" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F52" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G52" s="159" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="H52" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I52" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="168" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D53" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E53" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F53" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G53" s="159" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="H53" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I53" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="170" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K53" s="174" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="168" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D54" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E54" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F54" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산100% 도토리묵 묵사발 세트</t>
+        </is>
+      </c>
+      <c r="G54" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H54" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I54" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="168" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D55" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E55" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F55" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 명인 국산 콩물 우묵채 (2인분)</t>
+        </is>
+      </c>
+      <c r="G55" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H55" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I55" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="168" t="n">
+        <v>22</v>
+      </c>
+      <c r="C56" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D56" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E56" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F56" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G56" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H56" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I56" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="168" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D57" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E57" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F57" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G57" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H57" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I57" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="K57" s="174" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="168" t="n">
+        <v>24</v>
+      </c>
+      <c r="C58" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D58" s="169" t="inlineStr">
+        <is>
+          <t>그린몬스터즈</t>
+        </is>
+      </c>
+      <c r="E58" s="168" t="inlineStr">
+        <is>
+          <t>883-95-01472</t>
+        </is>
+      </c>
+      <c r="F58" s="169" t="inlineStr">
+        <is>
+          <t>당일수확발송 그린몬스터즈 프리미엄 미니오이 1.5kg 농장직거래 여름작기 첫수확 특가할인행사</t>
+        </is>
+      </c>
+      <c r="G58" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H58" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I58" s="170" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J58" s="170" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K58" s="174" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="168" t="n">
+        <v>25</v>
+      </c>
+      <c r="C59" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D59" s="169" t="inlineStr">
+        <is>
+          <t>어이딸부각</t>
+        </is>
+      </c>
+      <c r="E59" s="168" t="inlineStr">
+        <is>
+          <t>142-33-00898</t>
+        </is>
+      </c>
+      <c r="F59" s="169" t="inlineStr">
+        <is>
+          <t>고추크런치 70g 고추부각 튀각 찹쌀 수제 비건</t>
+        </is>
+      </c>
+      <c r="G59" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H59" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I59" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="168" t="n">
+        <v>26</v>
+      </c>
+      <c r="C60" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D60" s="169" t="inlineStr">
+        <is>
+          <t>어이딸부각</t>
+        </is>
+      </c>
+      <c r="E60" s="168" t="inlineStr">
+        <is>
+          <t>142-33-00898</t>
+        </is>
+      </c>
+      <c r="F60" s="169" t="inlineStr">
+        <is>
+          <t>어이딸 김부각 선물세트 소 5개입 찹쌀 수제 비건 글루텐프리 저당</t>
+        </is>
+      </c>
+      <c r="G60" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H60" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I60" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="170" t="n">
+        <v>690000</v>
+      </c>
+      <c r="K60" s="174" t="n">
+        <v>690000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="168" t="n">
+        <v>27</v>
+      </c>
+      <c r="C61" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D61" s="169" t="inlineStr">
+        <is>
+          <t>어이딸부각</t>
+        </is>
+      </c>
+      <c r="E61" s="168" t="inlineStr">
+        <is>
+          <t>142-33-00898</t>
+        </is>
+      </c>
+      <c r="F61" s="169" t="inlineStr">
+        <is>
+          <t>어이딸 김부각 선물세트 중 8개입 찹쌀 수제 비건 글루텐프리 저당</t>
+        </is>
+      </c>
+      <c r="G61" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H61" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I61" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="168" t="n">
+        <v>28</v>
+      </c>
+      <c r="C62" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D62" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E62" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F62" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G62" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H62" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I62" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="168" t="n">
+        <v>29</v>
+      </c>
+      <c r="C63" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D63" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E63" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F63" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G63" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H63" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I63" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="170" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K63" s="174" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="168" t="n">
+        <v>30</v>
+      </c>
+      <c r="C64" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D64" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E64" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F64" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G64" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H64" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I64" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J64" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="174" t="n">
+        <v>-240000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="168" t="n">
+        <v>31</v>
+      </c>
+      <c r="C65" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D65" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E65" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F65" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G65" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H65" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I65" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J65" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="K65" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="168" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D66" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E66" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F66" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 400g 4인분 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G66" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H66" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I66" s="170" t="n">
+        <v>54000</v>
+      </c>
+      <c r="J66" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="174" t="n">
+        <v>-54000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="168" t="n">
+        <v>33</v>
+      </c>
+      <c r="C67" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D67" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E67" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F67" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 400g 4인분 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G67" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H67" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I67" s="170" t="n">
+        <v>54000</v>
+      </c>
+      <c r="J67" s="170" t="n">
+        <v>54000</v>
+      </c>
+      <c r="K67" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="168" t="n">
+        <v>34</v>
+      </c>
+      <c r="C68" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D68" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E68" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F68" s="169" t="inlineStr">
+        <is>
+          <t>한돈 제육볶음 (650g X 1개)</t>
+        </is>
+      </c>
+      <c r="G68" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H68" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I68" s="170" t="n">
+        <v>20305100</v>
+      </c>
+      <c r="J68" s="170" t="n">
+        <v>46426900</v>
+      </c>
+      <c r="K68" s="174" t="n">
+        <v>26121800</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="168" t="n">
+        <v>35</v>
+      </c>
+      <c r="C69" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D69" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E69" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F69" s="169" t="inlineStr">
+        <is>
+          <t>한돈 칼집 양념구이 (650g X 1개)</t>
+        </is>
+      </c>
+      <c r="G69" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H69" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I69" s="170" t="n">
+        <v>16019900</v>
+      </c>
+      <c r="J69" s="170" t="n">
+        <v>30197000</v>
+      </c>
+      <c r="K69" s="174" t="n">
+        <v>14177100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="168" t="n">
+        <v>36</v>
+      </c>
+      <c r="C70" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D70" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E70" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F70" s="169" t="inlineStr">
+        <is>
+          <t>한돈 성북동식 돼지불백 (650g X 1개)</t>
+        </is>
+      </c>
+      <c r="G70" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H70" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I70" s="170" t="n">
+        <v>10928700</v>
+      </c>
+      <c r="J70" s="170" t="n">
+        <v>21744400</v>
+      </c>
+      <c r="K70" s="174" t="n">
+        <v>10815700</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="168" t="n">
+        <v>37</v>
+      </c>
+      <c r="C71" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D71" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E71" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F71" s="169" t="inlineStr">
+        <is>
+          <t>서울식 한우 불고기 밀키트 (800g X 1개)</t>
+        </is>
+      </c>
+      <c r="G71" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H71" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I71" s="170" t="n">
+        <v>6922200</v>
+      </c>
+      <c r="J71" s="170" t="n">
+        <v>15422600</v>
+      </c>
+      <c r="K71" s="174" t="n">
+        <v>8500400</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="168" t="n">
+        <v>38</v>
+      </c>
+      <c r="C72" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D72" s="169" t="inlineStr">
+        <is>
+          <t>해담는집</t>
+        </is>
+      </c>
+      <c r="E72" s="168" t="inlineStr">
+        <is>
+          <t>745-96-00315</t>
+        </is>
+      </c>
+      <c r="F72" s="169" t="inlineStr">
+        <is>
+          <t>해담는집 유기농 고춧가루 500g/200g(순한맛/보통맛/매운맛)</t>
+        </is>
+      </c>
+      <c r="G72" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H72" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I72" s="170" t="n">
+        <v>208400</v>
+      </c>
+      <c r="J72" s="170" t="n">
+        <v>434900</v>
+      </c>
+      <c r="K72" s="174" t="n">
+        <v>226500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
+++ b/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
@@ -7,20 +7,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="농산물업체" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①농산물raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유기농업체" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②유기농raw" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="※ 이상치 및 규정검토" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="※ 이상치 및 규정검토" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="농산물업체" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①농산물raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유기농업체" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②유기농raw" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'농산물업체'!$A$2:$J$287</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'①농산물raw'!$A$5:$K$1454</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'①농산물raw'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'①농산물raw'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'②유기농raw'!$A$5:$I$96</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'②유기농raw'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'②유기농raw'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'농산물업체'!$A$2:$J$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'①농산물raw'!$A$5:$K$1454</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'①농산물raw'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'①농산물raw'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'②유기농raw'!$A$5:$I$96</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'②유기농raw'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'②유기농raw'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -8684,6 +8684,2517 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:K72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="21" min="1" max="1"/>
+    <col width="14" customWidth="1" style="21" min="2" max="2"/>
+    <col width="16" customWidth="1" style="21" min="3" max="3"/>
+    <col width="26" customWidth="1" style="21" min="4" max="4"/>
+    <col width="16" customWidth="1" style="21" min="5" max="5"/>
+    <col width="45" customWidth="1" style="21" min="6" max="6"/>
+    <col width="15" customWidth="1" style="21" min="7" max="7"/>
+    <col width="15" customWidth="1" style="21" min="8" max="8"/>
+    <col width="16" customWidth="1" style="21" min="9" max="9"/>
+    <col width="16" customWidth="1" style="21" min="10" max="10"/>
+    <col width="16" customWidth="1" style="21" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="156" t="inlineStr">
+        <is>
+          <t>2026 aT 온라인 판로지원 사업 - 실적 이상치 및 규정 준수 검토 리포트</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="157" t="inlineStr">
+        <is>
+          <t>1. 사업 규정 준수 여부 전수 검토 결과 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="158" t="inlineStr">
+        <is>
+          <t>검토 규정 항목</t>
+        </is>
+      </c>
+      <c r="C5" s="158" t="inlineStr">
+        <is>
+          <t>사업 운영 기준</t>
+        </is>
+      </c>
+      <c r="D5" s="158" t="inlineStr">
+        <is>
+          <t>전수 검토 결과</t>
+        </is>
+      </c>
+      <c r="E5" s="158" t="inlineStr">
+        <is>
+          <t>준수 여부</t>
+        </is>
+      </c>
+      <c r="F5" s="158" t="inlineStr">
+        <is>
+          <t>세부 검토 내역</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="159" t="inlineStr">
+        <is>
+          <t>업체당 쿠폰 한도</t>
+        </is>
+      </c>
+      <c r="C6" s="160" t="inlineStr">
+        <is>
+          <t>업체당 최대 8,000,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="161" t="inlineStr">
+        <is>
+          <t>초과 업체 0개 (최대 소진액 6,140,240원 / 76.8%)</t>
+        </is>
+      </c>
+      <c r="E6" s="162" t="inlineStr">
+        <is>
+          <t>정상 준수</t>
+        </is>
+      </c>
+      <c r="F6" s="163" t="inlineStr">
+        <is>
+          <t>농부들(76.8%), 자연푸드(73.1%), 팜앤유(71.6%) 등 전 업체 한도 내 안전 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="159" t="inlineStr">
+        <is>
+          <t>쿠폰 할인율 상한</t>
+        </is>
+      </c>
+      <c r="C7" s="160" t="inlineStr">
+        <is>
+          <t>매출액 대비 최대 20.0%</t>
+        </is>
+      </c>
+      <c r="D7" s="161" t="inlineStr">
+        <is>
+          <t>초과 건수 0건 (최대 할인율 정확히 20.00%)</t>
+        </is>
+      </c>
+      <c r="E7" s="162" t="inlineStr">
+        <is>
+          <t>정상 준수</t>
+        </is>
+      </c>
+      <c r="F7" s="163" t="inlineStr">
+        <is>
+          <t>1,651개 로우데이터 행 전수 검사 결과 20% 초과 할인 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="159" t="inlineStr">
+        <is>
+          <t>건당 쿠폰 한도</t>
+        </is>
+      </c>
+      <c r="C8" s="160" t="inlineStr">
+        <is>
+          <t>건당(개당) 최대 10,000원</t>
+        </is>
+      </c>
+      <c r="D8" s="161" t="inlineStr">
+        <is>
+          <t>초과 건수 0건 (건당 최대 쿠폰액 정확히 10,000원)</t>
+        </is>
+      </c>
+      <c r="E8" s="162" t="inlineStr">
+        <is>
+          <t>정상 준수</t>
+        </is>
+      </c>
+      <c r="F8" s="163" t="inlineStr">
+        <is>
+          <t>롯데ON 등 10,000원 정액 적용 건 존재하나 초과 건 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="157" t="inlineStr">
+        <is>
+          <t>2. 누적 실적 역전(감소) 이상치 내역 (총 4건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="158" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C12" s="158" t="inlineStr">
+        <is>
+          <t>유통사</t>
+        </is>
+      </c>
+      <c r="D12" s="158" t="inlineStr">
+        <is>
+          <t>사업자명</t>
+        </is>
+      </c>
+      <c r="E12" s="158" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="F12" s="158" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="G12" s="158" t="inlineStr">
+        <is>
+          <t>7월 실적</t>
+        </is>
+      </c>
+      <c r="H12" s="158" t="inlineStr">
+        <is>
+          <t>8월 누적실적</t>
+        </is>
+      </c>
+      <c r="I12" s="158" t="inlineStr">
+        <is>
+          <t>증감(8월순수)</t>
+        </is>
+      </c>
+      <c r="J12" s="158" t="inlineStr">
+        <is>
+          <t>이상 원인 분석 및 특이사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="164" t="inlineStr">
+        <is>
+          <t>업체 쿠폰 역전</t>
+        </is>
+      </c>
+      <c r="C13" s="164" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="D13" s="165" t="inlineStr">
+        <is>
+          <t>농업회사법인 랑이네세상 주식회사</t>
+        </is>
+      </c>
+      <c r="E13" s="164" t="inlineStr">
+        <is>
+          <t>488-88-03205</t>
+        </is>
+      </c>
+      <c r="F13" s="165" t="inlineStr">
+        <is>
+          <t>[업체 전체 쿠폰]</t>
+        </is>
+      </c>
+      <c r="G13" s="166" t="inlineStr">
+        <is>
+          <t>4,955,760원</t>
+        </is>
+      </c>
+      <c r="H13" s="166" t="inlineStr">
+        <is>
+          <t>4,947,920원</t>
+        </is>
+      </c>
+      <c r="I13" s="167" t="inlineStr">
+        <is>
+          <t>-7,840원</t>
+        </is>
+      </c>
+      <c r="J13" s="165" t="inlineStr">
+        <is>
+          <t>매출/건수는 증가했으나 쿠폰 사용액이 7월 대비 누적에서 7,840원 감소 (주문취소/환불 반영 의심)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="164" t="inlineStr">
+        <is>
+          <t>상품 매출 역전</t>
+        </is>
+      </c>
+      <c r="C14" s="164" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="D14" s="165" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)더봄</t>
+        </is>
+      </c>
+      <c r="E14" s="164" t="inlineStr">
+        <is>
+          <t>138-81-67809</t>
+        </is>
+      </c>
+      <c r="F14" s="165" t="inlineStr">
+        <is>
+          <t>생화용 백합 꽃 백합생화 1000ml x 5</t>
+        </is>
+      </c>
+      <c r="G14" s="166" t="inlineStr">
+        <is>
+          <t>60,000원 (1건)</t>
+        </is>
+      </c>
+      <c r="H14" s="166" t="inlineStr">
+        <is>
+          <t>0원 (0건)</t>
+        </is>
+      </c>
+      <c r="I14" s="167" t="inlineStr">
+        <is>
+          <t>-60,000원 (-1건)</t>
+        </is>
+      </c>
+      <c r="J14" s="165" t="inlineStr">
+        <is>
+          <t>7월에 1건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="164" t="inlineStr">
+        <is>
+          <t>상품 매출 역전</t>
+        </is>
+      </c>
+      <c r="C15" s="164" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="D15" s="165" t="inlineStr">
+        <is>
+          <t>더모닝</t>
+        </is>
+      </c>
+      <c r="E15" s="164" t="inlineStr">
+        <is>
+          <t>655-09-02685</t>
+        </is>
+      </c>
+      <c r="F15" s="165" t="inlineStr">
+        <is>
+          <t>더모닝 닭 볶음탕 닭볶음탕 90g 1인분 x 5팩 캠핑 밀키트</t>
+        </is>
+      </c>
+      <c r="G15" s="166" t="inlineStr">
+        <is>
+          <t>240,000원 (12건)</t>
+        </is>
+      </c>
+      <c r="H15" s="166" t="inlineStr">
+        <is>
+          <t>0원 (0건)</t>
+        </is>
+      </c>
+      <c r="I15" s="167" t="inlineStr">
+        <is>
+          <t>-240,000원 (-12건)</t>
+        </is>
+      </c>
+      <c r="J15" s="165" t="inlineStr">
+        <is>
+          <t>7월에 12건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="164" t="inlineStr">
+        <is>
+          <t>상품 매출 역전</t>
+        </is>
+      </c>
+      <c r="C16" s="164" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="D16" s="165" t="inlineStr">
+        <is>
+          <t>더모닝</t>
+        </is>
+      </c>
+      <c r="E16" s="164" t="inlineStr">
+        <is>
+          <t>655-09-02685</t>
+        </is>
+      </c>
+      <c r="F16" s="165" t="inlineStr">
+        <is>
+          <t>더모닝 닭 볶음탕 닭볶음탕 400g 4인분 캠핑 밀키트</t>
+        </is>
+      </c>
+      <c r="G16" s="166" t="inlineStr">
+        <is>
+          <t>54,000원 (3건)</t>
+        </is>
+      </c>
+      <c r="H16" s="166" t="inlineStr">
+        <is>
+          <t>0원 (0건)</t>
+        </is>
+      </c>
+      <c r="I16" s="167" t="inlineStr">
+        <is>
+          <t>-54,000원 (-3건)</t>
+        </is>
+      </c>
+      <c r="J16" s="165" t="inlineStr">
+        <is>
+          <t>7월에 3건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="157" t="inlineStr">
+        <is>
+          <t>3. 업체별 쿠폰 한도(800만원) 소진율 상위 Top 10 업체 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="158" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C20" s="158" t="inlineStr">
+        <is>
+          <t>사업자명</t>
+        </is>
+      </c>
+      <c r="D20" s="158" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="E20" s="158" t="inlineStr">
+        <is>
+          <t>참여 유통사</t>
+        </is>
+      </c>
+      <c r="F20" s="158" t="inlineStr">
+        <is>
+          <t>누적 매출액</t>
+        </is>
+      </c>
+      <c r="G20" s="158" t="inlineStr">
+        <is>
+          <t>누적 쿠폰사용액</t>
+        </is>
+      </c>
+      <c r="H20" s="158" t="inlineStr">
+        <is>
+          <t>한도(800만원) 소진율</t>
+        </is>
+      </c>
+      <c r="I20" s="158" t="inlineStr">
+        <is>
+          <t>잔여 한도액</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="169" t="inlineStr">
+        <is>
+          <t>농부들</t>
+        </is>
+      </c>
+      <c r="D21" s="168" t="inlineStr">
+        <is>
+          <t>579-90-00021</t>
+        </is>
+      </c>
+      <c r="E21" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F21" s="170" t="n">
+        <v>53342360</v>
+      </c>
+      <c r="G21" s="171" t="n">
+        <v>6140240</v>
+      </c>
+      <c r="H21" s="172" t="inlineStr">
+        <is>
+          <t>76.8%</t>
+        </is>
+      </c>
+      <c r="I21" s="170" t="n">
+        <v>1859760</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="168" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)자연푸드</t>
+        </is>
+      </c>
+      <c r="D22" s="168" t="inlineStr">
+        <is>
+          <t>412-81-50546</t>
+        </is>
+      </c>
+      <c r="E22" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F22" s="170" t="n">
+        <v>55214000</v>
+      </c>
+      <c r="G22" s="171" t="n">
+        <v>5847700</v>
+      </c>
+      <c r="H22" s="172" t="inlineStr">
+        <is>
+          <t>73.1%</t>
+        </is>
+      </c>
+      <c r="I22" s="170" t="n">
+        <v>2152300</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="169" t="inlineStr">
+        <is>
+          <t>팜앤유</t>
+        </is>
+      </c>
+      <c r="D23" s="168" t="inlineStr">
+        <is>
+          <t>477-93-01384</t>
+        </is>
+      </c>
+      <c r="E23" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="F23" s="170" t="n">
+        <v>41243100</v>
+      </c>
+      <c r="G23" s="171" t="n">
+        <v>5728100</v>
+      </c>
+      <c r="H23" s="172" t="inlineStr">
+        <is>
+          <t>71.6%</t>
+        </is>
+      </c>
+      <c r="I23" s="170" t="n">
+        <v>2271900</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="169" t="inlineStr">
+        <is>
+          <t>(주)다채몰</t>
+        </is>
+      </c>
+      <c r="D24" s="168" t="inlineStr">
+        <is>
+          <t>114-86-65039</t>
+        </is>
+      </c>
+      <c r="E24" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F24" s="170" t="n">
+        <v>39871200</v>
+      </c>
+      <c r="G24" s="171" t="n">
+        <v>5268240</v>
+      </c>
+      <c r="H24" s="159" t="inlineStr">
+        <is>
+          <t>65.9%</t>
+        </is>
+      </c>
+      <c r="I24" s="170" t="n">
+        <v>2731760</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="169" t="inlineStr">
+        <is>
+          <t>해남농협</t>
+        </is>
+      </c>
+      <c r="D25" s="168" t="inlineStr">
+        <is>
+          <t>323-88-00158</t>
+        </is>
+      </c>
+      <c r="E25" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="F25" s="170" t="n">
+        <v>45120000</v>
+      </c>
+      <c r="G25" s="171" t="n">
+        <v>5136630</v>
+      </c>
+      <c r="H25" s="159" t="inlineStr">
+        <is>
+          <t>64.2%</t>
+        </is>
+      </c>
+      <c r="I25" s="170" t="n">
+        <v>2863370</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인 주식회사 드림마이스터</t>
+        </is>
+      </c>
+      <c r="D26" s="168" t="inlineStr">
+        <is>
+          <t>485-88-00795</t>
+        </is>
+      </c>
+      <c r="E26" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F26" s="170" t="n">
+        <v>36240000</v>
+      </c>
+      <c r="G26" s="171" t="n">
+        <v>5105280</v>
+      </c>
+      <c r="H26" s="159" t="inlineStr">
+        <is>
+          <t>63.8%</t>
+        </is>
+      </c>
+      <c r="I26" s="170" t="n">
+        <v>2894720</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인 철원이곡 주식회사</t>
+        </is>
+      </c>
+      <c r="D27" s="168" t="inlineStr">
+        <is>
+          <t>127-81-93991</t>
+        </is>
+      </c>
+      <c r="E27" s="168" t="inlineStr">
+        <is>
+          <t>농가살리기</t>
+        </is>
+      </c>
+      <c r="F27" s="170" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="G27" s="171" t="n">
+        <v>5097728</v>
+      </c>
+      <c r="H27" s="159" t="inlineStr">
+        <is>
+          <t>63.7%</t>
+        </is>
+      </c>
+      <c r="I27" s="170" t="n">
+        <v>2902272</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="168" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="169" t="inlineStr">
+        <is>
+          <t>해주농협통합</t>
+        </is>
+      </c>
+      <c r="D28" s="168" t="inlineStr">
+        <is>
+          <t>126-82-11620</t>
+        </is>
+      </c>
+      <c r="E28" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="F28" s="170" t="n">
+        <v>48900000</v>
+      </c>
+      <c r="G28" s="171" t="n">
+        <v>5085890</v>
+      </c>
+      <c r="H28" s="159" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="I28" s="170" t="n">
+        <v>2914110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="168" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="169" t="inlineStr">
+        <is>
+          <t>두원식품(주)</t>
+        </is>
+      </c>
+      <c r="D29" s="168" t="inlineStr">
+        <is>
+          <t>606-81-52718</t>
+        </is>
+      </c>
+      <c r="E29" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="F29" s="170" t="n">
+        <v>55053800</v>
+      </c>
+      <c r="G29" s="171" t="n">
+        <v>5062400</v>
+      </c>
+      <c r="H29" s="159" t="inlineStr">
+        <is>
+          <t>63.3%</t>
+        </is>
+      </c>
+      <c r="I29" s="170" t="n">
+        <v>2937600</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="168" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="169" t="inlineStr">
+        <is>
+          <t>청양농협</t>
+        </is>
+      </c>
+      <c r="D30" s="168" t="inlineStr">
+        <is>
+          <t>499-51-00634</t>
+        </is>
+      </c>
+      <c r="E30" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="F30" s="170" t="n">
+        <v>38100000</v>
+      </c>
+      <c r="G30" s="171" t="n">
+        <v>5049440</v>
+      </c>
+      <c r="H30" s="159" t="inlineStr">
+        <is>
+          <t>63.1%</t>
+        </is>
+      </c>
+      <c r="I30" s="170" t="n">
+        <v>2950560</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="157" t="inlineStr">
+        <is>
+          <t>4. 농가·유통사 품목분류 자의적 변경 이상건 전수 내역 (총 38건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="158" t="inlineStr">
+        <is>
+          <t>유통사</t>
+        </is>
+      </c>
+      <c r="D34" s="158" t="inlineStr">
+        <is>
+          <t>사업자명</t>
+        </is>
+      </c>
+      <c r="E34" s="158" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="F34" s="158" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="G34" s="158" t="inlineStr">
+        <is>
+          <t>7월 분류</t>
+        </is>
+      </c>
+      <c r="H34" s="158" t="inlineStr">
+        <is>
+          <t>8월 변경분류</t>
+        </is>
+      </c>
+      <c r="I34" s="158" t="inlineStr">
+        <is>
+          <t>7월 매출액</t>
+        </is>
+      </c>
+      <c r="J34" s="158" t="inlineStr">
+        <is>
+          <t>8월 누적매출액</t>
+        </is>
+      </c>
+      <c r="K34" s="158" t="inlineStr">
+        <is>
+          <t>8월 순수매출액</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="D35" s="169" t="inlineStr">
+        <is>
+          <t>주식회사 태범프레시</t>
+        </is>
+      </c>
+      <c r="E35" s="168" t="inlineStr">
+        <is>
+          <t>832-86-02035</t>
+        </is>
+      </c>
+      <c r="F35" s="169" t="inlineStr">
+        <is>
+          <t>[홍익상회] 춘천닭갈비 500g x 3팩 국내산닭고기 양념 순살</t>
+        </is>
+      </c>
+      <c r="G35" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H35" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I35" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="168" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="D36" s="169" t="inlineStr">
+        <is>
+          <t>주식회사 태범프레시</t>
+        </is>
+      </c>
+      <c r="E36" s="168" t="inlineStr">
+        <is>
+          <t>832-86-02035</t>
+        </is>
+      </c>
+      <c r="F36" s="169" t="inlineStr">
+        <is>
+          <t>[홍익상회] 춘천 홍익닭갈비 500g x 3팩 국내산 닭고기 양념 순살</t>
+        </is>
+      </c>
+      <c r="G36" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H36" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I36" s="170" t="n">
+        <v>2552440</v>
+      </c>
+      <c r="J36" s="170" t="n">
+        <v>2552440</v>
+      </c>
+      <c r="K36" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="D37" s="169" t="inlineStr">
+        <is>
+          <t>신선식품</t>
+        </is>
+      </c>
+      <c r="E37" s="168" t="inlineStr">
+        <is>
+          <t>131-35-96215</t>
+        </is>
+      </c>
+      <c r="F37" s="169" t="inlineStr">
+        <is>
+          <t>[온누리7%혜택]고소한 국산 볶은참깨 200g</t>
+        </is>
+      </c>
+      <c r="G37" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H37" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I37" s="170" t="n">
+        <v>25600</v>
+      </c>
+      <c r="J37" s="170" t="n">
+        <v>204800</v>
+      </c>
+      <c r="K37" s="174" t="n">
+        <v>179200</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D38" s="169" t="inlineStr">
+        <is>
+          <t>두원식품(주)</t>
+        </is>
+      </c>
+      <c r="E38" s="168" t="inlineStr">
+        <is>
+          <t>606-81-52718</t>
+        </is>
+      </c>
+      <c r="F38" s="169" t="inlineStr">
+        <is>
+          <t>(신선집중) 국내산 한돈 프리미엄 대패 삼겹살 1.2kg</t>
+        </is>
+      </c>
+      <c r="G38" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H38" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I38" s="170" t="n">
+        <v>51796200</v>
+      </c>
+      <c r="J38" s="170" t="n">
+        <v>55053800</v>
+      </c>
+      <c r="K38" s="174" t="n">
+        <v>3257600</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D39" s="169" t="inlineStr">
+        <is>
+          <t>다모아영농조합법인</t>
+        </is>
+      </c>
+      <c r="E39" s="168" t="inlineStr">
+        <is>
+          <t>613-81-60803</t>
+        </is>
+      </c>
+      <c r="F39" s="169" t="inlineStr">
+        <is>
+          <t>농협 공동선별 햇 남해 통마늘 3kg(상) 실중량 지리적표시품</t>
+        </is>
+      </c>
+      <c r="G39" s="159" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="H39" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I39" s="170" t="n">
+        <v>73800</v>
+      </c>
+      <c r="J39" s="170" t="n">
+        <v>701100</v>
+      </c>
+      <c r="K39" s="174" t="n">
+        <v>627300</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D40" s="169" t="inlineStr">
+        <is>
+          <t>청정태안식품</t>
+        </is>
+      </c>
+      <c r="E40" s="168" t="inlineStr">
+        <is>
+          <t>316-01-24597</t>
+        </is>
+      </c>
+      <c r="F40" s="169" t="inlineStr">
+        <is>
+          <t>김명월 검정콩 청국장가루 1kg(500g2통)</t>
+        </is>
+      </c>
+      <c r="G40" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H40" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I40" s="170" t="n">
+        <v>74000</v>
+      </c>
+      <c r="J40" s="170" t="n">
+        <v>222000</v>
+      </c>
+      <c r="K40" s="174" t="n">
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="168" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D41" s="169" t="inlineStr">
+        <is>
+          <t>청정태안식품</t>
+        </is>
+      </c>
+      <c r="E41" s="168" t="inlineStr">
+        <is>
+          <t>316-01-24597</t>
+        </is>
+      </c>
+      <c r="F41" s="169" t="inlineStr">
+        <is>
+          <t>김명월 검정콩 청국장가루 1kg(500g2통)</t>
+        </is>
+      </c>
+      <c r="G41" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H41" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I41" s="170" t="n">
+        <v>74000</v>
+      </c>
+      <c r="J41" s="170" t="n">
+        <v>259000</v>
+      </c>
+      <c r="K41" s="174" t="n">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="168" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D42" s="169" t="inlineStr">
+        <is>
+          <t>형지표고버섯</t>
+        </is>
+      </c>
+      <c r="E42" s="168" t="inlineStr">
+        <is>
+          <t>290-94-00335</t>
+        </is>
+      </c>
+      <c r="F42" s="169" t="inlineStr">
+        <is>
+          <t>형지표고버섯 흑화고 상황버섯 혼합2호 표고 버섯 선물세트</t>
+        </is>
+      </c>
+      <c r="G42" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H42" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I42" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="168" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D43" s="169" t="inlineStr">
+        <is>
+          <t>농부플러스</t>
+        </is>
+      </c>
+      <c r="E43" s="168" t="inlineStr">
+        <is>
+          <t>571-81-00383</t>
+        </is>
+      </c>
+      <c r="F43" s="169" t="inlineStr">
+        <is>
+          <t>국산 볶음참깨 햇 참깨 볶은참깨 토종 통깨 200g</t>
+        </is>
+      </c>
+      <c r="G43" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H43" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I43" s="170" t="n">
+        <v>360800</v>
+      </c>
+      <c r="J43" s="170" t="n">
+        <v>1098800</v>
+      </c>
+      <c r="K43" s="174" t="n">
+        <v>738000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="168" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D44" s="169" t="inlineStr">
+        <is>
+          <t>농부플러스</t>
+        </is>
+      </c>
+      <c r="E44" s="168" t="inlineStr">
+        <is>
+          <t>571-81-00383</t>
+        </is>
+      </c>
+      <c r="F44" s="169" t="inlineStr">
+        <is>
+          <t>국산 볶음참깨 햇 참깨 볶은참깨 토종 통깨 150g</t>
+        </is>
+      </c>
+      <c r="G44" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H44" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I44" s="170" t="n">
+        <v>13900</v>
+      </c>
+      <c r="J44" s="170" t="n">
+        <v>42700</v>
+      </c>
+      <c r="K44" s="174" t="n">
+        <v>28800</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="168" t="n">
+        <v>11</v>
+      </c>
+      <c r="C45" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D45" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간</t>
+        </is>
+      </c>
+      <c r="E45" s="168" t="inlineStr">
+        <is>
+          <t>181-02-01980</t>
+        </is>
+      </c>
+      <c r="F45" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간 국내산 볶은 귀리 / 아침식사대용 간식</t>
+        </is>
+      </c>
+      <c r="G45" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H45" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I45" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="168" t="n">
+        <v>12</v>
+      </c>
+      <c r="C46" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D46" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간</t>
+        </is>
+      </c>
+      <c r="E46" s="168" t="inlineStr">
+        <is>
+          <t>181-02-01980</t>
+        </is>
+      </c>
+      <c r="F46" s="169" t="inlineStr">
+        <is>
+          <t>듬뿍곡간 국내산 쑥미숫가루 / 선식 식사대용 간식 500g</t>
+        </is>
+      </c>
+      <c r="G46" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H46" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I46" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="170" t="n">
+        <v>23800</v>
+      </c>
+      <c r="K46" s="174" t="n">
+        <v>23800</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="168" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D47" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)가남농원</t>
+        </is>
+      </c>
+      <c r="E47" s="168" t="inlineStr">
+        <is>
+          <t>416-81-59229</t>
+        </is>
+      </c>
+      <c r="F47" s="169" t="inlineStr">
+        <is>
+          <t>김승희매실가 신지식 농업인이 만든 매실절임 1kg</t>
+        </is>
+      </c>
+      <c r="G47" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H47" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I47" s="170" t="n">
+        <v>66000</v>
+      </c>
+      <c r="J47" s="170" t="n">
+        <v>165000</v>
+      </c>
+      <c r="K47" s="174" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="168" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D48" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)가남농원</t>
+        </is>
+      </c>
+      <c r="E48" s="168" t="inlineStr">
+        <is>
+          <t>416-81-59229</t>
+        </is>
+      </c>
+      <c r="F48" s="169" t="inlineStr">
+        <is>
+          <t>천기누설 매실 장인이만든 매실고 (농축액) 150g</t>
+        </is>
+      </c>
+      <c r="G48" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H48" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I48" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="168" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D49" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인(주)가남농원</t>
+        </is>
+      </c>
+      <c r="E49" s="168" t="inlineStr">
+        <is>
+          <t>416-81-59229</t>
+        </is>
+      </c>
+      <c r="F49" s="169" t="inlineStr">
+        <is>
+          <t>천기누설 매실 장인이만든 매실고 (농축액) 150g</t>
+        </is>
+      </c>
+      <c r="G49" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H49" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I49" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="170" t="n">
+        <v>43000</v>
+      </c>
+      <c r="K49" s="174" t="n">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="168" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D50" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인 팜팜(주)</t>
+        </is>
+      </c>
+      <c r="E50" s="168" t="inlineStr">
+        <is>
+          <t>177-81-00798</t>
+        </is>
+      </c>
+      <c r="F50" s="169" t="inlineStr">
+        <is>
+          <t>(품질보증) 산지직송 정품과 완숙토마토 5KG 당일수확 유럽종</t>
+        </is>
+      </c>
+      <c r="G50" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H50" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I50" s="170" t="n">
+        <v>694600</v>
+      </c>
+      <c r="J50" s="170" t="n">
+        <v>5967100</v>
+      </c>
+      <c r="K50" s="174" t="n">
+        <v>5272500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="168" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D51" s="169" t="inlineStr">
+        <is>
+          <t>농업회사법인주식회사 늘해랑</t>
+        </is>
+      </c>
+      <c r="E51" s="168" t="inlineStr">
+        <is>
+          <t>756-87-00841</t>
+        </is>
+      </c>
+      <c r="F51" s="169" t="inlineStr">
+        <is>
+          <t>조은해남 고구마 못난이 10kg (꿀호박 랜덤발송)</t>
+        </is>
+      </c>
+      <c r="G51" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H51" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I51" s="170" t="n">
+        <v>371800</v>
+      </c>
+      <c r="J51" s="170" t="n">
+        <v>2827100</v>
+      </c>
+      <c r="K51" s="174" t="n">
+        <v>2455300</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="168" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D52" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E52" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F52" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G52" s="159" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="H52" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I52" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="168" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D53" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E53" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F53" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G53" s="159" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="H53" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I53" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="170" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K53" s="174" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="168" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D54" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E54" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F54" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산100% 도토리묵 묵사발 세트</t>
+        </is>
+      </c>
+      <c r="G54" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H54" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I54" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="168" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D55" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E55" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F55" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 명인 국산 콩물 우묵채 (2인분)</t>
+        </is>
+      </c>
+      <c r="G55" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H55" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I55" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="168" t="n">
+        <v>22</v>
+      </c>
+      <c r="C56" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D56" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E56" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F56" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G56" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H56" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I56" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="168" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D57" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E57" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F57" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G57" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H57" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I57" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="K57" s="174" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="168" t="n">
+        <v>24</v>
+      </c>
+      <c r="C58" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D58" s="169" t="inlineStr">
+        <is>
+          <t>그린몬스터즈</t>
+        </is>
+      </c>
+      <c r="E58" s="168" t="inlineStr">
+        <is>
+          <t>883-95-01472</t>
+        </is>
+      </c>
+      <c r="F58" s="169" t="inlineStr">
+        <is>
+          <t>당일수확발송 그린몬스터즈 프리미엄 미니오이 1.5kg 농장직거래 여름작기 첫수확 특가할인행사</t>
+        </is>
+      </c>
+      <c r="G58" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H58" s="173" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="I58" s="170" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J58" s="170" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K58" s="174" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="168" t="n">
+        <v>25</v>
+      </c>
+      <c r="C59" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D59" s="169" t="inlineStr">
+        <is>
+          <t>어이딸부각</t>
+        </is>
+      </c>
+      <c r="E59" s="168" t="inlineStr">
+        <is>
+          <t>142-33-00898</t>
+        </is>
+      </c>
+      <c r="F59" s="169" t="inlineStr">
+        <is>
+          <t>고추크런치 70g 고추부각 튀각 찹쌀 수제 비건</t>
+        </is>
+      </c>
+      <c r="G59" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H59" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I59" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="168" t="n">
+        <v>26</v>
+      </c>
+      <c r="C60" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D60" s="169" t="inlineStr">
+        <is>
+          <t>어이딸부각</t>
+        </is>
+      </c>
+      <c r="E60" s="168" t="inlineStr">
+        <is>
+          <t>142-33-00898</t>
+        </is>
+      </c>
+      <c r="F60" s="169" t="inlineStr">
+        <is>
+          <t>어이딸 김부각 선물세트 소 5개입 찹쌀 수제 비건 글루텐프리 저당</t>
+        </is>
+      </c>
+      <c r="G60" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H60" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I60" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="170" t="n">
+        <v>690000</v>
+      </c>
+      <c r="K60" s="174" t="n">
+        <v>690000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="168" t="n">
+        <v>27</v>
+      </c>
+      <c r="C61" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D61" s="169" t="inlineStr">
+        <is>
+          <t>어이딸부각</t>
+        </is>
+      </c>
+      <c r="E61" s="168" t="inlineStr">
+        <is>
+          <t>142-33-00898</t>
+        </is>
+      </c>
+      <c r="F61" s="169" t="inlineStr">
+        <is>
+          <t>어이딸 김부각 선물세트 중 8개입 찹쌀 수제 비건 글루텐프리 저당</t>
+        </is>
+      </c>
+      <c r="G61" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H61" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I61" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="168" t="n">
+        <v>28</v>
+      </c>
+      <c r="C62" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D62" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E62" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F62" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G62" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H62" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I62" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="168" t="n">
+        <v>29</v>
+      </c>
+      <c r="C63" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D63" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E63" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F63" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
+        </is>
+      </c>
+      <c r="G63" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H63" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I63" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="170" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K63" s="174" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="168" t="n">
+        <v>30</v>
+      </c>
+      <c r="C64" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D64" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E64" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F64" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G64" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H64" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I64" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J64" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="174" t="n">
+        <v>-240000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="168" t="n">
+        <v>31</v>
+      </c>
+      <c r="C65" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D65" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E65" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F65" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G65" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H65" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I65" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J65" s="170" t="n">
+        <v>240000</v>
+      </c>
+      <c r="K65" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="168" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D66" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E66" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F66" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 400g 4인분 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G66" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H66" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I66" s="170" t="n">
+        <v>54000</v>
+      </c>
+      <c r="J66" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="174" t="n">
+        <v>-54000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="168" t="n">
+        <v>33</v>
+      </c>
+      <c r="C67" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="D67" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵</t>
+        </is>
+      </c>
+      <c r="E67" s="168" t="inlineStr">
+        <is>
+          <t>615-14-93195</t>
+        </is>
+      </c>
+      <c r="F67" s="169" t="inlineStr">
+        <is>
+          <t>초림단지묵 국산 콩물 콩가루 400g 4인분 물만타면 콩국수</t>
+        </is>
+      </c>
+      <c r="G67" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H67" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I67" s="170" t="n">
+        <v>54000</v>
+      </c>
+      <c r="J67" s="170" t="n">
+        <v>54000</v>
+      </c>
+      <c r="K67" s="174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="168" t="n">
+        <v>34</v>
+      </c>
+      <c r="C68" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D68" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E68" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F68" s="169" t="inlineStr">
+        <is>
+          <t>한돈 제육볶음 (650g X 1개)</t>
+        </is>
+      </c>
+      <c r="G68" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H68" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I68" s="170" t="n">
+        <v>20305100</v>
+      </c>
+      <c r="J68" s="170" t="n">
+        <v>46426900</v>
+      </c>
+      <c r="K68" s="174" t="n">
+        <v>26121800</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="168" t="n">
+        <v>35</v>
+      </c>
+      <c r="C69" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D69" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E69" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F69" s="169" t="inlineStr">
+        <is>
+          <t>한돈 칼집 양념구이 (650g X 1개)</t>
+        </is>
+      </c>
+      <c r="G69" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H69" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I69" s="170" t="n">
+        <v>16019900</v>
+      </c>
+      <c r="J69" s="170" t="n">
+        <v>30197000</v>
+      </c>
+      <c r="K69" s="174" t="n">
+        <v>14177100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="168" t="n">
+        <v>36</v>
+      </c>
+      <c r="C70" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D70" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E70" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F70" s="169" t="inlineStr">
+        <is>
+          <t>한돈 성북동식 돼지불백 (650g X 1개)</t>
+        </is>
+      </c>
+      <c r="G70" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H70" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I70" s="170" t="n">
+        <v>10928700</v>
+      </c>
+      <c r="J70" s="170" t="n">
+        <v>21744400</v>
+      </c>
+      <c r="K70" s="174" t="n">
+        <v>10815700</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="168" t="n">
+        <v>37</v>
+      </c>
+      <c r="C71" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D71" s="169" t="inlineStr">
+        <is>
+          <t>케이에프지</t>
+        </is>
+      </c>
+      <c r="E71" s="168" t="inlineStr">
+        <is>
+          <t>120-86-08936</t>
+        </is>
+      </c>
+      <c r="F71" s="169" t="inlineStr">
+        <is>
+          <t>서울식 한우 불고기 밀키트 (800g X 1개)</t>
+        </is>
+      </c>
+      <c r="G71" s="159" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="H71" s="173" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="I71" s="170" t="n">
+        <v>6922200</v>
+      </c>
+      <c r="J71" s="170" t="n">
+        <v>15422600</v>
+      </c>
+      <c r="K71" s="174" t="n">
+        <v>8500400</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="168" t="n">
+        <v>38</v>
+      </c>
+      <c r="C72" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="D72" s="169" t="inlineStr">
+        <is>
+          <t>해담는집</t>
+        </is>
+      </c>
+      <c r="E72" s="168" t="inlineStr">
+        <is>
+          <t>745-96-00315</t>
+        </is>
+      </c>
+      <c r="F72" s="169" t="inlineStr">
+        <is>
+          <t>해담는집 유기농 고춧가루 500g/200g(순한맛/보통맛/매운맛)</t>
+        </is>
+      </c>
+      <c r="G72" s="159" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="H72" s="173" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="I72" s="170" t="n">
+        <v>208400</v>
+      </c>
+      <c r="J72" s="170" t="n">
+        <v>434900</v>
+      </c>
+      <c r="K72" s="174" t="n">
+        <v>226500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
@@ -20354,7 +22865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -72661,7 +75172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -74976,7 +77487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -82376,2515 +84887,4 @@
   <pageSetup orientation="portrait" paperSize="9" scale="36"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:K72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" style="21" min="1" max="1"/>
-    <col width="14" customWidth="1" style="21" min="2" max="2"/>
-    <col width="16" customWidth="1" style="21" min="3" max="3"/>
-    <col width="26" customWidth="1" style="21" min="4" max="4"/>
-    <col width="16" customWidth="1" style="21" min="5" max="5"/>
-    <col width="45" customWidth="1" style="21" min="6" max="6"/>
-    <col width="15" customWidth="1" style="21" min="7" max="7"/>
-    <col width="15" customWidth="1" style="21" min="8" max="8"/>
-    <col width="16" customWidth="1" style="21" min="9" max="9"/>
-    <col width="16" customWidth="1" style="21" min="10" max="10"/>
-    <col width="16" customWidth="1" style="21" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="156" t="inlineStr">
-        <is>
-          <t>2026 aT 온라인 판로지원 사업 - 실적 이상치 및 규정 준수 검토 리포트</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="157" t="inlineStr">
-        <is>
-          <t>1. 사업 규정 준수 여부 전수 검토 결과 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="158" t="inlineStr">
-        <is>
-          <t>검토 규정 항목</t>
-        </is>
-      </c>
-      <c r="C5" s="158" t="inlineStr">
-        <is>
-          <t>사업 운영 기준</t>
-        </is>
-      </c>
-      <c r="D5" s="158" t="inlineStr">
-        <is>
-          <t>전수 검토 결과</t>
-        </is>
-      </c>
-      <c r="E5" s="158" t="inlineStr">
-        <is>
-          <t>준수 여부</t>
-        </is>
-      </c>
-      <c r="F5" s="158" t="inlineStr">
-        <is>
-          <t>세부 검토 내역</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="159" t="inlineStr">
-        <is>
-          <t>업체당 쿠폰 한도</t>
-        </is>
-      </c>
-      <c r="C6" s="160" t="inlineStr">
-        <is>
-          <t>업체당 최대 8,000,000원</t>
-        </is>
-      </c>
-      <c r="D6" s="161" t="inlineStr">
-        <is>
-          <t>초과 업체 0개 (최대 소진액 6,140,240원 / 76.8%)</t>
-        </is>
-      </c>
-      <c r="E6" s="162" t="inlineStr">
-        <is>
-          <t>정상 준수</t>
-        </is>
-      </c>
-      <c r="F6" s="163" t="inlineStr">
-        <is>
-          <t>농부들(76.8%), 자연푸드(73.1%), 팜앤유(71.6%) 등 전 업체 한도 내 안전 운영</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="159" t="inlineStr">
-        <is>
-          <t>쿠폰 할인율 상한</t>
-        </is>
-      </c>
-      <c r="C7" s="160" t="inlineStr">
-        <is>
-          <t>매출액 대비 최대 20.0%</t>
-        </is>
-      </c>
-      <c r="D7" s="161" t="inlineStr">
-        <is>
-          <t>초과 건수 0건 (최대 할인율 정확히 20.00%)</t>
-        </is>
-      </c>
-      <c r="E7" s="162" t="inlineStr">
-        <is>
-          <t>정상 준수</t>
-        </is>
-      </c>
-      <c r="F7" s="163" t="inlineStr">
-        <is>
-          <t>1,651개 로우데이터 행 전수 검사 결과 20% 초과 할인 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="159" t="inlineStr">
-        <is>
-          <t>건당 쿠폰 한도</t>
-        </is>
-      </c>
-      <c r="C8" s="160" t="inlineStr">
-        <is>
-          <t>건당(개당) 최대 10,000원</t>
-        </is>
-      </c>
-      <c r="D8" s="161" t="inlineStr">
-        <is>
-          <t>초과 건수 0건 (건당 최대 쿠폰액 정확히 10,000원)</t>
-        </is>
-      </c>
-      <c r="E8" s="162" t="inlineStr">
-        <is>
-          <t>정상 준수</t>
-        </is>
-      </c>
-      <c r="F8" s="163" t="inlineStr">
-        <is>
-          <t>롯데ON 등 10,000원 정액 적용 건 존재하나 초과 건 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="157" t="inlineStr">
-        <is>
-          <t>2. 누적 실적 역전(감소) 이상치 내역 (총 4건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="158" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C12" s="158" t="inlineStr">
-        <is>
-          <t>유통사</t>
-        </is>
-      </c>
-      <c r="D12" s="158" t="inlineStr">
-        <is>
-          <t>사업자명</t>
-        </is>
-      </c>
-      <c r="E12" s="158" t="inlineStr">
-        <is>
-          <t>사업자번호</t>
-        </is>
-      </c>
-      <c r="F12" s="158" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="G12" s="158" t="inlineStr">
-        <is>
-          <t>7월 실적</t>
-        </is>
-      </c>
-      <c r="H12" s="158" t="inlineStr">
-        <is>
-          <t>8월 누적실적</t>
-        </is>
-      </c>
-      <c r="I12" s="158" t="inlineStr">
-        <is>
-          <t>증감(8월순수)</t>
-        </is>
-      </c>
-      <c r="J12" s="158" t="inlineStr">
-        <is>
-          <t>이상 원인 분석 및 특이사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="164" t="inlineStr">
-        <is>
-          <t>업체 쿠폰 역전</t>
-        </is>
-      </c>
-      <c r="C13" s="164" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-      <c r="D13" s="165" t="inlineStr">
-        <is>
-          <t>농업회사법인 랑이네세상 주식회사</t>
-        </is>
-      </c>
-      <c r="E13" s="164" t="inlineStr">
-        <is>
-          <t>488-88-03205</t>
-        </is>
-      </c>
-      <c r="F13" s="165" t="inlineStr">
-        <is>
-          <t>[업체 전체 쿠폰]</t>
-        </is>
-      </c>
-      <c r="G13" s="166" t="inlineStr">
-        <is>
-          <t>4,955,760원</t>
-        </is>
-      </c>
-      <c r="H13" s="166" t="inlineStr">
-        <is>
-          <t>4,947,920원</t>
-        </is>
-      </c>
-      <c r="I13" s="167" t="inlineStr">
-        <is>
-          <t>-7,840원</t>
-        </is>
-      </c>
-      <c r="J13" s="165" t="inlineStr">
-        <is>
-          <t>매출/건수는 증가했으나 쿠폰 사용액이 7월 대비 누적에서 7,840원 감소 (주문취소/환불 반영 의심)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="164" t="inlineStr">
-        <is>
-          <t>상품 매출 역전</t>
-        </is>
-      </c>
-      <c r="C14" s="164" t="inlineStr">
-        <is>
-          <t>온누리마켓</t>
-        </is>
-      </c>
-      <c r="D14" s="165" t="inlineStr">
-        <is>
-          <t>농업회사법인(주)더봄</t>
-        </is>
-      </c>
-      <c r="E14" s="164" t="inlineStr">
-        <is>
-          <t>138-81-67809</t>
-        </is>
-      </c>
-      <c r="F14" s="165" t="inlineStr">
-        <is>
-          <t>생화용 백합 꽃 백합생화 1000ml x 5</t>
-        </is>
-      </c>
-      <c r="G14" s="166" t="inlineStr">
-        <is>
-          <t>60,000원 (1건)</t>
-        </is>
-      </c>
-      <c r="H14" s="166" t="inlineStr">
-        <is>
-          <t>0원 (0건)</t>
-        </is>
-      </c>
-      <c r="I14" s="167" t="inlineStr">
-        <is>
-          <t>-60,000원 (-1건)</t>
-        </is>
-      </c>
-      <c r="J14" s="165" t="inlineStr">
-        <is>
-          <t>7월에 1건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="164" t="inlineStr">
-        <is>
-          <t>상품 매출 역전</t>
-        </is>
-      </c>
-      <c r="C15" s="164" t="inlineStr">
-        <is>
-          <t>온누리마켓</t>
-        </is>
-      </c>
-      <c r="D15" s="165" t="inlineStr">
-        <is>
-          <t>더모닝</t>
-        </is>
-      </c>
-      <c r="E15" s="164" t="inlineStr">
-        <is>
-          <t>655-09-02685</t>
-        </is>
-      </c>
-      <c r="F15" s="165" t="inlineStr">
-        <is>
-          <t>더모닝 닭 볶음탕 닭볶음탕 90g 1인분 x 5팩 캠핑 밀키트</t>
-        </is>
-      </c>
-      <c r="G15" s="166" t="inlineStr">
-        <is>
-          <t>240,000원 (12건)</t>
-        </is>
-      </c>
-      <c r="H15" s="166" t="inlineStr">
-        <is>
-          <t>0원 (0건)</t>
-        </is>
-      </c>
-      <c r="I15" s="167" t="inlineStr">
-        <is>
-          <t>-240,000원 (-12건)</t>
-        </is>
-      </c>
-      <c r="J15" s="165" t="inlineStr">
-        <is>
-          <t>7월에 12건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="164" t="inlineStr">
-        <is>
-          <t>상품 매출 역전</t>
-        </is>
-      </c>
-      <c r="C16" s="164" t="inlineStr">
-        <is>
-          <t>온누리마켓</t>
-        </is>
-      </c>
-      <c r="D16" s="165" t="inlineStr">
-        <is>
-          <t>더모닝</t>
-        </is>
-      </c>
-      <c r="E16" s="164" t="inlineStr">
-        <is>
-          <t>655-09-02685</t>
-        </is>
-      </c>
-      <c r="F16" s="165" t="inlineStr">
-        <is>
-          <t>더모닝 닭 볶음탕 닭볶음탕 400g 4인분 캠핑 밀키트</t>
-        </is>
-      </c>
-      <c r="G16" s="166" t="inlineStr">
-        <is>
-          <t>54,000원 (3건)</t>
-        </is>
-      </c>
-      <c r="H16" s="166" t="inlineStr">
-        <is>
-          <t>0원 (0건)</t>
-        </is>
-      </c>
-      <c r="I16" s="167" t="inlineStr">
-        <is>
-          <t>-54,000원 (-3건)</t>
-        </is>
-      </c>
-      <c r="J16" s="165" t="inlineStr">
-        <is>
-          <t>7월에 3건 판매되었으나 8월 누적 로우데이터에서 0원으로 취합되어 8월 순수 실적 음수 발생</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="157" t="inlineStr">
-        <is>
-          <t>3. 업체별 쿠폰 한도(800만원) 소진율 상위 Top 10 업체 모니터링</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="158" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C20" s="158" t="inlineStr">
-        <is>
-          <t>사업자명</t>
-        </is>
-      </c>
-      <c r="D20" s="158" t="inlineStr">
-        <is>
-          <t>사업자번호</t>
-        </is>
-      </c>
-      <c r="E20" s="158" t="inlineStr">
-        <is>
-          <t>참여 유통사</t>
-        </is>
-      </c>
-      <c r="F20" s="158" t="inlineStr">
-        <is>
-          <t>누적 매출액</t>
-        </is>
-      </c>
-      <c r="G20" s="158" t="inlineStr">
-        <is>
-          <t>누적 쿠폰사용액</t>
-        </is>
-      </c>
-      <c r="H20" s="158" t="inlineStr">
-        <is>
-          <t>한도(800만원) 소진율</t>
-        </is>
-      </c>
-      <c r="I20" s="158" t="inlineStr">
-        <is>
-          <t>잔여 한도액</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="169" t="inlineStr">
-        <is>
-          <t>농부들</t>
-        </is>
-      </c>
-      <c r="D21" s="168" t="inlineStr">
-        <is>
-          <t>579-90-00021</t>
-        </is>
-      </c>
-      <c r="E21" s="168" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-      <c r="F21" s="170" t="n">
-        <v>53342360</v>
-      </c>
-      <c r="G21" s="171" t="n">
-        <v>6140240</v>
-      </c>
-      <c r="H21" s="172" t="inlineStr">
-        <is>
-          <t>76.8%</t>
-        </is>
-      </c>
-      <c r="I21" s="170" t="n">
-        <v>1859760</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인(주)자연푸드</t>
-        </is>
-      </c>
-      <c r="D22" s="168" t="inlineStr">
-        <is>
-          <t>412-81-50546</t>
-        </is>
-      </c>
-      <c r="E22" s="168" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-      <c r="F22" s="170" t="n">
-        <v>55214000</v>
-      </c>
-      <c r="G22" s="171" t="n">
-        <v>5847700</v>
-      </c>
-      <c r="H22" s="172" t="inlineStr">
-        <is>
-          <t>73.1%</t>
-        </is>
-      </c>
-      <c r="I22" s="170" t="n">
-        <v>2152300</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="168" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="169" t="inlineStr">
-        <is>
-          <t>팜앤유</t>
-        </is>
-      </c>
-      <c r="D23" s="168" t="inlineStr">
-        <is>
-          <t>477-93-01384</t>
-        </is>
-      </c>
-      <c r="E23" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="F23" s="170" t="n">
-        <v>41243100</v>
-      </c>
-      <c r="G23" s="171" t="n">
-        <v>5728100</v>
-      </c>
-      <c r="H23" s="172" t="inlineStr">
-        <is>
-          <t>71.6%</t>
-        </is>
-      </c>
-      <c r="I23" s="170" t="n">
-        <v>2271900</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="168" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="169" t="inlineStr">
-        <is>
-          <t>(주)다채몰</t>
-        </is>
-      </c>
-      <c r="D24" s="168" t="inlineStr">
-        <is>
-          <t>114-86-65039</t>
-        </is>
-      </c>
-      <c r="E24" s="168" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-      <c r="F24" s="170" t="n">
-        <v>39871200</v>
-      </c>
-      <c r="G24" s="171" t="n">
-        <v>5268240</v>
-      </c>
-      <c r="H24" s="159" t="inlineStr">
-        <is>
-          <t>65.9%</t>
-        </is>
-      </c>
-      <c r="I24" s="170" t="n">
-        <v>2731760</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="168" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="169" t="inlineStr">
-        <is>
-          <t>해남농협</t>
-        </is>
-      </c>
-      <c r="D25" s="168" t="inlineStr">
-        <is>
-          <t>323-88-00158</t>
-        </is>
-      </c>
-      <c r="E25" s="168" t="inlineStr">
-        <is>
-          <t>롯데ON</t>
-        </is>
-      </c>
-      <c r="F25" s="170" t="n">
-        <v>45120000</v>
-      </c>
-      <c r="G25" s="171" t="n">
-        <v>5136630</v>
-      </c>
-      <c r="H25" s="159" t="inlineStr">
-        <is>
-          <t>64.2%</t>
-        </is>
-      </c>
-      <c r="I25" s="170" t="n">
-        <v>2863370</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="168" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인 주식회사 드림마이스터</t>
-        </is>
-      </c>
-      <c r="D26" s="168" t="inlineStr">
-        <is>
-          <t>485-88-00795</t>
-        </is>
-      </c>
-      <c r="E26" s="168" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-      <c r="F26" s="170" t="n">
-        <v>36240000</v>
-      </c>
-      <c r="G26" s="171" t="n">
-        <v>5105280</v>
-      </c>
-      <c r="H26" s="159" t="inlineStr">
-        <is>
-          <t>63.8%</t>
-        </is>
-      </c>
-      <c r="I26" s="170" t="n">
-        <v>2894720</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="168" t="n">
-        <v>7</v>
-      </c>
-      <c r="C27" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인 철원이곡 주식회사</t>
-        </is>
-      </c>
-      <c r="D27" s="168" t="inlineStr">
-        <is>
-          <t>127-81-93991</t>
-        </is>
-      </c>
-      <c r="E27" s="168" t="inlineStr">
-        <is>
-          <t>농가살리기</t>
-        </is>
-      </c>
-      <c r="F27" s="170" t="n">
-        <v>34500000</v>
-      </c>
-      <c r="G27" s="171" t="n">
-        <v>5097728</v>
-      </c>
-      <c r="H27" s="159" t="inlineStr">
-        <is>
-          <t>63.7%</t>
-        </is>
-      </c>
-      <c r="I27" s="170" t="n">
-        <v>2902272</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="168" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" s="169" t="inlineStr">
-        <is>
-          <t>해주농협통합</t>
-        </is>
-      </c>
-      <c r="D28" s="168" t="inlineStr">
-        <is>
-          <t>126-82-11620</t>
-        </is>
-      </c>
-      <c r="E28" s="168" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-      <c r="F28" s="170" t="n">
-        <v>48900000</v>
-      </c>
-      <c r="G28" s="171" t="n">
-        <v>5085890</v>
-      </c>
-      <c r="H28" s="159" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="I28" s="170" t="n">
-        <v>2914110</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="168" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" s="169" t="inlineStr">
-        <is>
-          <t>두원식품(주)</t>
-        </is>
-      </c>
-      <c r="D29" s="168" t="inlineStr">
-        <is>
-          <t>606-81-52718</t>
-        </is>
-      </c>
-      <c r="E29" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="F29" s="170" t="n">
-        <v>55053800</v>
-      </c>
-      <c r="G29" s="171" t="n">
-        <v>5062400</v>
-      </c>
-      <c r="H29" s="159" t="inlineStr">
-        <is>
-          <t>63.3%</t>
-        </is>
-      </c>
-      <c r="I29" s="170" t="n">
-        <v>2937600</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="168" t="n">
-        <v>10</v>
-      </c>
-      <c r="C30" s="169" t="inlineStr">
-        <is>
-          <t>청양농협</t>
-        </is>
-      </c>
-      <c r="D30" s="168" t="inlineStr">
-        <is>
-          <t>499-51-00634</t>
-        </is>
-      </c>
-      <c r="E30" s="168" t="inlineStr">
-        <is>
-          <t>롯데ON</t>
-        </is>
-      </c>
-      <c r="F30" s="170" t="n">
-        <v>38100000</v>
-      </c>
-      <c r="G30" s="171" t="n">
-        <v>5049440</v>
-      </c>
-      <c r="H30" s="159" t="inlineStr">
-        <is>
-          <t>63.1%</t>
-        </is>
-      </c>
-      <c r="I30" s="170" t="n">
-        <v>2950560</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="157" t="inlineStr">
-        <is>
-          <t>4. 농가·유통사 품목분류 자의적 변경 이상건 전수 내역 (총 38건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="158" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C34" s="158" t="inlineStr">
-        <is>
-          <t>유통사</t>
-        </is>
-      </c>
-      <c r="D34" s="158" t="inlineStr">
-        <is>
-          <t>사업자명</t>
-        </is>
-      </c>
-      <c r="E34" s="158" t="inlineStr">
-        <is>
-          <t>사업자번호</t>
-        </is>
-      </c>
-      <c r="F34" s="158" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="G34" s="158" t="inlineStr">
-        <is>
-          <t>7월 분류</t>
-        </is>
-      </c>
-      <c r="H34" s="158" t="inlineStr">
-        <is>
-          <t>8월 변경분류</t>
-        </is>
-      </c>
-      <c r="I34" s="158" t="inlineStr">
-        <is>
-          <t>7월 매출액</t>
-        </is>
-      </c>
-      <c r="J34" s="158" t="inlineStr">
-        <is>
-          <t>8월 누적매출액</t>
-        </is>
-      </c>
-      <c r="K34" s="158" t="inlineStr">
-        <is>
-          <t>8월 순수매출액</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="168" t="inlineStr">
-        <is>
-          <t>롯데ON</t>
-        </is>
-      </c>
-      <c r="D35" s="169" t="inlineStr">
-        <is>
-          <t>주식회사 태범프레시</t>
-        </is>
-      </c>
-      <c r="E35" s="168" t="inlineStr">
-        <is>
-          <t>832-86-02035</t>
-        </is>
-      </c>
-      <c r="F35" s="169" t="inlineStr">
-        <is>
-          <t>[홍익상회] 춘천닭갈비 500g x 3팩 국내산닭고기 양념 순살</t>
-        </is>
-      </c>
-      <c r="G35" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H35" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I35" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="168" t="inlineStr">
-        <is>
-          <t>롯데ON</t>
-        </is>
-      </c>
-      <c r="D36" s="169" t="inlineStr">
-        <is>
-          <t>주식회사 태범프레시</t>
-        </is>
-      </c>
-      <c r="E36" s="168" t="inlineStr">
-        <is>
-          <t>832-86-02035</t>
-        </is>
-      </c>
-      <c r="F36" s="169" t="inlineStr">
-        <is>
-          <t>[홍익상회] 춘천 홍익닭갈비 500g x 3팩 국내산 닭고기 양념 순살</t>
-        </is>
-      </c>
-      <c r="G36" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H36" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I36" s="170" t="n">
-        <v>2552440</v>
-      </c>
-      <c r="J36" s="170" t="n">
-        <v>2552440</v>
-      </c>
-      <c r="K36" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="168" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" s="168" t="inlineStr">
-        <is>
-          <t>롯데ON</t>
-        </is>
-      </c>
-      <c r="D37" s="169" t="inlineStr">
-        <is>
-          <t>신선식품</t>
-        </is>
-      </c>
-      <c r="E37" s="168" t="inlineStr">
-        <is>
-          <t>131-35-96215</t>
-        </is>
-      </c>
-      <c r="F37" s="169" t="inlineStr">
-        <is>
-          <t>[온누리7%혜택]고소한 국산 볶은참깨 200g</t>
-        </is>
-      </c>
-      <c r="G37" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H37" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I37" s="170" t="n">
-        <v>25600</v>
-      </c>
-      <c r="J37" s="170" t="n">
-        <v>204800</v>
-      </c>
-      <c r="K37" s="174" t="n">
-        <v>179200</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="168" t="n">
-        <v>4</v>
-      </c>
-      <c r="C38" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D38" s="169" t="inlineStr">
-        <is>
-          <t>두원식품(주)</t>
-        </is>
-      </c>
-      <c r="E38" s="168" t="inlineStr">
-        <is>
-          <t>606-81-52718</t>
-        </is>
-      </c>
-      <c r="F38" s="169" t="inlineStr">
-        <is>
-          <t>(신선집중) 국내산 한돈 프리미엄 대패 삼겹살 1.2kg</t>
-        </is>
-      </c>
-      <c r="G38" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H38" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I38" s="170" t="n">
-        <v>51796200</v>
-      </c>
-      <c r="J38" s="170" t="n">
-        <v>55053800</v>
-      </c>
-      <c r="K38" s="174" t="n">
-        <v>3257600</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="168" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D39" s="169" t="inlineStr">
-        <is>
-          <t>다모아영농조합법인</t>
-        </is>
-      </c>
-      <c r="E39" s="168" t="inlineStr">
-        <is>
-          <t>613-81-60803</t>
-        </is>
-      </c>
-      <c r="F39" s="169" t="inlineStr">
-        <is>
-          <t>농협 공동선별 햇 남해 통마늘 3kg(상) 실중량 지리적표시품</t>
-        </is>
-      </c>
-      <c r="G39" s="159" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="H39" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I39" s="170" t="n">
-        <v>73800</v>
-      </c>
-      <c r="J39" s="170" t="n">
-        <v>701100</v>
-      </c>
-      <c r="K39" s="174" t="n">
-        <v>627300</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="168" t="n">
-        <v>6</v>
-      </c>
-      <c r="C40" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D40" s="169" t="inlineStr">
-        <is>
-          <t>청정태안식품</t>
-        </is>
-      </c>
-      <c r="E40" s="168" t="inlineStr">
-        <is>
-          <t>316-01-24597</t>
-        </is>
-      </c>
-      <c r="F40" s="169" t="inlineStr">
-        <is>
-          <t>김명월 검정콩 청국장가루 1kg(500g2통)</t>
-        </is>
-      </c>
-      <c r="G40" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H40" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I40" s="170" t="n">
-        <v>74000</v>
-      </c>
-      <c r="J40" s="170" t="n">
-        <v>222000</v>
-      </c>
-      <c r="K40" s="174" t="n">
-        <v>148000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="168" t="n">
-        <v>7</v>
-      </c>
-      <c r="C41" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D41" s="169" t="inlineStr">
-        <is>
-          <t>청정태안식품</t>
-        </is>
-      </c>
-      <c r="E41" s="168" t="inlineStr">
-        <is>
-          <t>316-01-24597</t>
-        </is>
-      </c>
-      <c r="F41" s="169" t="inlineStr">
-        <is>
-          <t>김명월 검정콩 청국장가루 1kg(500g2통)</t>
-        </is>
-      </c>
-      <c r="G41" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H41" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I41" s="170" t="n">
-        <v>74000</v>
-      </c>
-      <c r="J41" s="170" t="n">
-        <v>259000</v>
-      </c>
-      <c r="K41" s="174" t="n">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="168" t="n">
-        <v>8</v>
-      </c>
-      <c r="C42" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D42" s="169" t="inlineStr">
-        <is>
-          <t>형지표고버섯</t>
-        </is>
-      </c>
-      <c r="E42" s="168" t="inlineStr">
-        <is>
-          <t>290-94-00335</t>
-        </is>
-      </c>
-      <c r="F42" s="169" t="inlineStr">
-        <is>
-          <t>형지표고버섯 흑화고 상황버섯 혼합2호 표고 버섯 선물세트</t>
-        </is>
-      </c>
-      <c r="G42" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H42" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I42" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="168" t="n">
-        <v>9</v>
-      </c>
-      <c r="C43" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D43" s="169" t="inlineStr">
-        <is>
-          <t>농부플러스</t>
-        </is>
-      </c>
-      <c r="E43" s="168" t="inlineStr">
-        <is>
-          <t>571-81-00383</t>
-        </is>
-      </c>
-      <c r="F43" s="169" t="inlineStr">
-        <is>
-          <t>국산 볶음참깨 햇 참깨 볶은참깨 토종 통깨 200g</t>
-        </is>
-      </c>
-      <c r="G43" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H43" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I43" s="170" t="n">
-        <v>360800</v>
-      </c>
-      <c r="J43" s="170" t="n">
-        <v>1098800</v>
-      </c>
-      <c r="K43" s="174" t="n">
-        <v>738000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="168" t="n">
-        <v>10</v>
-      </c>
-      <c r="C44" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D44" s="169" t="inlineStr">
-        <is>
-          <t>농부플러스</t>
-        </is>
-      </c>
-      <c r="E44" s="168" t="inlineStr">
-        <is>
-          <t>571-81-00383</t>
-        </is>
-      </c>
-      <c r="F44" s="169" t="inlineStr">
-        <is>
-          <t>국산 볶음참깨 햇 참깨 볶은참깨 토종 통깨 150g</t>
-        </is>
-      </c>
-      <c r="G44" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H44" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I44" s="170" t="n">
-        <v>13900</v>
-      </c>
-      <c r="J44" s="170" t="n">
-        <v>42700</v>
-      </c>
-      <c r="K44" s="174" t="n">
-        <v>28800</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="168" t="n">
-        <v>11</v>
-      </c>
-      <c r="C45" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D45" s="169" t="inlineStr">
-        <is>
-          <t>듬뿍곡간</t>
-        </is>
-      </c>
-      <c r="E45" s="168" t="inlineStr">
-        <is>
-          <t>181-02-01980</t>
-        </is>
-      </c>
-      <c r="F45" s="169" t="inlineStr">
-        <is>
-          <t>듬뿍곡간 국내산 볶은 귀리 / 아침식사대용 간식</t>
-        </is>
-      </c>
-      <c r="G45" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H45" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I45" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="168" t="n">
-        <v>12</v>
-      </c>
-      <c r="C46" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D46" s="169" t="inlineStr">
-        <is>
-          <t>듬뿍곡간</t>
-        </is>
-      </c>
-      <c r="E46" s="168" t="inlineStr">
-        <is>
-          <t>181-02-01980</t>
-        </is>
-      </c>
-      <c r="F46" s="169" t="inlineStr">
-        <is>
-          <t>듬뿍곡간 국내산 쑥미숫가루 / 선식 식사대용 간식 500g</t>
-        </is>
-      </c>
-      <c r="G46" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H46" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I46" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="170" t="n">
-        <v>23800</v>
-      </c>
-      <c r="K46" s="174" t="n">
-        <v>23800</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="168" t="n">
-        <v>13</v>
-      </c>
-      <c r="C47" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D47" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인(주)가남농원</t>
-        </is>
-      </c>
-      <c r="E47" s="168" t="inlineStr">
-        <is>
-          <t>416-81-59229</t>
-        </is>
-      </c>
-      <c r="F47" s="169" t="inlineStr">
-        <is>
-          <t>김승희매실가 신지식 농업인이 만든 매실절임 1kg</t>
-        </is>
-      </c>
-      <c r="G47" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H47" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I47" s="170" t="n">
-        <v>66000</v>
-      </c>
-      <c r="J47" s="170" t="n">
-        <v>165000</v>
-      </c>
-      <c r="K47" s="174" t="n">
-        <v>99000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="168" t="n">
-        <v>14</v>
-      </c>
-      <c r="C48" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D48" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인(주)가남농원</t>
-        </is>
-      </c>
-      <c r="E48" s="168" t="inlineStr">
-        <is>
-          <t>416-81-59229</t>
-        </is>
-      </c>
-      <c r="F48" s="169" t="inlineStr">
-        <is>
-          <t>천기누설 매실 장인이만든 매실고 (농축액) 150g</t>
-        </is>
-      </c>
-      <c r="G48" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H48" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I48" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="168" t="n">
-        <v>15</v>
-      </c>
-      <c r="C49" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D49" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인(주)가남농원</t>
-        </is>
-      </c>
-      <c r="E49" s="168" t="inlineStr">
-        <is>
-          <t>416-81-59229</t>
-        </is>
-      </c>
-      <c r="F49" s="169" t="inlineStr">
-        <is>
-          <t>천기누설 매실 장인이만든 매실고 (농축액) 150g</t>
-        </is>
-      </c>
-      <c r="G49" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H49" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I49" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="170" t="n">
-        <v>43000</v>
-      </c>
-      <c r="K49" s="174" t="n">
-        <v>43000</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="168" t="n">
-        <v>16</v>
-      </c>
-      <c r="C50" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D50" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인 팜팜(주)</t>
-        </is>
-      </c>
-      <c r="E50" s="168" t="inlineStr">
-        <is>
-          <t>177-81-00798</t>
-        </is>
-      </c>
-      <c r="F50" s="169" t="inlineStr">
-        <is>
-          <t>(품질보증) 산지직송 정품과 완숙토마토 5KG 당일수확 유럽종</t>
-        </is>
-      </c>
-      <c r="G50" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H50" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I50" s="170" t="n">
-        <v>694600</v>
-      </c>
-      <c r="J50" s="170" t="n">
-        <v>5967100</v>
-      </c>
-      <c r="K50" s="174" t="n">
-        <v>5272500</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="168" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D51" s="169" t="inlineStr">
-        <is>
-          <t>농업회사법인주식회사 늘해랑</t>
-        </is>
-      </c>
-      <c r="E51" s="168" t="inlineStr">
-        <is>
-          <t>756-87-00841</t>
-        </is>
-      </c>
-      <c r="F51" s="169" t="inlineStr">
-        <is>
-          <t>조은해남 고구마 못난이 10kg (꿀호박 랜덤발송)</t>
-        </is>
-      </c>
-      <c r="G51" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H51" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I51" s="170" t="n">
-        <v>371800</v>
-      </c>
-      <c r="J51" s="170" t="n">
-        <v>2827100</v>
-      </c>
-      <c r="K51" s="174" t="n">
-        <v>2455300</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="168" t="n">
-        <v>18</v>
-      </c>
-      <c r="C52" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D52" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E52" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F52" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
-        </is>
-      </c>
-      <c r="G52" s="159" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="H52" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I52" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="168" t="n">
-        <v>19</v>
-      </c>
-      <c r="C53" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D53" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E53" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F53" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
-        </is>
-      </c>
-      <c r="G53" s="159" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="H53" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I53" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="170" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K53" s="174" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="168" t="n">
-        <v>20</v>
-      </c>
-      <c r="C54" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D54" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E54" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F54" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산100% 도토리묵 묵사발 세트</t>
-        </is>
-      </c>
-      <c r="G54" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H54" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I54" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="168" t="n">
-        <v>21</v>
-      </c>
-      <c r="C55" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D55" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E55" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F55" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 명인 국산 콩물 우묵채 (2인분)</t>
-        </is>
-      </c>
-      <c r="G55" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H55" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I55" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="168" t="n">
-        <v>22</v>
-      </c>
-      <c r="C56" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D56" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E56" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F56" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
-        </is>
-      </c>
-      <c r="G56" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H56" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I56" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="168" t="n">
-        <v>23</v>
-      </c>
-      <c r="C57" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D57" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E57" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F57" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
-        </is>
-      </c>
-      <c r="G57" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H57" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I57" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="170" t="n">
-        <v>240000</v>
-      </c>
-      <c r="K57" s="174" t="n">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="168" t="n">
-        <v>24</v>
-      </c>
-      <c r="C58" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D58" s="169" t="inlineStr">
-        <is>
-          <t>그린몬스터즈</t>
-        </is>
-      </c>
-      <c r="E58" s="168" t="inlineStr">
-        <is>
-          <t>883-95-01472</t>
-        </is>
-      </c>
-      <c r="F58" s="169" t="inlineStr">
-        <is>
-          <t>당일수확발송 그린몬스터즈 프리미엄 미니오이 1.5kg 농장직거래 여름작기 첫수확 특가할인행사</t>
-        </is>
-      </c>
-      <c r="G58" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H58" s="173" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="I58" s="170" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J58" s="170" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K58" s="174" t="n">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="168" t="n">
-        <v>25</v>
-      </c>
-      <c r="C59" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D59" s="169" t="inlineStr">
-        <is>
-          <t>어이딸부각</t>
-        </is>
-      </c>
-      <c r="E59" s="168" t="inlineStr">
-        <is>
-          <t>142-33-00898</t>
-        </is>
-      </c>
-      <c r="F59" s="169" t="inlineStr">
-        <is>
-          <t>고추크런치 70g 고추부각 튀각 찹쌀 수제 비건</t>
-        </is>
-      </c>
-      <c r="G59" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H59" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I59" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="168" t="n">
-        <v>26</v>
-      </c>
-      <c r="C60" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D60" s="169" t="inlineStr">
-        <is>
-          <t>어이딸부각</t>
-        </is>
-      </c>
-      <c r="E60" s="168" t="inlineStr">
-        <is>
-          <t>142-33-00898</t>
-        </is>
-      </c>
-      <c r="F60" s="169" t="inlineStr">
-        <is>
-          <t>어이딸 김부각 선물세트 소 5개입 찹쌀 수제 비건 글루텐프리 저당</t>
-        </is>
-      </c>
-      <c r="G60" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H60" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I60" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="170" t="n">
-        <v>690000</v>
-      </c>
-      <c r="K60" s="174" t="n">
-        <v>690000</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="168" t="n">
-        <v>27</v>
-      </c>
-      <c r="C61" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D61" s="169" t="inlineStr">
-        <is>
-          <t>어이딸부각</t>
-        </is>
-      </c>
-      <c r="E61" s="168" t="inlineStr">
-        <is>
-          <t>142-33-00898</t>
-        </is>
-      </c>
-      <c r="F61" s="169" t="inlineStr">
-        <is>
-          <t>어이딸 김부각 선물세트 중 8개입 찹쌀 수제 비건 글루텐프리 저당</t>
-        </is>
-      </c>
-      <c r="G61" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H61" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I61" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="168" t="n">
-        <v>28</v>
-      </c>
-      <c r="C62" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D62" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E62" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F62" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
-        </is>
-      </c>
-      <c r="G62" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H62" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I62" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="168" t="n">
-        <v>29</v>
-      </c>
-      <c r="C63" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D63" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E63" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F63" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 100% 도토리묵 400g 2인분 x 1팩</t>
-        </is>
-      </c>
-      <c r="G63" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H63" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I63" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="170" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K63" s="174" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="168" t="n">
-        <v>30</v>
-      </c>
-      <c r="C64" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D64" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E64" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F64" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
-        </is>
-      </c>
-      <c r="G64" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H64" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I64" s="170" t="n">
-        <v>240000</v>
-      </c>
-      <c r="J64" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="174" t="n">
-        <v>-240000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="168" t="n">
-        <v>31</v>
-      </c>
-      <c r="C65" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D65" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E65" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F65" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 콩물 콩가루 90g 1인분 x 5팩 물만타면 콩국수</t>
-        </is>
-      </c>
-      <c r="G65" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H65" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I65" s="170" t="n">
-        <v>240000</v>
-      </c>
-      <c r="J65" s="170" t="n">
-        <v>240000</v>
-      </c>
-      <c r="K65" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="168" t="n">
-        <v>32</v>
-      </c>
-      <c r="C66" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D66" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E66" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F66" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 콩물 콩가루 400g 4인분 물만타면 콩국수</t>
-        </is>
-      </c>
-      <c r="G66" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H66" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I66" s="170" t="n">
-        <v>54000</v>
-      </c>
-      <c r="J66" s="170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="174" t="n">
-        <v>-54000</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="168" t="n">
-        <v>33</v>
-      </c>
-      <c r="C67" s="168" t="inlineStr">
-        <is>
-          <t>지마켓</t>
-        </is>
-      </c>
-      <c r="D67" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵</t>
-        </is>
-      </c>
-      <c r="E67" s="168" t="inlineStr">
-        <is>
-          <t>615-14-93195</t>
-        </is>
-      </c>
-      <c r="F67" s="169" t="inlineStr">
-        <is>
-          <t>초림단지묵 국산 콩물 콩가루 400g 4인분 물만타면 콩국수</t>
-        </is>
-      </c>
-      <c r="G67" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H67" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I67" s="170" t="n">
-        <v>54000</v>
-      </c>
-      <c r="J67" s="170" t="n">
-        <v>54000</v>
-      </c>
-      <c r="K67" s="174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="168" t="n">
-        <v>34</v>
-      </c>
-      <c r="C68" s="168" t="inlineStr">
-        <is>
-          <t>오아시스</t>
-        </is>
-      </c>
-      <c r="D68" s="169" t="inlineStr">
-        <is>
-          <t>케이에프지</t>
-        </is>
-      </c>
-      <c r="E68" s="168" t="inlineStr">
-        <is>
-          <t>120-86-08936</t>
-        </is>
-      </c>
-      <c r="F68" s="169" t="inlineStr">
-        <is>
-          <t>한돈 제육볶음 (650g X 1개)</t>
-        </is>
-      </c>
-      <c r="G68" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H68" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I68" s="170" t="n">
-        <v>20305100</v>
-      </c>
-      <c r="J68" s="170" t="n">
-        <v>46426900</v>
-      </c>
-      <c r="K68" s="174" t="n">
-        <v>26121800</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="168" t="n">
-        <v>35</v>
-      </c>
-      <c r="C69" s="168" t="inlineStr">
-        <is>
-          <t>오아시스</t>
-        </is>
-      </c>
-      <c r="D69" s="169" t="inlineStr">
-        <is>
-          <t>케이에프지</t>
-        </is>
-      </c>
-      <c r="E69" s="168" t="inlineStr">
-        <is>
-          <t>120-86-08936</t>
-        </is>
-      </c>
-      <c r="F69" s="169" t="inlineStr">
-        <is>
-          <t>한돈 칼집 양념구이 (650g X 1개)</t>
-        </is>
-      </c>
-      <c r="G69" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H69" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I69" s="170" t="n">
-        <v>16019900</v>
-      </c>
-      <c r="J69" s="170" t="n">
-        <v>30197000</v>
-      </c>
-      <c r="K69" s="174" t="n">
-        <v>14177100</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="168" t="n">
-        <v>36</v>
-      </c>
-      <c r="C70" s="168" t="inlineStr">
-        <is>
-          <t>오아시스</t>
-        </is>
-      </c>
-      <c r="D70" s="169" t="inlineStr">
-        <is>
-          <t>케이에프지</t>
-        </is>
-      </c>
-      <c r="E70" s="168" t="inlineStr">
-        <is>
-          <t>120-86-08936</t>
-        </is>
-      </c>
-      <c r="F70" s="169" t="inlineStr">
-        <is>
-          <t>한돈 성북동식 돼지불백 (650g X 1개)</t>
-        </is>
-      </c>
-      <c r="G70" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H70" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I70" s="170" t="n">
-        <v>10928700</v>
-      </c>
-      <c r="J70" s="170" t="n">
-        <v>21744400</v>
-      </c>
-      <c r="K70" s="174" t="n">
-        <v>10815700</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="168" t="n">
-        <v>37</v>
-      </c>
-      <c r="C71" s="168" t="inlineStr">
-        <is>
-          <t>오아시스</t>
-        </is>
-      </c>
-      <c r="D71" s="169" t="inlineStr">
-        <is>
-          <t>케이에프지</t>
-        </is>
-      </c>
-      <c r="E71" s="168" t="inlineStr">
-        <is>
-          <t>120-86-08936</t>
-        </is>
-      </c>
-      <c r="F71" s="169" t="inlineStr">
-        <is>
-          <t>서울식 한우 불고기 밀키트 (800g X 1개)</t>
-        </is>
-      </c>
-      <c r="G71" s="159" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="H71" s="173" t="inlineStr">
-        <is>
-          <t>축산물</t>
-        </is>
-      </c>
-      <c r="I71" s="170" t="n">
-        <v>6922200</v>
-      </c>
-      <c r="J71" s="170" t="n">
-        <v>15422600</v>
-      </c>
-      <c r="K71" s="174" t="n">
-        <v>8500400</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="168" t="n">
-        <v>38</v>
-      </c>
-      <c r="C72" s="168" t="inlineStr">
-        <is>
-          <t>오아시스</t>
-        </is>
-      </c>
-      <c r="D72" s="169" t="inlineStr">
-        <is>
-          <t>해담는집</t>
-        </is>
-      </c>
-      <c r="E72" s="168" t="inlineStr">
-        <is>
-          <t>745-96-00315</t>
-        </is>
-      </c>
-      <c r="F72" s="169" t="inlineStr">
-        <is>
-          <t>해담는집 유기농 고춧가루 500g/200g(순한맛/보통맛/매운맛)</t>
-        </is>
-      </c>
-      <c r="G72" s="159" t="inlineStr">
-        <is>
-          <t>농산물</t>
-        </is>
-      </c>
-      <c r="H72" s="173" t="inlineStr">
-        <is>
-          <t>가공식품</t>
-        </is>
-      </c>
-      <c r="I72" s="170" t="n">
-        <v>208400</v>
-      </c>
-      <c r="J72" s="170" t="n">
-        <v>434900</v>
-      </c>
-      <c r="K72" s="174" t="n">
-        <v>226500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
+++ b/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
@@ -8,19 +8,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="※ 이상치 및 규정검토" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="농산물업체" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①농산물raw" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유기농업체" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②유기농raw" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="※ 피벗_교차검증" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="농산물업체" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①농산물raw" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유기농업체" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②유기농raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'농산물업체'!$A$2:$J$287</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'①농산물raw'!$A$5:$K$1454</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'①농산물raw'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'①농산물raw'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'②유기농raw'!$A$5:$I$96</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'②유기농raw'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'②유기농raw'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'농산물업체'!$A$2:$J$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'①농산물raw'!$A$5:$K$1454</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'①농산물raw'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'①농산물raw'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'②유기농raw'!$A$5:$I$96</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'②유기농raw'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'②유기농raw'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="###\-##\-#####"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -256,6 +257,12 @@
       <b val="1"/>
       <color rgb="00B91C1C"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="23">
@@ -672,7 +679,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1151,6 +1158,14 @@
     </xf>
     <xf numFmtId="3" fontId="27" fillId="22" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="27" fillId="21" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -11195,6 +11210,751 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="21" min="2" max="2"/>
+    <col width="16" customWidth="1" style="21" min="3" max="3"/>
+    <col width="16" customWidth="1" style="21" min="4" max="4"/>
+    <col width="16" customWidth="1" style="21" min="5" max="5"/>
+    <col width="16" customWidth="1" style="21" min="6" max="6"/>
+    <col width="16" customWidth="1" style="21" min="7" max="7"/>
+    <col width="16" customWidth="1" style="21" min="8" max="8"/>
+    <col width="16" customWidth="1" style="21" min="9" max="9"/>
+    <col width="16" customWidth="1" style="21" min="10" max="10"/>
+    <col width="16" customWidth="1" style="21" min="11" max="11"/>
+    <col width="16" customWidth="1" style="21" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="175" t="inlineStr">
+        <is>
+          <t>로우데이터 기반 수동 피벗(Pivot Table) 집계 vs 분석 시트 전수 대조 검증표</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="176" t="inlineStr">
+        <is>
+          <t>※ 로우데이터 1,651개 행을 피벗 집계하여 7월을 차감한 수치와 '분석' 시트의 SUMIFS 공식 수치 간 1원/1건 단위 전수 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="157" t="inlineStr">
+        <is>
+          <t>1. [농산물 온라인 마케터] 유통사별 피벗 집계 vs 분석 시트 대조 (8월 순수 실적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="158" t="inlineStr">
+        <is>
+          <t>유통사명</t>
+        </is>
+      </c>
+      <c r="C6" s="158" t="inlineStr">
+        <is>
+          <t>피벗 매출액(원)</t>
+        </is>
+      </c>
+      <c r="D6" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 매출액</t>
+        </is>
+      </c>
+      <c r="E6" s="158" t="inlineStr">
+        <is>
+          <t>매출 오차</t>
+        </is>
+      </c>
+      <c r="F6" s="158" t="inlineStr">
+        <is>
+          <t>피벗 판촉액(원)</t>
+        </is>
+      </c>
+      <c r="G6" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 판촉액</t>
+        </is>
+      </c>
+      <c r="H6" s="158" t="inlineStr">
+        <is>
+          <t>판촉액 오차</t>
+        </is>
+      </c>
+      <c r="I6" s="158" t="inlineStr">
+        <is>
+          <t>피벗 판매건수</t>
+        </is>
+      </c>
+      <c r="J6" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 건수</t>
+        </is>
+      </c>
+      <c r="K6" s="158" t="inlineStr">
+        <is>
+          <t>건수 오차</t>
+        </is>
+      </c>
+      <c r="L6" s="158" t="inlineStr">
+        <is>
+          <t>검증 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="C7" s="170" t="n">
+        <v>1753708870</v>
+      </c>
+      <c r="D7" s="170" t="n">
+        <v>1753708870</v>
+      </c>
+      <c r="E7" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="170" t="n">
+        <v>40427410</v>
+      </c>
+      <c r="G7" s="170" t="n">
+        <v>40427410</v>
+      </c>
+      <c r="H7" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="170" t="n">
+        <v>68547</v>
+      </c>
+      <c r="J7" s="170" t="n">
+        <v>68547</v>
+      </c>
+      <c r="K7" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="168" t="inlineStr">
+        <is>
+          <t>지마켓</t>
+        </is>
+      </c>
+      <c r="C8" s="170" t="n">
+        <v>578020340</v>
+      </c>
+      <c r="D8" s="170" t="n">
+        <v>578020340</v>
+      </c>
+      <c r="E8" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="170" t="n">
+        <v>30255530</v>
+      </c>
+      <c r="G8" s="170" t="n">
+        <v>30255530</v>
+      </c>
+      <c r="H8" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="170" t="n">
+        <v>29453</v>
+      </c>
+      <c r="J8" s="170" t="n">
+        <v>29453</v>
+      </c>
+      <c r="K8" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="168" t="inlineStr">
+        <is>
+          <t>롯데ON</t>
+        </is>
+      </c>
+      <c r="C9" s="170" t="n">
+        <v>82976410</v>
+      </c>
+      <c r="D9" s="170" t="n">
+        <v>82976410</v>
+      </c>
+      <c r="E9" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="170" t="n">
+        <v>12110560</v>
+      </c>
+      <c r="G9" s="170" t="n">
+        <v>12110560</v>
+      </c>
+      <c r="H9" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="170" t="n">
+        <v>2577</v>
+      </c>
+      <c r="J9" s="170" t="n">
+        <v>2577</v>
+      </c>
+      <c r="K9" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="168" t="inlineStr">
+        <is>
+          <t>온누리마켓</t>
+        </is>
+      </c>
+      <c r="C10" s="170" t="n">
+        <v>53636800</v>
+      </c>
+      <c r="D10" s="170" t="n">
+        <v>53636800</v>
+      </c>
+      <c r="E10" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="170" t="n">
+        <v>8399420</v>
+      </c>
+      <c r="G10" s="170" t="n">
+        <v>8399420</v>
+      </c>
+      <c r="H10" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="170" t="n">
+        <v>1804</v>
+      </c>
+      <c r="J10" s="170" t="n">
+        <v>1804</v>
+      </c>
+      <c r="K10" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="168" t="inlineStr">
+        <is>
+          <t>농가살리기</t>
+        </is>
+      </c>
+      <c r="C11" s="170" t="n">
+        <v>247036467</v>
+      </c>
+      <c r="D11" s="170" t="n">
+        <v>247036467</v>
+      </c>
+      <c r="E11" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="170" t="n">
+        <v>4112540</v>
+      </c>
+      <c r="G11" s="170" t="n">
+        <v>4112540</v>
+      </c>
+      <c r="H11" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="170" t="n">
+        <v>16004</v>
+      </c>
+      <c r="J11" s="170" t="n">
+        <v>16004</v>
+      </c>
+      <c r="K11" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="C12" s="170" t="n">
+        <v>575740180</v>
+      </c>
+      <c r="D12" s="170" t="n">
+        <v>575740180</v>
+      </c>
+      <c r="E12" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="170" t="n">
+        <v>7485204</v>
+      </c>
+      <c r="G12" s="170" t="n">
+        <v>7485204</v>
+      </c>
+      <c r="H12" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="170" t="n">
+        <v>130274</v>
+      </c>
+      <c r="J12" s="170" t="n">
+        <v>130274</v>
+      </c>
+      <c r="K12" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="159" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="C13" s="177" t="n">
+        <v>3291119067</v>
+      </c>
+      <c r="D13" s="177" t="n">
+        <v>3291119067</v>
+      </c>
+      <c r="E13" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="177" t="n">
+        <v>102790664</v>
+      </c>
+      <c r="G13" s="177" t="n">
+        <v>102790664</v>
+      </c>
+      <c r="H13" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="177" t="n">
+        <v>248659</v>
+      </c>
+      <c r="J13" s="177" t="n">
+        <v>248659</v>
+      </c>
+      <c r="K13" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="178" t="inlineStr">
+        <is>
+          <t>오차 0원 / 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="157" t="inlineStr">
+        <is>
+          <t>2. [유기농 기획전] 유통사별 피벗 집계 vs 분석 시트 대조 (8월 순수 실적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="158" t="inlineStr">
+        <is>
+          <t>유통사명</t>
+        </is>
+      </c>
+      <c r="C17" s="158" t="inlineStr">
+        <is>
+          <t>피벗 매출액(원)</t>
+        </is>
+      </c>
+      <c r="D17" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 매출액</t>
+        </is>
+      </c>
+      <c r="E17" s="158" t="inlineStr">
+        <is>
+          <t>매출 오차</t>
+        </is>
+      </c>
+      <c r="F17" s="158" t="inlineStr">
+        <is>
+          <t>피벗 판촉액(원)</t>
+        </is>
+      </c>
+      <c r="G17" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 판촉액</t>
+        </is>
+      </c>
+      <c r="H17" s="158" t="inlineStr">
+        <is>
+          <t>판촉액 오차</t>
+        </is>
+      </c>
+      <c r="I17" s="158" t="inlineStr">
+        <is>
+          <t>피벗 판매건수</t>
+        </is>
+      </c>
+      <c r="J17" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 건수</t>
+        </is>
+      </c>
+      <c r="K17" s="158" t="inlineStr">
+        <is>
+          <t>건수 오차</t>
+        </is>
+      </c>
+      <c r="L17" s="158" t="inlineStr">
+        <is>
+          <t>검증 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="168" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="C18" s="170" t="n">
+        <v>163153890</v>
+      </c>
+      <c r="D18" s="170" t="n">
+        <v>163153890</v>
+      </c>
+      <c r="E18" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="170" t="n">
+        <v>13894790</v>
+      </c>
+      <c r="G18" s="170" t="n">
+        <v>13894790</v>
+      </c>
+      <c r="H18" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="170" t="n">
+        <v>6420</v>
+      </c>
+      <c r="J18" s="170" t="n">
+        <v>6420</v>
+      </c>
+      <c r="K18" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="168" t="inlineStr">
+        <is>
+          <t>오아시스</t>
+        </is>
+      </c>
+      <c r="C19" s="170" t="n">
+        <v>643403790</v>
+      </c>
+      <c r="D19" s="170" t="n">
+        <v>643403790</v>
+      </c>
+      <c r="E19" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="170" t="n">
+        <v>10412848</v>
+      </c>
+      <c r="G19" s="170" t="n">
+        <v>10412848</v>
+      </c>
+      <c r="H19" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="170" t="n">
+        <v>146836</v>
+      </c>
+      <c r="J19" s="170" t="n">
+        <v>146836</v>
+      </c>
+      <c r="K19" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="159" t="inlineStr">
+        <is>
+          <t>총 계</t>
+        </is>
+      </c>
+      <c r="C20" s="177" t="n">
+        <v>806557680</v>
+      </c>
+      <c r="D20" s="177" t="n">
+        <v>806557680</v>
+      </c>
+      <c r="E20" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="177" t="n">
+        <v>24307638</v>
+      </c>
+      <c r="G20" s="177" t="n">
+        <v>24307638</v>
+      </c>
+      <c r="H20" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="177" t="n">
+        <v>153256</v>
+      </c>
+      <c r="J20" s="177" t="n">
+        <v>153256</v>
+      </c>
+      <c r="K20" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="178" t="inlineStr">
+        <is>
+          <t>오차 0원 / 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="157" t="inlineStr">
+        <is>
+          <t>3. 품목분류별 피벗 집계 vs 분석 시트 대조 (8월 순수 실적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="158" t="inlineStr">
+        <is>
+          <t>품목구분</t>
+        </is>
+      </c>
+      <c r="C24" s="158" t="inlineStr">
+        <is>
+          <t>농산물마케터 피벗매출</t>
+        </is>
+      </c>
+      <c r="D24" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 매출</t>
+        </is>
+      </c>
+      <c r="E24" s="158" t="inlineStr">
+        <is>
+          <t>오차</t>
+        </is>
+      </c>
+      <c r="F24" s="158" t="inlineStr">
+        <is>
+          <t>유기농 피벗매출</t>
+        </is>
+      </c>
+      <c r="G24" s="158" t="inlineStr">
+        <is>
+          <t>분석시트 매출</t>
+        </is>
+      </c>
+      <c r="H24" s="158" t="inlineStr">
+        <is>
+          <t>오차</t>
+        </is>
+      </c>
+      <c r="I24" s="158" t="inlineStr">
+        <is>
+          <t>합계 매출</t>
+        </is>
+      </c>
+      <c r="J24" s="158" t="inlineStr">
+        <is>
+          <t>검증 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="168" t="inlineStr">
+        <is>
+          <t>농산물</t>
+        </is>
+      </c>
+      <c r="C25" s="170" t="n">
+        <v>1430067731</v>
+      </c>
+      <c r="D25" s="170" t="n">
+        <v>1430067731</v>
+      </c>
+      <c r="E25" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="170" t="n">
+        <v>576101240</v>
+      </c>
+      <c r="G25" s="170" t="n">
+        <v>576101240</v>
+      </c>
+      <c r="H25" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="170" t="n">
+        <v>2006168971</v>
+      </c>
+      <c r="J25" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="168" t="inlineStr">
+        <is>
+          <t>축산물</t>
+        </is>
+      </c>
+      <c r="C26" s="170" t="n">
+        <v>421329860</v>
+      </c>
+      <c r="D26" s="170" t="n">
+        <v>421329860</v>
+      </c>
+      <c r="E26" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="170" t="n">
+        <v>4303100</v>
+      </c>
+      <c r="G26" s="170" t="n">
+        <v>4303100</v>
+      </c>
+      <c r="H26" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="170" t="n">
+        <v>425632960</v>
+      </c>
+      <c r="J26" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="168" t="inlineStr">
+        <is>
+          <t>가공식품</t>
+        </is>
+      </c>
+      <c r="C27" s="170" t="n">
+        <v>1439721476</v>
+      </c>
+      <c r="D27" s="170" t="n">
+        <v>1439721476</v>
+      </c>
+      <c r="E27" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="170" t="n">
+        <v>226153340</v>
+      </c>
+      <c r="G27" s="170" t="n">
+        <v>226153340</v>
+      </c>
+      <c r="H27" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="170" t="n">
+        <v>1665874816</v>
+      </c>
+      <c r="J27" s="162" t="inlineStr">
+        <is>
+          <t>100% 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="159" t="inlineStr">
+        <is>
+          <t>소계 합계</t>
+        </is>
+      </c>
+      <c r="C28" s="177" t="n">
+        <v>3291119067</v>
+      </c>
+      <c r="D28" s="177" t="n">
+        <v>3291119067</v>
+      </c>
+      <c r="E28" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="177" t="n">
+        <v>806557680</v>
+      </c>
+      <c r="G28" s="177" t="n">
+        <v>806557680</v>
+      </c>
+      <c r="H28" s="177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="177" t="n">
+        <v>4097676747</v>
+      </c>
+      <c r="J28" s="178" t="inlineStr">
+        <is>
+          <t>오차 0원 / 일치</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
@@ -22865,7 +23625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -75172,7 +75932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -77487,7 +78247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
+++ b/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월).xlsx
@@ -36,7 +36,7 @@
     <numFmt numFmtId="166" formatCode="###\-##\-#####"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -306,6 +306,12 @@
       <color rgb="001E293B"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="25">
     <fill>
@@ -449,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -698,6 +704,20 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -733,7 +753,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1299,6 +1319,22 @@
     </xf>
     <xf numFmtId="167" fontId="27" fillId="21" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="39" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="12" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3040,52 +3076,95 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="211" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="C8" s="212">
+        <f>SUM(D8,K8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="213">
+        <f>SUM(E8:J8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="214" t="n">
+        <v>93</v>
+      </c>
+      <c r="F8" s="214" t="n">
+        <v>41</v>
+      </c>
+      <c r="G8" s="214" t="n">
+        <v>34</v>
+      </c>
+      <c r="H8" s="214" t="n">
+        <v>19</v>
+      </c>
+      <c r="I8" s="214" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="214" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" s="215">
+        <f>SUM(L8:M8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="214" t="n">
+        <v>18</v>
+      </c>
+      <c r="M8" s="214" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>상품수</t>
         </is>
       </c>
-      <c r="C8" s="41">
-        <f>D8+K8</f>
-        <v/>
-      </c>
-      <c r="D8" s="42">
-        <f>SUM(E8:J8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="43">
+      <c r="C9" s="41">
+        <f>D9+K9</f>
+        <v/>
+      </c>
+      <c r="D9" s="42">
+        <f>SUM(E9:J9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,E$5)</f>
         <v/>
       </c>
-      <c r="F8" s="43">
+      <c r="F9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,F$5)</f>
         <v/>
       </c>
-      <c r="G8" s="43">
+      <c r="G9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,G$5)</f>
         <v/>
       </c>
-      <c r="H8" s="43">
+      <c r="H9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,H$5)</f>
         <v/>
       </c>
-      <c r="I8" s="43">
+      <c r="I9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,I$5)</f>
         <v/>
       </c>
-      <c r="J8" s="43">
+      <c r="J9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,J$5)</f>
         <v/>
       </c>
-      <c r="K8" s="44">
-        <f>SUM(L8:M8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="43">
+      <c r="K9" s="44">
+        <f>SUM(L9:M9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="216">
         <f>COUNTIF(②유기농raw!$A$6:$A$207,L$5)</f>
         <v/>
       </c>
-      <c r="M8" s="43">
+      <c r="M9" s="216">
         <f>COUNTIF(②유기농raw!$A$6:$A$207,M$5)</f>
         <v/>
       </c>
